--- a/research/traditional_assets/database/data/switzerland/switzerland_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_semiconductor.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08529999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E2">
         <v>0.0809</v>
@@ -599,115 +599,115 @@
         <v>-0.0858</v>
       </c>
       <c r="G2">
-        <v>0.5930845456462155</v>
+        <v>0.5780003925842194</v>
       </c>
       <c r="H2">
-        <v>0.4442336074214632</v>
+        <v>0.4193415415022438</v>
       </c>
       <c r="I2">
-        <v>0.1757201690497165</v>
+        <v>0.1389207524034701</v>
       </c>
       <c r="J2">
-        <v>0.1601227950588584</v>
+        <v>0.1364545597722585</v>
       </c>
       <c r="K2">
-        <v>2066</v>
+        <v>1339.4</v>
       </c>
       <c r="L2">
-        <v>0.1451964298264108</v>
+        <v>0.0906598799233784</v>
       </c>
       <c r="M2">
-        <v>606</v>
+        <v>614.2049</v>
       </c>
       <c r="N2">
-        <v>0.02684444838202396</v>
+        <v>0.02613193073519401</v>
       </c>
       <c r="O2">
-        <v>0.2933204259438529</v>
+        <v>0.4585671942660892</v>
       </c>
       <c r="P2">
-        <v>261</v>
+        <v>269.2029</v>
       </c>
       <c r="Q2">
-        <v>0.01156171786750537</v>
+        <v>0.01145349302246426</v>
       </c>
       <c r="R2">
-        <v>0.1263310745401743</v>
+        <v>0.2009876810512169</v>
       </c>
       <c r="S2">
-        <v>345</v>
+        <v>345.002</v>
       </c>
       <c r="T2">
-        <v>0.5693069306930693</v>
+        <v>0.5617050596633144</v>
       </c>
       <c r="U2">
-        <v>3077</v>
+        <v>3409</v>
       </c>
       <c r="V2">
-        <v>0.1363042370816629</v>
+        <v>0.1450391422736556</v>
       </c>
       <c r="W2">
-        <v>0.1338516358924522</v>
+        <v>-0.1780250347705146</v>
       </c>
       <c r="X2">
-        <v>0.1268256242184626</v>
+        <v>0.1267735319461213</v>
       </c>
       <c r="Y2">
-        <v>0.007026011673989668</v>
+        <v>-0.304798566716636</v>
       </c>
       <c r="Z2">
-        <v>0.9467451008354364</v>
+        <v>0.9181203448684273</v>
       </c>
       <c r="AA2">
-        <v>0.1515954717540508</v>
+        <v>-0.6002928158474168</v>
       </c>
       <c r="AB2">
-        <v>0.1164677127556764</v>
+        <v>0.1164224799669187</v>
       </c>
       <c r="AC2">
-        <v>0.03512775899837442</v>
+        <v>-0.7117053534571789</v>
       </c>
       <c r="AD2">
-        <v>3115</v>
+        <v>3582.8</v>
       </c>
       <c r="AE2">
-        <v>308.3885729579175</v>
+        <v>465.3784803318686</v>
       </c>
       <c r="AF2">
-        <v>3423.388572957917</v>
+        <v>4048.178480331869</v>
       </c>
       <c r="AG2">
-        <v>346.3885729579174</v>
+        <v>639.1784803318687</v>
       </c>
       <c r="AH2">
-        <v>0.1316794847916536</v>
+        <v>0.1469277096626556</v>
       </c>
       <c r="AI2">
-        <v>0.1612722432244471</v>
+        <v>0.1810269406739352</v>
       </c>
       <c r="AJ2">
-        <v>0.01511235360074945</v>
+        <v>0.02647449592656462</v>
       </c>
       <c r="AK2">
-        <v>0.01908436128326191</v>
+        <v>0.03372386505679495</v>
       </c>
       <c r="AL2">
-        <v>107</v>
+        <v>146.02</v>
       </c>
       <c r="AM2">
-        <v>16</v>
+        <v>32.31400000000001</v>
       </c>
       <c r="AN2">
-        <v>0.727973825660201</v>
+        <v>0.9044329787344149</v>
       </c>
       <c r="AO2">
-        <v>23.23364485981308</v>
+        <v>14.02273661142309</v>
       </c>
       <c r="AP2">
-        <v>0.08095082331337168</v>
+        <v>0.1613526004548087</v>
       </c>
       <c r="AQ2">
-        <v>155.375</v>
+        <v>63.36572383487032</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.1338516358924522</v>
       </c>
       <c r="X3">
-        <v>0.1268256242184626</v>
+        <v>0.1267735319461213</v>
       </c>
       <c r="Y3">
-        <v>0.007026011673989668</v>
+        <v>0.007078103946330877</v>
       </c>
       <c r="Z3">
         <v>0.9467451008354364</v>
@@ -799,10 +799,10 @@
         <v>0.1515954717540508</v>
       </c>
       <c r="AB3">
-        <v>0.1164677127556764</v>
+        <v>0.1164224799669187</v>
       </c>
       <c r="AC3">
-        <v>0.03512775899837442</v>
+        <v>0.03517299178713211</v>
       </c>
       <c r="AD3">
         <v>3115</v>
@@ -845,6 +845,518 @@
       </c>
       <c r="AQ3">
         <v>155.375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>u-blox Holding AG (SWX:UBXN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0101</v>
+      </c>
+      <c r="G4">
+        <v>0.718496683861459</v>
+      </c>
+      <c r="H4">
+        <v>0.2087939081306804</v>
+      </c>
+      <c r="I4">
+        <v>-0.1021861950380742</v>
+      </c>
+      <c r="J4">
+        <v>-0.1021861950380742</v>
+      </c>
+      <c r="K4">
+        <v>-89.59999999999999</v>
+      </c>
+      <c r="L4">
+        <v>-0.220093343158929</v>
+      </c>
+      <c r="M4">
+        <v>8.2029</v>
+      </c>
+      <c r="N4">
+        <v>0.01378638655462185</v>
+      </c>
+      <c r="O4">
+        <v>-0.09155022321428571</v>
+      </c>
+      <c r="P4">
+        <v>8.2029</v>
+      </c>
+      <c r="Q4">
+        <v>0.01378638655462185</v>
+      </c>
+      <c r="R4">
+        <v>-0.09155022321428571</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>110.3</v>
+      </c>
+      <c r="V4">
+        <v>0.1853781512605042</v>
+      </c>
+      <c r="W4">
+        <v>-0.1780250347705146</v>
+      </c>
+      <c r="X4">
+        <v>0.1212243115358684</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2992493463063829</v>
+      </c>
+      <c r="Z4">
+        <v>0.9715990453460621</v>
+      </c>
+      <c r="AA4">
+        <v>-0.09928400954653939</v>
+      </c>
+      <c r="AB4">
+        <v>0.1169693908186942</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2162534003652336</v>
+      </c>
+      <c r="AD4">
+        <v>36.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>36.3</v>
+      </c>
+      <c r="AG4">
+        <v>-74</v>
+      </c>
+      <c r="AH4">
+        <v>0.05750039600823697</v>
+      </c>
+      <c r="AI4">
+        <v>0.07848648648648648</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1420345489443378</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2101078932424759</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-15</v>
+      </c>
+      <c r="AN4">
+        <v>-1.080357142857143</v>
+      </c>
+      <c r="AP4">
+        <v>2.202380952380952</v>
+      </c>
+      <c r="AQ4">
+        <v>2.773333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Meyer Burger Technology AG (SWX:MBTN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.218</v>
+      </c>
+      <c r="G5">
+        <v>-1.923784901758014</v>
+      </c>
+      <c r="H5">
+        <v>-2.011375387797311</v>
+      </c>
+      <c r="I5">
+        <v>-3.850663741080062</v>
+      </c>
+      <c r="J5">
+        <v>-3.850663741080062</v>
+      </c>
+      <c r="K5">
+        <v>-605.9</v>
+      </c>
+      <c r="L5">
+        <v>-6.265770423991727</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>176.5</v>
+      </c>
+      <c r="V5">
+        <v>2.347074468085106</v>
+      </c>
+      <c r="W5">
+        <v>-1.31860718171926</v>
+      </c>
+      <c r="X5">
+        <v>0.5663973024350466</v>
+      </c>
+      <c r="Y5">
+        <v>-1.885004484154307</v>
+      </c>
+      <c r="Z5">
+        <v>0.1558933358535852</v>
+      </c>
+      <c r="AA5">
+        <v>-0.6002928158474168</v>
+      </c>
+      <c r="AB5">
+        <v>0.1114125376097621</v>
+      </c>
+      <c r="AC5">
+        <v>-0.7117053534571789</v>
+      </c>
+      <c r="AD5">
+        <v>397.6</v>
+      </c>
+      <c r="AE5">
+        <v>153.7959188122098</v>
+      </c>
+      <c r="AF5">
+        <v>551.3959188122099</v>
+      </c>
+      <c r="AG5">
+        <v>374.8959188122099</v>
+      </c>
+      <c r="AH5">
+        <v>0.8799864510088879</v>
+      </c>
+      <c r="AI5">
+        <v>0.9008325359891466</v>
+      </c>
+      <c r="AJ5">
+        <v>0.832924501518586</v>
+      </c>
+      <c r="AK5">
+        <v>0.8606506687080132</v>
+      </c>
+      <c r="AL5">
+        <v>35.3</v>
+      </c>
+      <c r="AM5">
+        <v>28.25</v>
+      </c>
+      <c r="AN5">
+        <v>-1.577151923839746</v>
+      </c>
+      <c r="AO5">
+        <v>-10.26912181303116</v>
+      </c>
+      <c r="AP5">
+        <v>-1.487092101595438</v>
+      </c>
+      <c r="AQ5">
+        <v>-12.83185840707965</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WISeKey International Holding AG (SWX:WIHN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0699</v>
+      </c>
+      <c r="G6">
+        <v>-0.3528571428571428</v>
+      </c>
+      <c r="H6">
+        <v>-0.6</v>
+      </c>
+      <c r="I6">
+        <v>-1.012177184071452</v>
+      </c>
+      <c r="J6">
+        <v>-1.012177184071452</v>
+      </c>
+      <c r="K6">
+        <v>-17.9</v>
+      </c>
+      <c r="L6">
+        <v>-0.8523809523809524</v>
+      </c>
+      <c r="M6">
+        <v>0.002</v>
+      </c>
+      <c r="N6">
+        <v>2.724795640326975E-05</v>
+      </c>
+      <c r="O6">
+        <v>-0.000111731843575419</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0.002</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>26.3</v>
+      </c>
+      <c r="V6">
+        <v>0.3583106267029972</v>
+      </c>
+      <c r="W6">
+        <v>-0.7552742616033755</v>
+      </c>
+      <c r="X6">
+        <v>0.1319888010637822</v>
+      </c>
+      <c r="Y6">
+        <v>-0.8872630626671577</v>
+      </c>
+      <c r="Z6">
+        <v>2.04407327073936</v>
+      </c>
+      <c r="AA6">
+        <v>-1</v>
+      </c>
+      <c r="AB6">
+        <v>0.1161669405630489</v>
+      </c>
+      <c r="AC6">
+        <v>-1.116166940563049</v>
+      </c>
+      <c r="AD6">
+        <v>15.4</v>
+      </c>
+      <c r="AE6">
+        <v>1.98360432750246</v>
+      </c>
+      <c r="AF6">
+        <v>17.38360432750246</v>
+      </c>
+      <c r="AG6">
+        <v>-8.91639567249754</v>
+      </c>
+      <c r="AH6">
+        <v>0.1914839629498625</v>
+      </c>
+      <c r="AI6">
+        <v>0.4912898122702209</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1382738413196092</v>
+      </c>
+      <c r="AK6">
+        <v>-0.9815922568865465</v>
+      </c>
+      <c r="AL6">
+        <v>2.01</v>
+      </c>
+      <c r="AM6">
+        <v>1.641</v>
+      </c>
+      <c r="AN6">
+        <v>-0.7677351812154146</v>
+      </c>
+      <c r="AO6">
+        <v>-10.69651741293533</v>
+      </c>
+      <c r="AP6">
+        <v>0.4445084835982622</v>
+      </c>
+      <c r="AQ6">
+        <v>-13.10176721511274</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SEALSQ Corp (NasdaqCM:LAES)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.06268656716417909</v>
+      </c>
+      <c r="H7">
+        <v>-0.1786069651741293</v>
+      </c>
+      <c r="I7">
+        <v>-0.6321431267088443</v>
+      </c>
+      <c r="J7">
+        <v>-0.6321431267088443</v>
+      </c>
+      <c r="K7">
+        <v>-13.2</v>
+      </c>
+      <c r="L7">
+        <v>-0.6567164179104477</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>18.9</v>
+      </c>
+      <c r="V7">
+        <v>0.1016675632060247</v>
+      </c>
+      <c r="W7">
+        <v>20.46511627906976</v>
+      </c>
+      <c r="X7">
+        <v>0.1239804552040674</v>
+      </c>
+      <c r="Y7">
+        <v>20.3411358238657</v>
+      </c>
+      <c r="Z7">
+        <v>1.607307670320726</v>
+      </c>
+      <c r="AA7">
+        <v>-1</v>
+      </c>
+      <c r="AB7">
+        <v>0.1168272455214799</v>
+      </c>
+      <c r="AC7">
+        <v>-1.11682724552148</v>
+      </c>
+      <c r="AD7">
+        <v>18.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.210384234238859</v>
+      </c>
+      <c r="AF7">
+        <v>19.71038423423886</v>
+      </c>
+      <c r="AG7">
+        <v>0.8103842342388603</v>
+      </c>
+      <c r="AH7">
+        <v>0.09586278585902581</v>
+      </c>
+      <c r="AI7">
+        <v>0.7906169455330351</v>
+      </c>
+      <c r="AJ7">
+        <v>0.004340327601823083</v>
+      </c>
+      <c r="AK7">
+        <v>0.1343835156701495</v>
+      </c>
+      <c r="AL7">
+        <v>1.71</v>
+      </c>
+      <c r="AM7">
+        <v>1.423</v>
+      </c>
+      <c r="AN7">
+        <v>-1.559339177343223</v>
+      </c>
+      <c r="AO7">
+        <v>-7.485380116959065</v>
+      </c>
+      <c r="AP7">
+        <v>-0.06830615595405094</v>
+      </c>
+      <c r="AQ7">
+        <v>-8.995080815179199</v>
       </c>
     </row>
   </sheetData>
@@ -1139,49 +1651,49 @@
         <v>23.9439252336449</v>
       </c>
       <c r="F2">
-        <v>3.03930620441384</v>
+        <v>3.02039612504718</v>
       </c>
       <c r="G2">
         <v>0.800044069398906</v>
       </c>
       <c r="H2">
-        <v>3.4023878478281</v>
+        <v>3.58465862539032</v>
       </c>
       <c r="I2">
         <v>0.131679484791654</v>
       </c>
       <c r="J2">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="K2">
         <v>22574.5</v>
       </c>
       <c r="L2">
-        <v>12369.0239098833</v>
+        <v>12133.1071254297</v>
       </c>
       <c r="M2">
         <v>22920.8885729579</v>
       </c>
       <c r="N2">
-        <v>23850.8415107397</v>
+        <v>24394.8613834749</v>
       </c>
       <c r="O2">
         <v>3423.38857295792</v>
       </c>
       <c r="P2">
-        <v>14558.8176008564</v>
+        <v>15338.7542580452</v>
       </c>
       <c r="Q2">
-        <v>0.116467712755676</v>
+        <v>0.116422479966919</v>
       </c>
       <c r="R2">
-        <v>0.113712353073551</v>
+        <v>0.112155367576068</v>
       </c>
       <c r="S2">
         <v>0.0481656</v>
       </c>
       <c r="T2">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1706,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.126825624218463</v>
+        <v>0.126773531946121</v>
       </c>
       <c r="X2">
-        <v>0.195505129712615</v>
+        <v>0.205590023356263</v>
       </c>
       <c r="Y2">
         <v>1.87005847450627</v>
       </c>
       <c r="Z2">
-        <v>3.45517049941276</v>
+        <v>3.69030077035249</v>
       </c>
       <c r="AA2">
         <v>3115</v>
@@ -1236,7 +1748,7 @@
         <v>22574.5</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999998</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1175353383358934</v>
+        <v>0.1174892188913704</v>
       </c>
       <c r="C2">
-        <v>25656.76065010335</v>
+        <v>25656.82468075896</v>
       </c>
       <c r="D2">
-        <v>22579.76065010335</v>
+        <v>22579.82468075896</v>
       </c>
       <c r="E2">
         <v>-3423.388572957917</v>
@@ -1475,19 +1987,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1175353383358934</v>
+        <v>0.1174892188913704</v>
       </c>
       <c r="T2">
         <v>1.655640159154051</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +2018,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.117414122741923</v>
+        <v>0.117356114631789</v>
       </c>
       <c r="C3">
-        <v>25435.0007495979</v>
+        <v>25438.84738861891</v>
       </c>
       <c r="D3">
-        <v>22617.97963532748</v>
+        <v>22621.82627434849</v>
       </c>
       <c r="E3">
         <v>-3163.409687228338</v>
@@ -1539,37 +2051,37 @@
         <v>2562</v>
       </c>
       <c r="M3">
-        <v>13.44090839221924</v>
+        <v>13.07693795219783</v>
       </c>
       <c r="N3">
-        <v>2548.559091607781</v>
+        <v>2548.923062047802</v>
       </c>
       <c r="O3">
-        <v>372.089627374736</v>
+        <v>372.1427670589791</v>
       </c>
       <c r="P3">
-        <v>2176.469464233045</v>
+        <v>2176.780294988823</v>
       </c>
       <c r="Q3">
-        <v>3893.469464233045</v>
+        <v>3893.780294988823</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1181541462039626</v>
+        <v>0.118107628920999</v>
       </c>
       <c r="T3">
         <v>1.669922145981501</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +2089,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.612116773529</v>
+        <v>195.9174241986371</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +2100,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1172929071479526</v>
+        <v>0.1172230103722076</v>
       </c>
       <c r="C4">
-        <v>25213.37044899765</v>
+        <v>25221.02664521537</v>
       </c>
       <c r="D4">
-        <v>22656.32822045681</v>
+        <v>22663.98441667453</v>
       </c>
       <c r="E4">
         <v>-2903.430801498759</v>
@@ -1621,37 +2133,37 @@
         <v>2562</v>
       </c>
       <c r="M4">
-        <v>26.88181678443849</v>
+        <v>26.15387590439567</v>
       </c>
       <c r="N4">
-        <v>2535.118183215562</v>
+        <v>2535.846124095604</v>
       </c>
       <c r="O4">
-        <v>370.127254749472</v>
+        <v>370.2335341179582</v>
       </c>
       <c r="P4">
-        <v>2164.99092846609</v>
+        <v>2165.612589977646</v>
       </c>
       <c r="Q4">
-        <v>3881.99092846609</v>
+        <v>3882.612589977646</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1187855828040332</v>
+        <v>0.1187386595634772</v>
       </c>
       <c r="T4">
         <v>1.684495601927879</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +2171,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.30605838676449</v>
+        <v>97.95871209931857</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +2182,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1171716915539822</v>
+        <v>0.1170899061126262</v>
       </c>
       <c r="C5">
-        <v>24991.87040862868</v>
+        <v>25003.3633274174</v>
       </c>
       <c r="D5">
-        <v>22694.80706581742</v>
+        <v>22706.29998460614</v>
       </c>
       <c r="E5">
         <v>-2643.45191576918</v>
@@ -1703,37 +2215,37 @@
         <v>2562</v>
       </c>
       <c r="M5">
-        <v>40.32272517665773</v>
+        <v>39.23081385659349</v>
       </c>
       <c r="N5">
-        <v>2521.677274823342</v>
+        <v>2522.769186143406</v>
       </c>
       <c r="O5">
-        <v>368.164882124208</v>
+        <v>368.3243011769373</v>
       </c>
       <c r="P5">
-        <v>2153.512392699135</v>
+        <v>2154.444884966469</v>
       </c>
       <c r="Q5">
-        <v>3870.512392699135</v>
+        <v>3871.444884966469</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1194300387154455</v>
+        <v>0.1193827011470373</v>
       </c>
       <c r="T5">
         <v>1.699369541502017</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +2253,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.537372257843</v>
+        <v>65.30580806621238</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +2264,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1170504759600117</v>
+        <v>0.1169568018530448</v>
       </c>
       <c r="C6">
-        <v>24770.50129331062</v>
+        <v>24785.858318655</v>
       </c>
       <c r="D6">
-        <v>22733.41683622893</v>
+        <v>22748.77386157331</v>
       </c>
       <c r="E6">
         <v>-2383.4730300396</v>
@@ -1785,37 +2297,37 @@
         <v>2562</v>
       </c>
       <c r="M6">
-        <v>53.76363356887698</v>
+        <v>52.30775180879133</v>
       </c>
       <c r="N6">
-        <v>2508.236366431123</v>
+        <v>2509.692248191209</v>
       </c>
       <c r="O6">
-        <v>366.2025094989439</v>
+        <v>366.4150682359165</v>
       </c>
       <c r="P6">
-        <v>2142.033856932179</v>
+        <v>2143.277179955292</v>
       </c>
       <c r="Q6">
-        <v>3859.033856932179</v>
+        <v>3860.277179955292</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1200879207916789</v>
+        <v>0.1200401602635883</v>
       </c>
       <c r="T6">
         <v>1.714553354817283</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +2335,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.65302919338224</v>
+        <v>48.97935604965929</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +2346,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1169292603660413</v>
+        <v>0.1168236975934634</v>
       </c>
       <c r="C7">
-        <v>24549.26377239489</v>
+        <v>24568.5125089807</v>
       </c>
       <c r="D7">
-        <v>22772.15820104279</v>
+        <v>22791.40693762859</v>
       </c>
       <c r="E7">
         <v>-2123.494144310022</v>
@@ -1867,37 +2379,37 @@
         <v>2562</v>
       </c>
       <c r="M7">
-        <v>67.20454196109623</v>
+        <v>65.38468976098916</v>
       </c>
       <c r="N7">
-        <v>2494.795458038904</v>
+        <v>2496.615310239011</v>
       </c>
       <c r="O7">
-        <v>364.2401368736799</v>
+        <v>364.5058352948956</v>
       </c>
       <c r="P7">
-        <v>2130.555321165224</v>
+        <v>2132.109474944115</v>
       </c>
       <c r="Q7">
-        <v>3847.555321165224</v>
+        <v>3849.109474944115</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1207596530168856</v>
+        <v>0.1207114606246983</v>
       </c>
       <c r="T7">
         <v>1.730056827360239</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2417,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.12242335470579</v>
+        <v>39.18348483972743</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2428,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.116808044772071</v>
+        <v>0.116690593333882</v>
       </c>
       <c r="C8">
-        <v>24328.15851980346</v>
+        <v>24351.32679513167</v>
       </c>
       <c r="D8">
-        <v>22811.03183418093</v>
+        <v>22834.20010950915</v>
       </c>
       <c r="E8">
         <v>-1863.515258580443</v>
@@ -1949,37 +2461,37 @@
         <v>2562</v>
       </c>
       <c r="M8">
-        <v>80.64545035331545</v>
+        <v>78.46162771318699</v>
       </c>
       <c r="N8">
-        <v>2481.354549646685</v>
+        <v>2483.538372286813</v>
       </c>
       <c r="O8">
-        <v>362.2777642484159</v>
+        <v>362.5966023538747</v>
       </c>
       <c r="P8">
-        <v>2119.076785398269</v>
+        <v>2120.941769932939</v>
       </c>
       <c r="Q8">
-        <v>3836.076785398269</v>
+        <v>3837.941769932939</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1214456774170968</v>
+        <v>0.1213970439722149</v>
       </c>
       <c r="T8">
         <v>1.74589016102113</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2499,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.7686861289215</v>
+        <v>32.6529040331062</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2510,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1166868291781005</v>
+        <v>0.1165574890743006</v>
       </c>
       <c r="C9">
-        <v>24107.1862140679</v>
+        <v>24134.30208059262</v>
       </c>
       <c r="D9">
-        <v>22850.03841417496</v>
+        <v>22877.15428069968</v>
       </c>
       <c r="E9">
         <v>-1603.536372850863</v>
@@ -2031,37 +2543,37 @@
         <v>2562</v>
       </c>
       <c r="M9">
-        <v>94.08635874553471</v>
+        <v>91.53856566538484</v>
       </c>
       <c r="N9">
-        <v>2467.913641254465</v>
+        <v>2470.461434334615</v>
       </c>
       <c r="O9">
-        <v>360.3153916231519</v>
+        <v>360.6873694128538</v>
       </c>
       <c r="P9">
-        <v>2107.598249631314</v>
+        <v>2109.774064921761</v>
       </c>
       <c r="Q9">
-        <v>3824.598249631314</v>
+        <v>3826.774064921761</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1221464550302157</v>
+        <v>0.122097371047635</v>
       </c>
       <c r="T9">
         <v>1.76206399648118</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2581,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.23030239621842</v>
+        <v>27.98820345694816</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2592,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1165656135841301</v>
+        <v>0.1164243848147192</v>
       </c>
       <c r="C10">
-        <v>23886.34753836883</v>
+        <v>23917.43927565937</v>
       </c>
       <c r="D10">
-        <v>22889.17862420547</v>
+        <v>22920.270361496</v>
       </c>
       <c r="E10">
         <v>-1343.557487121284</v>
@@ -2113,37 +2625,37 @@
         <v>2562</v>
       </c>
       <c r="M10">
-        <v>107.527267137754</v>
+        <v>104.6155036175827</v>
       </c>
       <c r="N10">
-        <v>2454.472732862246</v>
+        <v>2457.384496382417</v>
       </c>
       <c r="O10">
-        <v>358.3530189978879</v>
+        <v>358.7781364718329</v>
       </c>
       <c r="P10">
-        <v>2096.119713864358</v>
+        <v>2098.606359910584</v>
       </c>
       <c r="Q10">
-        <v>3813.119713864358</v>
+        <v>3815.606359910584</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1228624669392719</v>
+        <v>0.1228129226246948</v>
       </c>
       <c r="T10">
         <v>1.778589437059926</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2663,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.82651459669112</v>
+        <v>24.48967802482964</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2674,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1164443979901598</v>
+        <v>0.1162912805551378</v>
       </c>
       <c r="C11">
-        <v>23665.64318057584</v>
+        <v>23700.73929750313</v>
       </c>
       <c r="D11">
-        <v>22928.45315214205</v>
+        <v>22963.54926906934</v>
       </c>
       <c r="E11">
         <v>-1083.578601391705</v>
@@ -2195,37 +2707,37 @@
         <v>2562</v>
       </c>
       <c r="M11">
-        <v>120.9681755299732</v>
+        <v>117.6924415697805</v>
       </c>
       <c r="N11">
-        <v>2441.031824470027</v>
+        <v>2444.30755843022</v>
       </c>
       <c r="O11">
-        <v>356.3906463726239</v>
+        <v>356.868903530812</v>
       </c>
       <c r="P11">
-        <v>2084.641178097403</v>
+        <v>2087.438654899408</v>
       </c>
       <c r="Q11">
-        <v>3801.641178097403</v>
+        <v>3804.438654899408</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1235942153738019</v>
+        <v>0.1235442006100415</v>
       </c>
       <c r="T11">
         <v>1.795478074134909</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2745,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.17912408594766</v>
+        <v>21.76860268873746</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2756,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1163231823961893</v>
+        <v>0.1161581762955564</v>
       </c>
       <c r="C12">
-        <v>23445.07383328776</v>
+        <v>23484.2030702356</v>
       </c>
       <c r="D12">
-        <v>22967.86269058355</v>
+        <v>23006.9919275314</v>
       </c>
       <c r="E12">
         <v>-823.5997156621256</v>
@@ -2277,37 +2789,37 @@
         <v>2562</v>
       </c>
       <c r="M12">
-        <v>134.4090839221925</v>
+        <v>130.7693795219783</v>
       </c>
       <c r="N12">
-        <v>2427.590916077807</v>
+        <v>2431.230620478022</v>
       </c>
       <c r="O12">
-        <v>354.4282737473599</v>
+        <v>354.9596705897911</v>
       </c>
       <c r="P12">
-        <v>2073.162642330447</v>
+        <v>2076.27094988823</v>
       </c>
       <c r="Q12">
-        <v>3790.162642330447</v>
+        <v>3793.27094988823</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1243422248846548</v>
+        <v>0.1242917292172849</v>
       </c>
       <c r="T12">
         <v>1.812742014256002</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2827,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.06121167735289</v>
+        <v>19.59174241986371</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2838,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1162019668022189</v>
+        <v>0.116025072035975</v>
       </c>
       <c r="C13">
-        <v>23224.6401938734</v>
+        <v>23267.83152497468</v>
       </c>
       <c r="D13">
-        <v>23007.40793689877</v>
+        <v>23050.59926800006</v>
       </c>
       <c r="E13">
         <v>-563.6208299325467</v>
@@ -2359,37 +2871,37 @@
         <v>2562</v>
       </c>
       <c r="M13">
-        <v>147.8499923144117</v>
+        <v>143.8463174741761</v>
       </c>
       <c r="N13">
-        <v>2414.150007685588</v>
+        <v>2418.153682525824</v>
       </c>
       <c r="O13">
-        <v>352.4659011220958</v>
+        <v>353.0504376487703</v>
       </c>
       <c r="P13">
-        <v>2061.684106563493</v>
+        <v>2065.103244877054</v>
       </c>
       <c r="Q13">
-        <v>3778.684106563493</v>
+        <v>3782.103244877054</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1251070435979988</v>
+        <v>0.1250560562201966</v>
       </c>
       <c r="T13">
         <v>1.830393908087683</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2909,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.328374252139</v>
+        <v>17.81067492714883</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2920,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1160807512082485</v>
+        <v>0.1158919677763936</v>
       </c>
       <c r="C14">
-        <v>23004.34296451268</v>
+        <v>23051.62559991105</v>
       </c>
       <c r="D14">
-        <v>23047.08959326763</v>
+        <v>23094.372228666</v>
       </c>
       <c r="E14">
         <v>-303.6419442029678</v>
@@ -2441,37 +2953,37 @@
         <v>2562</v>
       </c>
       <c r="M14">
-        <v>161.2909007066309</v>
+        <v>156.923255426374</v>
       </c>
       <c r="N14">
-        <v>2400.709099293369</v>
+        <v>2405.076744573626</v>
       </c>
       <c r="O14">
-        <v>350.5035284968318</v>
+        <v>351.1412047077494</v>
       </c>
       <c r="P14">
-        <v>2050.205570796537</v>
+        <v>2053.935539865877</v>
       </c>
       <c r="Q14">
-        <v>3767.205570796537</v>
+        <v>3770.935539865877</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1258892445548279</v>
+        <v>0.1258377542913564</v>
       </c>
       <c r="T14">
         <v>1.848446981324628</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2991,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.88434306446075</v>
+        <v>16.3264520165531</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +3002,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1159595356142781</v>
+        <v>0.1157588635168122</v>
       </c>
       <c r="C15">
-        <v>22784.18285223816</v>
+        <v>22835.5862403754</v>
       </c>
       <c r="D15">
-        <v>23086.90836672269</v>
+        <v>23138.31175485993</v>
       </c>
       <c r="E15">
         <v>-43.66305847338799</v>
@@ -2523,37 +3035,37 @@
         <v>2562</v>
       </c>
       <c r="M15">
-        <v>174.7318090988502</v>
+        <v>170.0001933785718</v>
       </c>
       <c r="N15">
-        <v>2387.26819090115</v>
+        <v>2391.999806621428</v>
       </c>
       <c r="O15">
-        <v>348.5411558715679</v>
+        <v>349.2319717667285</v>
       </c>
       <c r="P15">
-        <v>2038.727035029582</v>
+        <v>2042.767834854699</v>
       </c>
       <c r="Q15">
-        <v>3755.727035029582</v>
+        <v>3759.7678348547</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1266894271428484</v>
+        <v>0.1266374224331175</v>
       </c>
       <c r="T15">
         <v>1.866915067739434</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +3073,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.66247052104069</v>
+        <v>15.07057109220286</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +3084,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1158383200203077</v>
+        <v>0.1156257592572308</v>
       </c>
       <c r="C16">
-        <v>22564.16056897707</v>
+        <v>22619.7143989065</v>
       </c>
       <c r="D16">
-        <v>23126.86496919118</v>
+        <v>23182.41879912061</v>
       </c>
       <c r="E16">
         <v>216.3158272561914</v>
@@ -2605,37 +3117,37 @@
         <v>2562</v>
       </c>
       <c r="M16">
-        <v>188.1727174910694</v>
+        <v>183.0771313307697</v>
       </c>
       <c r="N16">
-        <v>2373.827282508931</v>
+        <v>2378.92286866923</v>
       </c>
       <c r="O16">
-        <v>346.5787832463039</v>
+        <v>347.3227388257076</v>
       </c>
       <c r="P16">
-        <v>2027.248499262627</v>
+        <v>2031.600129843523</v>
       </c>
       <c r="Q16">
-        <v>3744.248499262627</v>
+        <v>3748.600129843523</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1275082186282648</v>
+        <v>0.1274556875084079</v>
       </c>
       <c r="T16">
         <v>1.88581264453598</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +3155,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.61515119810921</v>
+        <v>13.99410172847408</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +3166,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1157171044263373</v>
+        <v>0.1154926549976494</v>
       </c>
       <c r="C17">
-        <v>22344.27683159374</v>
+        <v>22404.01103532005</v>
       </c>
       <c r="D17">
-        <v>23166.96011753743</v>
+        <v>23226.69432126374</v>
       </c>
       <c r="E17">
         <v>476.2947129857698</v>
@@ -2687,37 +3199,37 @@
         <v>2562</v>
       </c>
       <c r="M17">
-        <v>201.6136258832886</v>
+        <v>196.1540692829675</v>
       </c>
       <c r="N17">
-        <v>2360.386374116712</v>
+        <v>2365.845930717032</v>
       </c>
       <c r="O17">
-        <v>344.6164106210398</v>
+        <v>345.4135058846867</v>
       </c>
       <c r="P17">
-        <v>2015.769963495672</v>
+        <v>2020.432424832346</v>
       </c>
       <c r="Q17">
-        <v>3732.769963495672</v>
+        <v>3737.432424832346</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.128346275795691</v>
+        <v>0.1282932058795875</v>
       </c>
       <c r="T17">
         <v>1.905154870198327</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +3237,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.7074744515686</v>
+        <v>13.06116161324248</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +3248,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1155958888323669</v>
+        <v>0.115359550738068</v>
       </c>
       <c r="C18">
-        <v>22124.53236193243</v>
+        <v>22188.47711677834</v>
       </c>
       <c r="D18">
-        <v>23207.19453360569</v>
+        <v>23271.1392884516</v>
       </c>
       <c r="E18">
         <v>736.2735987153496</v>
@@ -2769,37 +3281,37 @@
         <v>2562</v>
       </c>
       <c r="M18">
-        <v>215.0545342755079</v>
+        <v>209.2310072351653</v>
       </c>
       <c r="N18">
-        <v>2346.945465724492</v>
+        <v>2352.768992764835</v>
       </c>
       <c r="O18">
-        <v>342.6540379957758</v>
+        <v>343.5042729436659</v>
       </c>
       <c r="P18">
-        <v>2004.291427728716</v>
+        <v>2009.264719821169</v>
       </c>
       <c r="Q18">
-        <v>3721.291427728716</v>
+        <v>3726.264719821169</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1292042867051987</v>
+        <v>0.1291506651643667</v>
       </c>
       <c r="T18">
         <v>1.924957625043111</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +3319,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.91325729834556</v>
+        <v>12.24483901241482</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +3330,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1154746732383965</v>
+        <v>0.1152264464784866</v>
       </c>
       <c r="C19">
-        <v>21904.92788686069</v>
+        <v>21973.11361786054</v>
       </c>
       <c r="D19">
-        <v>23247.56894426353</v>
+        <v>23315.75467526339</v>
       </c>
       <c r="E19">
         <v>996.2524844449285</v>
@@ -2851,37 +3363,37 @@
         <v>2562</v>
       </c>
       <c r="M19">
-        <v>228.4954426677272</v>
+        <v>222.3079451873631</v>
       </c>
       <c r="N19">
-        <v>2333.504557332273</v>
+        <v>2339.692054812637</v>
       </c>
       <c r="O19">
-        <v>340.6916653705118</v>
+        <v>341.595040002645</v>
       </c>
       <c r="P19">
-        <v>1992.812891961761</v>
+        <v>1998.097014809992</v>
       </c>
       <c r="Q19">
-        <v>3709.812891961761</v>
+        <v>3715.097014809992</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1300829725763813</v>
+        <v>0.1300287861186585</v>
       </c>
       <c r="T19">
         <v>1.945237554703431</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3401,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.21247745726641</v>
+        <v>11.52455436462571</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3412,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1153534576444261</v>
+        <v>0.1150933422189052</v>
       </c>
       <c r="C20">
-        <v>21685.46413831311</v>
+        <v>21757.92152063408</v>
       </c>
       <c r="D20">
-        <v>23288.08408144553</v>
+        <v>23360.5414637665</v>
       </c>
       <c r="E20">
         <v>1256.231370174507</v>
@@ -2933,37 +3445,37 @@
         <v>2562</v>
       </c>
       <c r="M20">
-        <v>241.9363510599464</v>
+        <v>235.384883139561</v>
       </c>
       <c r="N20">
-        <v>2320.063648940054</v>
+        <v>2326.615116860439</v>
       </c>
       <c r="O20">
-        <v>338.7292927452478</v>
+        <v>339.6858070616241</v>
       </c>
       <c r="P20">
-        <v>1981.334356194806</v>
+        <v>1986.929309798815</v>
       </c>
       <c r="Q20">
-        <v>3698.334356194806</v>
+        <v>3703.929309798815</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1309830898102757</v>
+        <v>0.1309283246572014</v>
       </c>
       <c r="T20">
         <v>1.966012116794492</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3483,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.58956204297383</v>
+        <v>10.88430134436873</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3494,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1152322420504557</v>
+        <v>0.1149602379593238</v>
       </c>
       <c r="C21">
-        <v>21466.14185333558</v>
+        <v>21542.90181472663</v>
       </c>
       <c r="D21">
-        <v>23328.74068219758</v>
+        <v>23405.50064358864</v>
       </c>
       <c r="E21">
         <v>1516.210255904086</v>
@@ -3015,37 +3527,37 @@
         <v>2562</v>
       </c>
       <c r="M21">
-        <v>255.3772594521656</v>
+        <v>248.4618210917588</v>
       </c>
       <c r="N21">
-        <v>2306.622740547834</v>
+        <v>2313.538178908241</v>
       </c>
       <c r="O21">
-        <v>336.7669201199838</v>
+        <v>337.7765741206032</v>
       </c>
       <c r="P21">
-        <v>1969.855820427851</v>
+        <v>1975.761604787638</v>
       </c>
       <c r="Q21">
-        <v>3686.855820427851</v>
+        <v>3692.761604787638</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1319054321610564</v>
+        <v>0.1318500740238565</v>
       </c>
       <c r="T21">
         <v>1.987299631035948</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3565,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.032216672291</v>
+        <v>10.31144337887564</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3576,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1151110264564853</v>
+        <v>0.1148271336997424</v>
       </c>
       <c r="C22">
-        <v>21246.96177412995</v>
+        <v>21328.05549739905</v>
       </c>
       <c r="D22">
-        <v>23369.53948872153</v>
+        <v>23450.63321199064</v>
       </c>
       <c r="E22">
         <v>1776.189141633666</v>
@@ -3097,37 +3609,37 @@
         <v>2562</v>
       </c>
       <c r="M22">
-        <v>268.8181678443849</v>
+        <v>261.5387590439566</v>
       </c>
       <c r="N22">
-        <v>2293.181832155615</v>
+        <v>2300.461240956043</v>
       </c>
       <c r="O22">
-        <v>334.8045474947198</v>
+        <v>335.8673411795823</v>
       </c>
       <c r="P22">
-        <v>1958.377284660895</v>
+        <v>1964.593899776461</v>
       </c>
       <c r="Q22">
-        <v>3675.377284660895</v>
+        <v>3681.593899776461</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1328508330706066</v>
+        <v>0.132794867124678</v>
       </c>
       <c r="T22">
         <v>2.009119333133441</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3647,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.530605838676449</v>
+        <v>9.795871209931857</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3658,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1149898108625149</v>
+        <v>0.114694029440161</v>
       </c>
       <c r="C23">
-        <v>21027.92464809919</v>
+        <v>21113.38357361903</v>
       </c>
       <c r="D23">
-        <v>23410.48124842036</v>
+        <v>23495.94017394019</v>
       </c>
       <c r="E23">
         <v>2036.168027363245</v>
@@ -3179,37 +3691,37 @@
         <v>2562</v>
       </c>
       <c r="M23">
-        <v>282.2590762366041</v>
+        <v>274.6156969961544</v>
       </c>
       <c r="N23">
-        <v>2279.740923763396</v>
+        <v>2287.384303003846</v>
       </c>
       <c r="O23">
-        <v>332.8421748694558</v>
+        <v>333.9581082385615</v>
       </c>
       <c r="P23">
-        <v>1946.89874889394</v>
+        <v>1953.426194765284</v>
       </c>
       <c r="Q23">
-        <v>3663.89874889394</v>
+        <v>3670.426194765284</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1338201681803986</v>
+        <v>0.1337635790381785</v>
       </c>
       <c r="T23">
         <v>2.03149143275239</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3729,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.076767465406142</v>
+        <v>9.329401152316056</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3740,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1150752632685445</v>
+        <v>0.1145609251805796</v>
       </c>
       <c r="C24">
-        <v>20739.06847118946</v>
+        <v>20898.88705613577</v>
       </c>
       <c r="D24">
-        <v>23381.6039572402</v>
+        <v>23541.42254218651</v>
       </c>
       <c r="E24">
         <v>2296.146913092824</v>
@@ -3261,45 +3773,45 @@
         <v>2562</v>
       </c>
       <c r="M24">
-        <v>301.9914736634792</v>
+        <v>287.6926349483523</v>
       </c>
       <c r="N24">
-        <v>2260.008526336521</v>
+        <v>2274.307365051648</v>
       </c>
       <c r="O24">
-        <v>329.961244845132</v>
+        <v>332.0488752975405</v>
       </c>
       <c r="P24">
-        <v>1930.047281491389</v>
+        <v>1942.258489754107</v>
       </c>
       <c r="Q24">
-        <v>3647.047281491389</v>
+        <v>3659.258489754107</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1348143580365955</v>
+        <v>0.1347571297186918</v>
       </c>
       <c r="T24">
         <v>2.054437175951312</v>
       </c>
       <c r="U24">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.0450912</v>
+        <v>0.0429562</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.483683227609717</v>
+        <v>8.905337463574416</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3822,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1149634416745741</v>
+        <v>0.1147224509209982</v>
       </c>
       <c r="C25">
-        <v>20516.89233443794</v>
+        <v>20583.73680525854</v>
       </c>
       <c r="D25">
-        <v>23419.40670621826</v>
+        <v>23486.25117703886</v>
       </c>
       <c r="E25">
         <v>2556.125798822404</v>
@@ -3343,37 +3855,37 @@
         <v>2562</v>
       </c>
       <c r="M25">
-        <v>315.718358830001</v>
+        <v>309.7388444582206</v>
       </c>
       <c r="N25">
-        <v>2246.281641169999</v>
+        <v>2252.261155541779</v>
       </c>
       <c r="O25">
-        <v>327.9571196108199</v>
+        <v>328.8301287090998</v>
       </c>
       <c r="P25">
-        <v>1918.324521559179</v>
+        <v>1923.431026832679</v>
       </c>
       <c r="Q25">
-        <v>3635.324521559179</v>
+        <v>3640.431026832679</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1358343710059404</v>
+        <v>0.1357764869103872</v>
       </c>
       <c r="T25">
         <v>2.077978912480076</v>
       </c>
       <c r="U25">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3893,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.114827435104948</v>
+        <v>8.271484335396549</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3904,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1148516200806037</v>
+        <v>0.1146021566614168</v>
       </c>
       <c r="C26">
-        <v>20294.83863257332</v>
+        <v>20364.82147527748</v>
       </c>
       <c r="D26">
-        <v>23457.33189008322</v>
+        <v>23527.31473278738</v>
       </c>
       <c r="E26">
         <v>2816.104684551982</v>
@@ -3425,37 +3937,37 @@
         <v>2562</v>
       </c>
       <c r="M26">
-        <v>329.4452439965227</v>
+        <v>323.2057507390128</v>
       </c>
       <c r="N26">
-        <v>2232.554756003477</v>
+        <v>2238.794249260987</v>
       </c>
       <c r="O26">
-        <v>325.9529943765077</v>
+        <v>326.8639603921041</v>
       </c>
       <c r="P26">
-        <v>1906.60176162697</v>
+        <v>1911.930288868883</v>
       </c>
       <c r="Q26">
-        <v>3623.60176162697</v>
+        <v>3628.930288868883</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1368812264218469</v>
+        <v>0.1368226692913379</v>
       </c>
       <c r="T26">
         <v>2.102140168391176</v>
       </c>
       <c r="U26">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3975,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.77670962530891</v>
+        <v>7.926839154755027</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3986,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1147397984866333</v>
+        <v>0.1144818624018354</v>
       </c>
       <c r="C27">
-        <v>20072.90796137038</v>
+        <v>20146.04998851388</v>
       </c>
       <c r="D27">
-        <v>23495.38010460986</v>
+        <v>23568.52213175336</v>
       </c>
       <c r="E27">
         <v>3076.083570281562</v>
@@ -3507,37 +4019,37 @@
         <v>2562</v>
       </c>
       <c r="M27">
-        <v>343.1721291630445</v>
+        <v>336.672657019805</v>
       </c>
       <c r="N27">
-        <v>2218.827870836955</v>
+        <v>2225.327342980195</v>
       </c>
       <c r="O27">
-        <v>323.9488691421955</v>
+        <v>324.8977920751084</v>
       </c>
       <c r="P27">
-        <v>1894.87900169476</v>
+        <v>1900.429550905086</v>
       </c>
       <c r="Q27">
-        <v>3611.87900169476</v>
+        <v>3617.429550905086</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1379559979821777</v>
+        <v>0.1378967498691138</v>
       </c>
       <c r="T27">
         <v>2.126945724459905</v>
       </c>
       <c r="U27">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +4057,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.465641240296551</v>
+        <v>7.609765588564825</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +4068,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1146279768926629</v>
+        <v>0.114361568142254</v>
       </c>
       <c r="C28">
-        <v>19851.10092047556</v>
+        <v>19927.42310210534</v>
       </c>
       <c r="D28">
-        <v>23533.55194944462</v>
+        <v>23609.8741310744</v>
       </c>
       <c r="E28">
         <v>3336.062456011141</v>
@@ -3589,37 +4101,37 @@
         <v>2562</v>
       </c>
       <c r="M28">
-        <v>356.8990143295663</v>
+        <v>350.1395633005972</v>
       </c>
       <c r="N28">
-        <v>2205.100985670434</v>
+        <v>2211.860436699403</v>
       </c>
       <c r="O28">
-        <v>321.9447439078833</v>
+        <v>322.9316237581128</v>
       </c>
       <c r="P28">
-        <v>1883.15624176255</v>
+        <v>1888.92881294129</v>
       </c>
       <c r="Q28">
-        <v>3600.15624176255</v>
+        <v>3605.92881294129</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1390598174225174</v>
+        <v>0.1389998596516946</v>
       </c>
       <c r="T28">
         <v>2.152421700962924</v>
       </c>
       <c r="U28">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +4139,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.178501192592837</v>
+        <v>7.317082296696947</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +4150,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1145161552986925</v>
+        <v>0.1142412738826726</v>
       </c>
       <c r="C29">
-        <v>19629.4181134386</v>
+        <v>19708.94157851247</v>
       </c>
       <c r="D29">
-        <v>23571.84802813724</v>
+        <v>23651.37149321111</v>
       </c>
       <c r="E29">
         <v>3596.04134174072</v>
@@ -3671,37 +4183,37 @@
         <v>2562</v>
       </c>
       <c r="M29">
-        <v>370.6258994960881</v>
+        <v>363.6064695813894</v>
       </c>
       <c r="N29">
-        <v>2191.374100503912</v>
+        <v>2198.393530418611</v>
       </c>
       <c r="O29">
-        <v>319.9406186735711</v>
+        <v>320.9654554411171</v>
       </c>
       <c r="P29">
-        <v>1871.433481830341</v>
+        <v>1877.428074977493</v>
       </c>
       <c r="Q29">
-        <v>3588.43348183034</v>
+        <v>3594.428074977493</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1401938784913595</v>
+        <v>0.1401331916200994</v>
       </c>
       <c r="T29">
         <v>2.17859564942493</v>
       </c>
       <c r="U29">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +4221,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.912630778052362</v>
+        <v>7.046079248671134</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +4232,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.114930397704722</v>
+        <v>0.1141209796230912</v>
       </c>
       <c r="C30">
-        <v>19228.19226015292</v>
+        <v>19490.60618556588</v>
       </c>
       <c r="D30">
-        <v>23430.60106058114</v>
+        <v>23693.01498599409</v>
       </c>
       <c r="E30">
         <v>3856.0202274703</v>
@@ -3753,45 +4265,45 @@
         <v>2562</v>
       </c>
       <c r="M30">
-        <v>400.367484023552</v>
+        <v>377.0733758621816</v>
       </c>
       <c r="N30">
-        <v>2161.632515976448</v>
+        <v>2184.926624137818</v>
       </c>
       <c r="O30">
-        <v>315.5983473325614</v>
+        <v>318.9992871241215</v>
       </c>
       <c r="P30">
-        <v>1846.034168643886</v>
+        <v>1865.927337013697</v>
       </c>
       <c r="Q30">
-        <v>3563.034168643886</v>
+        <v>3582.927337013697</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1413594412565584</v>
+        <v>0.1412980050320711</v>
       </c>
       <c r="T30">
         <v>2.205496652010881</v>
       </c>
       <c r="U30">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.04697</v>
+        <v>0.0442372</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.399121063111329</v>
+        <v>6.794433561218593</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +4314,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1148373641107516</v>
+        <v>0.1144217073635098</v>
       </c>
       <c r="C31">
-        <v>18999.78805943095</v>
+        <v>19126.79504129604</v>
       </c>
       <c r="D31">
-        <v>23462.17574558874</v>
+        <v>23589.18272745384</v>
       </c>
       <c r="E31">
         <v>4115.999113199878</v>
@@ -3835,37 +4347,37 @@
         <v>2562</v>
       </c>
       <c r="M31">
-        <v>414.6663227386787</v>
+        <v>403.3572412094421</v>
       </c>
       <c r="N31">
-        <v>2147.333677261321</v>
+        <v>2158.642758790558</v>
       </c>
       <c r="O31">
-        <v>313.5107168801529</v>
+        <v>315.1618427834214</v>
       </c>
       <c r="P31">
-        <v>1833.822960381168</v>
+        <v>1843.480916007136</v>
       </c>
       <c r="Q31">
-        <v>3550.822960381168</v>
+        <v>3560.480916007136</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1425578367757065</v>
+        <v>0.1424956300894504</v>
       </c>
       <c r="T31">
         <v>2.233155429317562</v>
       </c>
       <c r="U31">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4385,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.178461716107491</v>
+        <v>6.351689614689944</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4396,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1147443305167812</v>
+        <v>0.1143159311039284</v>
       </c>
       <c r="C32">
-        <v>18771.46907257364</v>
+        <v>18903.23360586291</v>
       </c>
       <c r="D32">
-        <v>23493.83564446101</v>
+        <v>23625.60017775029</v>
       </c>
       <c r="E32">
         <v>4375.977998929457</v>
@@ -3917,37 +4429,37 @@
         <v>2562</v>
       </c>
       <c r="M32">
-        <v>428.9651614538056</v>
+        <v>417.2661115959745</v>
       </c>
       <c r="N32">
-        <v>2133.034838546194</v>
+        <v>2144.733888404025</v>
       </c>
       <c r="O32">
-        <v>311.4230864277444</v>
+        <v>313.1311477069877</v>
       </c>
       <c r="P32">
-        <v>1821.61175211845</v>
+        <v>1831.602740697038</v>
       </c>
       <c r="Q32">
-        <v>3538.61175211845</v>
+        <v>3548.602740697038</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1437904721668304</v>
+        <v>0.143727473005612</v>
       </c>
       <c r="T32">
         <v>2.261604457404434</v>
       </c>
       <c r="U32">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4467,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.972512992237242</v>
+        <v>6.139966627533614</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4478,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1146512969228109</v>
+        <v>0.114210154844347</v>
       </c>
       <c r="C33">
-        <v>18543.23564501028</v>
+        <v>18679.78478826216</v>
       </c>
       <c r="D33">
-        <v>23525.58110262723</v>
+        <v>23662.13024587912</v>
       </c>
       <c r="E33">
         <v>4635.956884659037</v>
@@ -3999,37 +4511,37 @@
         <v>2562</v>
       </c>
       <c r="M33">
-        <v>443.2640001689325</v>
+        <v>431.1749819825071</v>
       </c>
       <c r="N33">
-        <v>2118.735999831068</v>
+        <v>2130.825018017493</v>
       </c>
       <c r="O33">
-        <v>309.3354559753358</v>
+        <v>311.1004526305539</v>
       </c>
       <c r="P33">
-        <v>1809.400543855732</v>
+        <v>1819.724565386939</v>
       </c>
       <c r="Q33">
-        <v>3526.400543855731</v>
+        <v>3536.724565386939</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1450588361200157</v>
+        <v>0.1449950215135464</v>
       </c>
       <c r="T33">
         <v>2.290878095001072</v>
       </c>
       <c r="U33">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4549,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.779851282810234</v>
+        <v>5.941903187935754</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4560,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1149681833288404</v>
+        <v>0.1141043785847656</v>
       </c>
       <c r="C34">
-        <v>18175.47690318811</v>
+        <v>18456.44911169422</v>
       </c>
       <c r="D34">
-        <v>23417.80124653464</v>
+        <v>23698.77345504075</v>
       </c>
       <c r="E34">
         <v>4895.935770388616</v>
@@ -4081,45 +4593,45 @@
         <v>2562</v>
       </c>
       <c r="M34">
-        <v>470.0418253990792</v>
+        <v>445.0838523690396</v>
       </c>
       <c r="N34">
-        <v>2091.958174600921</v>
+        <v>2116.91614763096</v>
       </c>
       <c r="O34">
-        <v>305.4258934917344</v>
+        <v>309.0697575541202</v>
       </c>
       <c r="P34">
-        <v>1786.532281109186</v>
+        <v>1807.84639007684</v>
       </c>
       <c r="Q34">
-        <v>3503.532281109186</v>
+        <v>3524.84639007684</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1463645048953536</v>
+        <v>0.1462998508599494</v>
       </c>
       <c r="T34">
         <v>2.321012721938786</v>
       </c>
       <c r="U34">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.450578781632437</v>
+        <v>5.756218713312761</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4642,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.11488795973487</v>
+        <v>0.1142240583251842</v>
       </c>
       <c r="C35">
-        <v>17942.69031241254</v>
+        <v>18155.01897146788</v>
       </c>
       <c r="D35">
-        <v>23444.99354148865</v>
+        <v>23657.32220054399</v>
       </c>
       <c r="E35">
         <v>5155.914656118195</v>
@@ -4163,37 +4675,37 @@
         <v>2562</v>
       </c>
       <c r="M35">
-        <v>484.7306324428004</v>
+        <v>465.856165338833</v>
       </c>
       <c r="N35">
-        <v>2077.2693675572</v>
+        <v>2096.143834661167</v>
       </c>
       <c r="O35">
-        <v>303.2813276633511</v>
+        <v>306.0369998605304</v>
       </c>
       <c r="P35">
-        <v>1773.988039893849</v>
+        <v>1790.106834800637</v>
       </c>
       <c r="Q35">
-        <v>3490.988039893849</v>
+        <v>3507.106834800637</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.147709148858015</v>
+        <v>0.1476436303360958</v>
       </c>
       <c r="T35">
         <v>2.352046889979118</v>
       </c>
       <c r="U35">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4713,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.285409727643576</v>
+        <v>5.499551558229504</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4724,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1148077361408996</v>
+        <v>0.1141251140656028</v>
       </c>
       <c r="C36">
-        <v>17709.96694537829</v>
+        <v>17929.29917569114</v>
       </c>
       <c r="D36">
-        <v>23472.24906018398</v>
+        <v>23691.58129049683</v>
       </c>
       <c r="E36">
         <v>5415.893541847774</v>
@@ -4245,37 +4757,37 @@
         <v>2562</v>
       </c>
       <c r="M36">
-        <v>499.4194394865216</v>
+        <v>479.9730188339491</v>
       </c>
       <c r="N36">
-        <v>2062.580560513478</v>
+        <v>2082.026981166051</v>
       </c>
       <c r="O36">
-        <v>301.1367618349678</v>
+        <v>303.9759392502434</v>
       </c>
       <c r="P36">
-        <v>1761.443798678511</v>
+        <v>1778.051041915808</v>
       </c>
       <c r="Q36">
-        <v>3478.443798678511</v>
+        <v>3495.051041915808</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1490945396074237</v>
+        <v>0.1490281304024285</v>
       </c>
       <c r="T36">
         <v>2.384021487354007</v>
       </c>
       <c r="U36">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4795,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.129956500359942</v>
+        <v>5.337800041810989</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4806,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1147275125469292</v>
+        <v>0.1140261698060214</v>
       </c>
       <c r="C37">
-        <v>17477.30702284058</v>
+        <v>17703.67874765845</v>
       </c>
       <c r="D37">
-        <v>23499.56802337585</v>
+        <v>23725.93974819372</v>
       </c>
       <c r="E37">
         <v>5675.872427577353</v>
@@ -4327,37 +4839,37 @@
         <v>2562</v>
       </c>
       <c r="M37">
-        <v>514.1082465302428</v>
+        <v>494.0898723290652</v>
       </c>
       <c r="N37">
-        <v>2047.891753469757</v>
+        <v>2067.910127670935</v>
       </c>
       <c r="O37">
-        <v>298.9921960065845</v>
+        <v>301.9148786399564</v>
       </c>
       <c r="P37">
-        <v>1748.899557463173</v>
+        <v>1765.995249030978</v>
       </c>
       <c r="Q37">
-        <v>3465.899557463173</v>
+        <v>3482.995249030978</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1505225577645065</v>
+        <v>0.1504552304708021</v>
       </c>
       <c r="T37">
         <v>2.416979918494276</v>
       </c>
       <c r="U37">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4877,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.983386314635371</v>
+        <v>5.185291469187818</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4888,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1146472889529588</v>
+        <v>0.11392722554644</v>
       </c>
       <c r="C38">
-        <v>17244.71076658354</v>
+        <v>17478.15812031865</v>
       </c>
       <c r="D38">
-        <v>23526.95065284839</v>
+        <v>23760.3980065835</v>
       </c>
       <c r="E38">
         <v>5935.851313306932</v>
@@ -4409,37 +4921,37 @@
         <v>2562</v>
       </c>
       <c r="M38">
-        <v>528.797053573964</v>
+        <v>508.2067258241814</v>
       </c>
       <c r="N38">
-        <v>2033.202946426036</v>
+        <v>2053.793274175819</v>
       </c>
       <c r="O38">
-        <v>296.8476301782012</v>
+        <v>299.8538180296695</v>
       </c>
       <c r="P38">
-        <v>1736.355316247835</v>
+        <v>1753.939456146149</v>
       </c>
       <c r="Q38">
-        <v>3453.355316247835</v>
+        <v>3470.939456146149</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1519952014889981</v>
+        <v>0.1519269274163124</v>
       </c>
       <c r="T38">
         <v>2.450968300607679</v>
       </c>
       <c r="U38">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4959,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.844958917006611</v>
+        <v>5.041255595043712</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4970,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1145670653589884</v>
+        <v>0.1138282812868586</v>
       </c>
       <c r="C39">
-        <v>17012.17839942622</v>
+        <v>17252.73772913941</v>
       </c>
       <c r="D39">
-        <v>23554.39717142065</v>
+        <v>23794.95650113383</v>
       </c>
       <c r="E39">
         <v>6195.830199036511</v>
@@ -4491,37 +5003,37 @@
         <v>2562</v>
       </c>
       <c r="M39">
-        <v>543.4858606176853</v>
+        <v>522.3235793192974</v>
       </c>
       <c r="N39">
-        <v>2018.514139382315</v>
+        <v>2039.676420680702</v>
       </c>
       <c r="O39">
-        <v>294.7030643498179</v>
+        <v>297.7927574193826</v>
       </c>
       <c r="P39">
-        <v>1723.811075032497</v>
+        <v>1741.88366326132</v>
       </c>
       <c r="Q39">
-        <v>3440.811075032497</v>
+        <v>3458.88366326132</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1535145958079181</v>
+        <v>0.1534453448997755</v>
       </c>
       <c r="T39">
         <v>2.48603567897865</v>
       </c>
       <c r="U39">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +5041,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.714014081411838</v>
+        <v>4.905005443826315</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +5052,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.114486841765018</v>
+        <v>0.1137293370272772</v>
       </c>
       <c r="C40">
-        <v>16779.7101452287</v>
+        <v>17027.41801212556</v>
       </c>
       <c r="D40">
-        <v>23581.9078029527</v>
+        <v>23829.61566984957</v>
       </c>
       <c r="E40">
         <v>6455.80908476609</v>
@@ -4573,37 +5085,37 @@
         <v>2562</v>
       </c>
       <c r="M40">
-        <v>558.1746676614065</v>
+        <v>536.4404328144136</v>
       </c>
       <c r="N40">
-        <v>2003.825332338593</v>
+        <v>2025.559567185586</v>
       </c>
       <c r="O40">
-        <v>292.5584985214346</v>
+        <v>295.7316968090956</v>
       </c>
       <c r="P40">
-        <v>1711.266833817159</v>
+        <v>1729.827870376491</v>
       </c>
       <c r="Q40">
-        <v>3428.266833817159</v>
+        <v>3446.827870376491</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1550830028468032</v>
+        <v>0.1550127435923825</v>
       </c>
       <c r="T40">
         <v>2.522234263103523</v>
       </c>
       <c r="U40">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +5123,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.589961079269422</v>
+        <v>4.775926353199306</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +5134,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1144066181710476</v>
+        <v>0.1136303927676958</v>
       </c>
       <c r="C41">
-        <v>16547.30622889806</v>
+        <v>16802.19940983762</v>
       </c>
       <c r="D41">
-        <v>23609.48277235165</v>
+        <v>23864.3759532912</v>
       </c>
       <c r="E41">
         <v>6715.78797049567</v>
@@ -4655,37 +5167,37 @@
         <v>2562</v>
       </c>
       <c r="M41">
-        <v>572.8634747051277</v>
+        <v>550.5572863095299</v>
       </c>
       <c r="N41">
-        <v>1989.136525294872</v>
+        <v>2011.44271369047</v>
       </c>
       <c r="O41">
-        <v>290.4139326930513</v>
+        <v>293.6706361988086</v>
       </c>
       <c r="P41">
-        <v>1698.722592601821</v>
+        <v>1717.772077491662</v>
       </c>
       <c r="Q41">
-        <v>3415.722592601821</v>
+        <v>3434.772077491662</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1567028330672912</v>
+        <v>0.1566315324060586</v>
       </c>
       <c r="T41">
         <v>2.559619686052164</v>
       </c>
       <c r="U41">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +5205,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.472269769544564</v>
+        <v>4.653466703117272</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +5216,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1143263945770772</v>
+        <v>0.1135314485081144</v>
       </c>
       <c r="C42">
-        <v>16314.96687639461</v>
+        <v>16577.08236541043</v>
       </c>
       <c r="D42">
-        <v>23637.12230557778</v>
+        <v>23899.2377945936</v>
       </c>
       <c r="E42">
         <v>6975.766856225249</v>
@@ -4737,37 +5249,37 @@
         <v>2562</v>
       </c>
       <c r="M42">
-        <v>587.5522817488489</v>
+        <v>564.674139804646</v>
       </c>
       <c r="N42">
-        <v>1974.447718251151</v>
+        <v>1997.325860195354</v>
       </c>
       <c r="O42">
-        <v>288.269366864668</v>
+        <v>291.6095755885216</v>
       </c>
       <c r="P42">
-        <v>1686.178351386483</v>
+        <v>1705.716284606832</v>
       </c>
       <c r="Q42">
-        <v>3403.178351386483</v>
+        <v>3422.716284606832</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.158376657628462</v>
+        <v>0.1583042808468573</v>
       </c>
       <c r="T42">
         <v>2.598251289765758</v>
       </c>
       <c r="U42">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +5287,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.36046302530595</v>
+        <v>4.537130035539341</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +5298,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1142461709831068</v>
+        <v>0.113432504248533</v>
       </c>
       <c r="C43">
-        <v>16082.69231473802</v>
+        <v>16352.067324572</v>
       </c>
       <c r="D43">
-        <v>23664.82662965076</v>
+        <v>23934.20163948474</v>
       </c>
       <c r="E43">
         <v>7235.745741954828</v>
@@ -4819,37 +5331,37 @@
         <v>2562</v>
       </c>
       <c r="M43">
-        <v>602.2410887925702</v>
+        <v>578.7909932997621</v>
       </c>
       <c r="N43">
-        <v>1959.75891120743</v>
+        <v>1983.209006700238</v>
       </c>
       <c r="O43">
-        <v>286.1248010362847</v>
+        <v>289.5485149782347</v>
       </c>
       <c r="P43">
-        <v>1673.634110171145</v>
+        <v>1693.660491722003</v>
       </c>
       <c r="Q43">
-        <v>3390.634110171145</v>
+        <v>3410.660491722003</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1601072220052658</v>
+        <v>0.1600337326246322</v>
       </c>
       <c r="T43">
         <v>2.638192439367949</v>
       </c>
       <c r="U43">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +5369,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.254110268591171</v>
+        <v>4.426468327355455</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +5380,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1146680993891364</v>
+        <v>0.1133335599889516</v>
       </c>
       <c r="C44">
-        <v>15677.72812133506</v>
+        <v>16127.15473566252</v>
       </c>
       <c r="D44">
-        <v>23519.84132197738</v>
+        <v>23969.26793630484</v>
       </c>
       <c r="E44">
         <v>7495.724627684407</v>
@@ -4901,45 +5413,45 @@
         <v>2562</v>
       </c>
       <c r="M44">
-        <v>632.2166543171907</v>
+        <v>592.9078467948783</v>
       </c>
       <c r="N44">
-        <v>1929.783345682809</v>
+        <v>1969.092153205122</v>
       </c>
       <c r="O44">
-        <v>281.7483684696901</v>
+        <v>287.4874543679477</v>
       </c>
       <c r="P44">
-        <v>1648.034977213119</v>
+        <v>1681.604698837174</v>
       </c>
       <c r="Q44">
-        <v>3365.034977213119</v>
+        <v>3398.604698837174</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1618974610157524</v>
+        <v>0.1618228206706062</v>
       </c>
       <c r="T44">
         <v>2.679510869990905</v>
       </c>
       <c r="U44">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.052408272551792</v>
+        <v>4.321076224323181</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5462,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.114599831795166</v>
+        <v>0.1136018357293702</v>
       </c>
       <c r="C45">
-        <v>15441.08712663984</v>
+        <v>15772.335156702</v>
       </c>
       <c r="D45">
-        <v>23543.17921301174</v>
+        <v>23874.4272430739</v>
       </c>
       <c r="E45">
         <v>7755.703513413986</v>
@@ -4983,37 +5495,37 @@
         <v>2562</v>
       </c>
       <c r="M45">
-        <v>647.2694318009333</v>
+        <v>618.2037923763663</v>
       </c>
       <c r="N45">
-        <v>1914.730568199067</v>
+        <v>1943.796207623634</v>
       </c>
       <c r="O45">
-        <v>279.5506629570637</v>
+        <v>283.7942463130505</v>
       </c>
       <c r="P45">
-        <v>1635.179905242003</v>
+        <v>1660.001961310583</v>
       </c>
       <c r="Q45">
-        <v>3352.179905242003</v>
+        <v>3377.001961310583</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1637505154301158</v>
+        <v>0.1636746837357371</v>
       </c>
       <c r="T45">
         <v>2.722279070109404</v>
       </c>
       <c r="U45">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5533,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.95816621970175</v>
+        <v>4.144264450646136</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5544,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1145315642011956</v>
+        <v>0.1135114314697888</v>
       </c>
       <c r="C46">
-        <v>15204.49249264329</v>
+        <v>15544.23198044997</v>
       </c>
       <c r="D46">
-        <v>23566.56346474477</v>
+        <v>23906.30295255145</v>
       </c>
       <c r="E46">
         <v>8015.682399143565</v>
@@ -5065,37 +5577,37 @@
         <v>2562</v>
       </c>
       <c r="M46">
-        <v>662.3222092846759</v>
+        <v>632.580624757212</v>
       </c>
       <c r="N46">
-        <v>1899.677790715324</v>
+        <v>1929.419375242788</v>
       </c>
       <c r="O46">
-        <v>277.3529574444373</v>
+        <v>281.695228785447</v>
       </c>
       <c r="P46">
-        <v>1622.324833270887</v>
+        <v>1647.724146457341</v>
       </c>
       <c r="Q46">
-        <v>3339.324833270887</v>
+        <v>3364.724146457341</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1656697503592778</v>
+        <v>0.1655926847674799</v>
       </c>
       <c r="T46">
         <v>2.76657470594642</v>
       </c>
       <c r="U46">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5615,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.868207896526711</v>
+        <v>4.050076622222361</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5626,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1144632966072252</v>
+        <v>0.1134210272102074</v>
       </c>
       <c r="C47">
-        <v>14967.94435762602</v>
+        <v>15316.21403508048</v>
       </c>
       <c r="D47">
-        <v>23589.99421545708</v>
+        <v>23938.26389291155</v>
       </c>
       <c r="E47">
         <v>8275.661284873144</v>
@@ -5147,37 +5659,37 @@
         <v>2562</v>
       </c>
       <c r="M47">
-        <v>677.3749867684185</v>
+        <v>646.9574571380577</v>
       </c>
       <c r="N47">
-        <v>1884.625013231582</v>
+        <v>1915.042542861942</v>
       </c>
       <c r="O47">
-        <v>275.1552519318109</v>
+        <v>279.5962112578435</v>
       </c>
       <c r="P47">
-        <v>1609.469761299771</v>
+        <v>1635.446331604099</v>
       </c>
       <c r="Q47">
-        <v>3326.469761299771</v>
+        <v>3352.446331604099</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1676587756495003</v>
+        <v>0.1675804312912861</v>
       </c>
       <c r="T47">
         <v>2.81248109217751</v>
       </c>
       <c r="U47">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5697,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.78224772104834</v>
+        <v>3.960074919506309</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5708,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1143950290132548</v>
+        <v>0.113330622950626</v>
       </c>
       <c r="C48">
-        <v>14731.44286041907</v>
+        <v>15088.28166289314</v>
       </c>
       <c r="D48">
-        <v>23613.47160397971</v>
+        <v>23970.31040645378</v>
       </c>
       <c r="E48">
         <v>8535.640170602725</v>
@@ -5229,37 +5741,37 @@
         <v>2562</v>
       </c>
       <c r="M48">
-        <v>692.4277642521612</v>
+        <v>661.3342895189036</v>
       </c>
       <c r="N48">
-        <v>1869.572235747839</v>
+        <v>1900.665710481097</v>
       </c>
       <c r="O48">
-        <v>272.9575464191844</v>
+        <v>277.4971937302401</v>
       </c>
       <c r="P48">
-        <v>1596.614689328655</v>
+        <v>1623.168516750856</v>
       </c>
       <c r="Q48">
-        <v>3313.614689328655</v>
+        <v>3340.168516750857</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1697214685430644</v>
+        <v>0.1696417980567148</v>
       </c>
       <c r="T48">
         <v>2.860087714935676</v>
       </c>
       <c r="U48">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5779,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.70002494450381</v>
+        <v>3.873986334299649</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5790,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1143267614192844</v>
+        <v>0.1132402186910446</v>
       </c>
       <c r="C49">
-        <v>14494.98814040671</v>
+        <v>14860.43520802295</v>
       </c>
       <c r="D49">
-        <v>23636.99576969693</v>
+        <v>24002.44283731317</v>
       </c>
       <c r="E49">
         <v>8795.619056332303</v>
@@ -5311,37 +5823,37 @@
         <v>2562</v>
       </c>
       <c r="M49">
-        <v>707.4805417359038</v>
+        <v>675.7111218997493</v>
       </c>
       <c r="N49">
-        <v>1854.519458264096</v>
+        <v>1886.288878100251</v>
       </c>
       <c r="O49">
-        <v>270.759840906558</v>
+        <v>275.3981762026366</v>
       </c>
       <c r="P49">
-        <v>1583.759617357538</v>
+        <v>1610.890701897614</v>
       </c>
       <c r="Q49">
-        <v>3300.759617357538</v>
+        <v>3327.890701897614</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1718619989043101</v>
+        <v>0.1717809522472539</v>
       </c>
       <c r="T49">
         <v>2.909490814024341</v>
       </c>
       <c r="U49">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.146</v>
       </c>
       <c r="W49">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5861,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.621301009514367</v>
+        <v>3.791561093144337</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5872,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.114258493825314</v>
+        <v>0.1131498144314632</v>
       </c>
       <c r="C50">
-        <v>14258.58033752923</v>
+        <v>14632.67501645267</v>
       </c>
       <c r="D50">
-        <v>23660.56685254903</v>
+        <v>24034.66153147247</v>
       </c>
       <c r="E50">
         <v>9055.597942061881</v>
@@ -5393,37 +5905,37 @@
         <v>2562</v>
       </c>
       <c r="M50">
-        <v>722.5333192196463</v>
+        <v>690.0879542805949</v>
       </c>
       <c r="N50">
-        <v>1839.466680780354</v>
+        <v>1871.912045719405</v>
       </c>
       <c r="O50">
-        <v>268.5621353939316</v>
+        <v>273.2991586750331</v>
       </c>
       <c r="P50">
-        <v>1570.904545386422</v>
+        <v>1598.612887044372</v>
       </c>
       <c r="Q50">
-        <v>3287.904545386422</v>
+        <v>3315.612887044372</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.174084857356373</v>
+        <v>0.1740023815989676</v>
       </c>
       <c r="T50">
         <v>2.960794032308722</v>
       </c>
       <c r="U50">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.146</v>
       </c>
       <c r="W50">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5943,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.545857238482819</v>
+        <v>3.712570237037164</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5954,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1141902262313436</v>
+        <v>0.1130594101718818</v>
       </c>
       <c r="C51">
-        <v>14022.21959228562</v>
+        <v>14405.00143602519</v>
       </c>
       <c r="D51">
-        <v>23684.184993035</v>
+        <v>24066.96683677457</v>
       </c>
       <c r="E51">
         <v>9315.576827791461</v>
@@ -5475,37 +5987,37 @@
         <v>2562</v>
       </c>
       <c r="M51">
-        <v>737.5860967033891</v>
+        <v>704.4647866614407</v>
       </c>
       <c r="N51">
-        <v>1824.413903296611</v>
+        <v>1857.535213338559</v>
       </c>
       <c r="O51">
-        <v>266.3644298813052</v>
+        <v>271.2001411474296</v>
       </c>
       <c r="P51">
-        <v>1558.049473415306</v>
+        <v>1586.33507219113</v>
       </c>
       <c r="Q51">
-        <v>3275.049473415306</v>
+        <v>3303.33507219113</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1763948867281246</v>
+        <v>0.1763109258272192</v>
       </c>
       <c r="T51">
         <v>3.014109141506217</v>
       </c>
       <c r="U51">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +6025,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.473492805044393</v>
+        <v>3.636803497505793</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +6036,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1141219586373732</v>
+        <v>0.1129690059123004</v>
       </c>
       <c r="C52">
-        <v>13785.90604573646</v>
+        <v>14177.41481645613</v>
       </c>
       <c r="D52">
-        <v>23707.85033221542</v>
+        <v>24099.35910293509</v>
       </c>
       <c r="E52">
         <v>9575.55571352104</v>
@@ -5557,37 +6069,37 @@
         <v>2562</v>
       </c>
       <c r="M52">
-        <v>752.6388741871317</v>
+        <v>718.8416190422864</v>
       </c>
       <c r="N52">
-        <v>1809.361125812868</v>
+        <v>1843.158380957714</v>
       </c>
       <c r="O52">
-        <v>264.1667243686787</v>
+        <v>269.1011236198262</v>
       </c>
       <c r="P52">
-        <v>1545.19440144419</v>
+        <v>1574.057257337887</v>
       </c>
       <c r="Q52">
-        <v>3262.19440144419</v>
+        <v>3291.057257337888</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1787973172747463</v>
+        <v>0.1787118118246007</v>
       </c>
       <c r="T52">
         <v>3.069556855071612</v>
       </c>
       <c r="U52">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +6107,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.404022948943505</v>
+        <v>3.564067427555678</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +6118,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1140536910434028</v>
+        <v>0.112878601652719</v>
       </c>
       <c r="C53">
-        <v>13549.63983950669</v>
+        <v>13949.91550934637</v>
       </c>
       <c r="D53">
-        <v>23731.56301171523</v>
+        <v>24131.83868155491</v>
       </c>
       <c r="E53">
         <v>9835.534599250619</v>
@@ -5639,37 +6151,37 @@
         <v>2562</v>
       </c>
       <c r="M53">
-        <v>767.6916516708743</v>
+        <v>733.2184514231321</v>
       </c>
       <c r="N53">
-        <v>1794.308348329126</v>
+        <v>1828.781548576868</v>
       </c>
       <c r="O53">
-        <v>261.9690188560523</v>
+        <v>267.0021060922227</v>
       </c>
       <c r="P53">
-        <v>1532.339329473073</v>
+        <v>1561.779442484645</v>
       </c>
       <c r="Q53">
-        <v>3249.339329473073</v>
+        <v>3278.779442484645</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.181297806211026</v>
+        <v>0.1812106931688142</v>
       </c>
       <c r="T53">
         <v>3.127267740619267</v>
       </c>
       <c r="U53">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.146</v>
       </c>
       <c r="W53">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +6189,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.337277400925005</v>
+        <v>3.494183752505566</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +6200,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1139854234494324</v>
+        <v>0.1127881973931376</v>
       </c>
       <c r="C54">
-        <v>13313.42111578839</v>
+        <v>13722.50386819482</v>
       </c>
       <c r="D54">
-        <v>23755.32317372651</v>
+        <v>24164.40592613294</v>
       </c>
       <c r="E54">
         <v>10095.5134849802</v>
@@ -5721,37 +6233,37 @@
         <v>2562</v>
       </c>
       <c r="M54">
-        <v>782.744429154617</v>
+        <v>747.595283803978</v>
       </c>
       <c r="N54">
-        <v>1779.255570845383</v>
+        <v>1814.404716196022</v>
       </c>
       <c r="O54">
-        <v>259.7713133434259</v>
+        <v>264.9030885646192</v>
       </c>
       <c r="P54">
-        <v>1519.484257501957</v>
+        <v>1549.501627631403</v>
       </c>
       <c r="Q54">
-        <v>3236.484257501957</v>
+        <v>3266.501627631403</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1839024821863174</v>
+        <v>0.1838136945690366</v>
       </c>
       <c r="T54">
         <v>3.187383246398075</v>
       </c>
       <c r="U54">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.146</v>
       </c>
       <c r="W54">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +6271,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.273098989368755</v>
+        <v>3.426987911111228</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +6282,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.113917155855462</v>
+        <v>0.1126977931335562</v>
       </c>
       <c r="C55">
-        <v>13077.25001734372</v>
+        <v>13495.18024841124</v>
       </c>
       <c r="D55">
-        <v>23779.13096101142</v>
+        <v>24197.06119207894</v>
       </c>
       <c r="E55">
         <v>10355.49237070978</v>
@@ -5803,37 +6315,37 @@
         <v>2562</v>
       </c>
       <c r="M55">
-        <v>797.7972066383596</v>
+        <v>761.9721161848237</v>
       </c>
       <c r="N55">
-        <v>1764.20279336164</v>
+        <v>1800.027883815176</v>
       </c>
       <c r="O55">
-        <v>257.5736078307995</v>
+        <v>262.8040710370157</v>
       </c>
       <c r="P55">
-        <v>1506.629185530841</v>
+        <v>1537.22381277816</v>
       </c>
       <c r="Q55">
-        <v>3223.629185530841</v>
+        <v>3254.22381277816</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1866179954371531</v>
+        <v>0.1865274619862897</v>
       </c>
       <c r="T55">
         <v>3.250056858805769</v>
       </c>
       <c r="U55">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +6353,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.211342404663684</v>
+        <v>3.362327761844978</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +6364,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1138488882614915</v>
+        <v>0.1126073888739748</v>
       </c>
       <c r="C56">
-        <v>12841.12668750769</v>
+        <v>13267.94500732915</v>
       </c>
       <c r="D56">
-        <v>23802.98651690497</v>
+        <v>24229.80483672642</v>
       </c>
       <c r="E56">
         <v>10615.47125643936</v>
@@ -5885,37 +6397,37 @@
         <v>2562</v>
       </c>
       <c r="M56">
-        <v>812.8499841221022</v>
+        <v>776.3489485656694</v>
       </c>
       <c r="N56">
-        <v>1749.150015877898</v>
+        <v>1785.651051434331</v>
       </c>
       <c r="O56">
-        <v>255.375902318173</v>
+        <v>260.7050535094123</v>
       </c>
       <c r="P56">
-        <v>1493.774113559725</v>
+        <v>1524.945997924918</v>
       </c>
       <c r="Q56">
-        <v>3210.774113559724</v>
+        <v>3241.945997924919</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1894515744815034</v>
+        <v>0.1893592192912495</v>
       </c>
       <c r="T56">
         <v>3.315455410883361</v>
       </c>
       <c r="U56">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6435,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.151873100873616</v>
+        <v>3.300062432921923</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6446,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1137806206675211</v>
+        <v>0.1125169846143934</v>
       </c>
       <c r="C57">
-        <v>12605.05127019106</v>
+        <v>13040.79850421887</v>
       </c>
       <c r="D57">
-        <v>23826.88998531791</v>
+        <v>24262.63721934572</v>
       </c>
       <c r="E57">
         <v>10875.45014216894</v>
@@ -5967,37 +6479,37 @@
         <v>2562</v>
       </c>
       <c r="M57">
-        <v>827.9027616058448</v>
+        <v>790.7257809465151</v>
       </c>
       <c r="N57">
-        <v>1734.097238394155</v>
+        <v>1771.274219053485</v>
       </c>
       <c r="O57">
-        <v>253.1781968055467</v>
+        <v>258.6060359818088</v>
       </c>
       <c r="P57">
-        <v>1480.919041588609</v>
+        <v>1512.668183071676</v>
       </c>
       <c r="Q57">
-        <v>3197.919041588609</v>
+        <v>3229.668183071676</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1924110903722693</v>
+        <v>0.1923168324764297</v>
       </c>
       <c r="T57">
         <v>3.383760565275514</v>
       </c>
       <c r="U57">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V57">
         <v>0.146</v>
       </c>
       <c r="W57">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6517,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.094566317221369</v>
+        <v>3.240061297777888</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6528,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1137123530735507</v>
+        <v>0.112426580354812</v>
       </c>
       <c r="C58">
-        <v>12369.02390988328</v>
+        <v>12813.74110030069</v>
       </c>
       <c r="D58">
-        <v>23850.84151073972</v>
+        <v>24295.55870115713</v>
       </c>
       <c r="E58">
         <v>11135.42902789852</v>
@@ -6049,37 +6561,37 @@
         <v>2562</v>
       </c>
       <c r="M58">
-        <v>842.9555390895875</v>
+        <v>805.1026133273609</v>
       </c>
       <c r="N58">
-        <v>1719.044460910412</v>
+        <v>1756.897386672639</v>
       </c>
       <c r="O58">
-        <v>250.9804912929202</v>
+        <v>256.5070184542053</v>
       </c>
       <c r="P58">
-        <v>1468.063969617492</v>
+        <v>1500.390368218434</v>
       </c>
       <c r="Q58">
-        <v>3185.063969617492</v>
+        <v>3217.390368218434</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1955051297126153</v>
+        <v>0.1954088826245727</v>
       </c>
       <c r="T58">
         <v>3.455170499412765</v>
       </c>
       <c r="U58">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.146</v>
       </c>
       <c r="W58">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6599,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.039306204413844</v>
+        <v>3.182203060317569</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6610,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1149097134795803</v>
+        <v>0.1123361760952306</v>
       </c>
       <c r="C59">
-        <v>11695.81724707885</v>
+        <v>12586.7731587581</v>
       </c>
       <c r="D59">
-        <v>23437.61373366487</v>
+        <v>24328.56964534411</v>
       </c>
       <c r="E59">
         <v>11395.4079136281</v>
@@ -6131,45 +6643,45 @@
         <v>2562</v>
       </c>
       <c r="M59">
-        <v>896.5371874384538</v>
+        <v>819.4794457082066</v>
       </c>
       <c r="N59">
-        <v>1665.462812561546</v>
+        <v>1742.520554291793</v>
       </c>
       <c r="O59">
-        <v>243.1575706339858</v>
+        <v>254.4080009266018</v>
       </c>
       <c r="P59">
-        <v>1422.30524192756</v>
+        <v>1488.112553365192</v>
       </c>
       <c r="Q59">
-        <v>3139.30524192756</v>
+        <v>3205.112553365192</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1987430778594891</v>
+        <v>0.1986447490586757</v>
       </c>
       <c r="T59">
         <v>3.529901825835468</v>
       </c>
       <c r="U59">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.146</v>
       </c>
       <c r="W59">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.8576617187738</v>
+        <v>3.126374936452348</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6692,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1148636498856099</v>
+        <v>0.1122457718356492</v>
       </c>
       <c r="C60">
-        <v>11451.47061832455</v>
+        <v>12359.89504475109</v>
       </c>
       <c r="D60">
-        <v>23453.24599064015</v>
+        <v>24361.67041706668</v>
       </c>
       <c r="E60">
         <v>11655.38679935767</v>
@@ -6213,45 +6725,45 @@
         <v>2562</v>
       </c>
       <c r="M60">
-        <v>912.2659100250933</v>
+        <v>833.8562780890522</v>
       </c>
       <c r="N60">
-        <v>1649.734089974907</v>
+        <v>1728.143721910948</v>
       </c>
       <c r="O60">
-        <v>240.8611771363364</v>
+        <v>252.3089833989984</v>
       </c>
       <c r="P60">
-        <v>1408.87291283857</v>
+        <v>1475.834738511949</v>
       </c>
       <c r="Q60">
-        <v>3125.87291283857</v>
+        <v>3192.83473851195</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.202135214013357</v>
+        <v>0.2020347043705932</v>
       </c>
       <c r="T60">
         <v>3.608191786849729</v>
       </c>
       <c r="U60">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.808391689139769</v>
+        <v>3.072471920306619</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6774,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1148175862916395</v>
+        <v>0.1121553675760678</v>
       </c>
       <c r="C61">
-        <v>11207.14485607623</v>
+        <v>12133.10712542972</v>
       </c>
       <c r="D61">
-        <v>23468.8991141214</v>
+        <v>24394.86138347489</v>
       </c>
       <c r="E61">
         <v>11915.36568508725</v>
@@ -6295,45 +6807,45 @@
         <v>2562</v>
       </c>
       <c r="M61">
-        <v>927.9946326117328</v>
+        <v>848.233110469898</v>
       </c>
       <c r="N61">
-        <v>1634.005367388267</v>
+        <v>1713.766889530102</v>
       </c>
       <c r="O61">
-        <v>238.564783638687</v>
+        <v>250.2099658713949</v>
       </c>
       <c r="P61">
-        <v>1395.44058374958</v>
+        <v>1463.556923658707</v>
       </c>
       <c r="Q61">
-        <v>3112.44058374958</v>
+        <v>3180.556923658707</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.205692820223511</v>
+        <v>0.2055900233562628</v>
       </c>
       <c r="T61">
         <v>3.690300770352491</v>
       </c>
       <c r="U61">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V61">
         <v>0.146</v>
       </c>
       <c r="W61">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.760791830001807</v>
+        <v>3.020396125047184</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6856,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1147715226976691</v>
+        <v>0.1133459633164864</v>
       </c>
       <c r="C62">
-        <v>10962.84000214182</v>
+        <v>11443.13336472619</v>
       </c>
       <c r="D62">
-        <v>23484.57314591657</v>
+        <v>23964.86650850094</v>
       </c>
       <c r="E62">
         <v>12175.34457081683</v>
@@ -6377,37 +6889,37 @@
         <v>2562</v>
       </c>
       <c r="M62">
-        <v>943.7233551983722</v>
+        <v>901.6067757101805</v>
       </c>
       <c r="N62">
-        <v>1618.276644801628</v>
+        <v>1660.393224289819</v>
       </c>
       <c r="O62">
-        <v>236.2683901410376</v>
+        <v>242.4174107463136</v>
       </c>
       <c r="P62">
-        <v>1382.00825466059</v>
+        <v>1417.975813543506</v>
       </c>
       <c r="Q62">
-        <v>3099.00825466059</v>
+        <v>3134.975813543506</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2094283067441728</v>
+        <v>0.2093231082912159</v>
       </c>
       <c r="T62">
         <v>3.776515203030391</v>
       </c>
       <c r="U62">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V62">
         <v>0.146</v>
       </c>
       <c r="W62">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6927,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.71477863283511</v>
+        <v>2.841593551669968</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6938,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1147254591036987</v>
+        <v>0.113276909056905</v>
       </c>
       <c r="C63">
-        <v>10718.55609844108</v>
+        <v>11207.67955188214</v>
       </c>
       <c r="D63">
-        <v>23500.26812794541</v>
+        <v>23989.39158138647</v>
       </c>
       <c r="E63">
         <v>12435.32345654641</v>
@@ -6459,37 +6971,37 @@
         <v>2562</v>
       </c>
       <c r="M63">
-        <v>959.4520777850119</v>
+        <v>916.6335553053502</v>
       </c>
       <c r="N63">
-        <v>1602.547922214988</v>
+        <v>1645.36644469465</v>
       </c>
       <c r="O63">
-        <v>233.9719966433883</v>
+        <v>240.2235009254188</v>
       </c>
       <c r="P63">
-        <v>1368.5759255716</v>
+        <v>1405.142943769231</v>
       </c>
       <c r="Q63">
-        <v>3085.5759255716</v>
+        <v>3122.142943769231</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2133553566761506</v>
+        <v>0.2132476334792435</v>
       </c>
       <c r="T63">
         <v>3.867150888666133</v>
       </c>
       <c r="U63">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.146</v>
       </c>
       <c r="W63">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +7009,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.670274065083714</v>
+        <v>2.795010050822919</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +7020,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1146793955097283</v>
+        <v>0.1132078547973236</v>
       </c>
       <c r="C64">
-        <v>10474.29318700585</v>
+        <v>10972.27598721035</v>
       </c>
       <c r="D64">
-        <v>23515.98410223976</v>
+        <v>24013.96690244426</v>
       </c>
       <c r="E64">
         <v>12695.30234227599</v>
@@ -6541,37 +7053,37 @@
         <v>2562</v>
       </c>
       <c r="M64">
-        <v>975.1808003716515</v>
+        <v>931.66033490052</v>
       </c>
       <c r="N64">
-        <v>1586.819199628349</v>
+        <v>1630.33966509948</v>
       </c>
       <c r="O64">
-        <v>231.6756031457389</v>
+        <v>238.0295911045241</v>
       </c>
       <c r="P64">
-        <v>1355.14359648261</v>
+        <v>1392.310073994956</v>
       </c>
       <c r="Q64">
-        <v>3072.14359648261</v>
+        <v>3109.310073994956</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2174890934466535</v>
+        <v>0.2173787126245357</v>
       </c>
       <c r="T64">
         <v>3.96255687354586</v>
       </c>
       <c r="U64">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.146</v>
       </c>
       <c r="W64">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +7091,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.627205128550106</v>
+        <v>2.749929243551581</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +7102,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1146333319157579</v>
+        <v>0.1131388005377421</v>
       </c>
       <c r="C65">
-        <v>10230.05130998052</v>
+        <v>10736.92282529555</v>
       </c>
       <c r="D65">
-        <v>23531.72111094401</v>
+        <v>24038.59262625904</v>
       </c>
       <c r="E65">
         <v>12955.28122800557</v>
@@ -6623,37 +7135,37 @@
         <v>2562</v>
       </c>
       <c r="M65">
-        <v>990.9095229582909</v>
+        <v>946.6871144956897</v>
       </c>
       <c r="N65">
-        <v>1571.090477041709</v>
+        <v>1615.31288550431</v>
       </c>
       <c r="O65">
-        <v>229.3792096480895</v>
+        <v>235.8356812836293</v>
       </c>
       <c r="P65">
-        <v>1341.71126739362</v>
+        <v>1379.477204220681</v>
       </c>
       <c r="Q65">
-        <v>3058.71126739362</v>
+        <v>3096.477204220681</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2218462754479943</v>
+        <v>0.221733093345249</v>
       </c>
       <c r="T65">
         <v>4.063119938689356</v>
       </c>
       <c r="U65">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.146</v>
       </c>
       <c r="W65">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +7173,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.585503459842962</v>
+        <v>2.706279573019017</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +7184,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1145872683217875</v>
+        <v>0.1130697462781608</v>
       </c>
       <c r="C66">
-        <v>9985.830509622323</v>
+        <v>10501.62022135721</v>
       </c>
       <c r="D66">
-        <v>23547.47919631539</v>
+        <v>24063.26890805028</v>
       </c>
       <c r="E66">
         <v>13215.26011373515</v>
@@ -6705,37 +7217,37 @@
         <v>2562</v>
       </c>
       <c r="M66">
-        <v>1006.638245544931</v>
+        <v>961.7138940908594</v>
       </c>
       <c r="N66">
-        <v>1555.361754455069</v>
+        <v>1600.286105909141</v>
       </c>
       <c r="O66">
-        <v>227.0828161504401</v>
+        <v>233.6417714627345</v>
       </c>
       <c r="P66">
-        <v>1328.278938304629</v>
+        <v>1366.644334446406</v>
       </c>
       <c r="Q66">
-        <v>3045.278938304629</v>
+        <v>3083.644334446406</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2264455231160764</v>
+        <v>0.2263293841060021</v>
       </c>
       <c r="T66">
         <v>4.16926984078527</v>
       </c>
       <c r="U66">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.146</v>
       </c>
       <c r="W66">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +7255,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.545104968282915</v>
+        <v>2.663993954690595</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +7266,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1145412047278171</v>
+        <v>0.1130006920185794</v>
       </c>
       <c r="C67">
-        <v>9741.630828301808</v>
+        <v>10266.36833125282</v>
       </c>
       <c r="D67">
-        <v>23563.25840072445</v>
+        <v>24087.99590367547</v>
       </c>
       <c r="E67">
         <v>13475.23899946473</v>
@@ -6787,37 +7299,37 @@
         <v>2562</v>
       </c>
       <c r="M67">
-        <v>1022.36696813157</v>
+        <v>976.740673686029</v>
       </c>
       <c r="N67">
-        <v>1539.63303186843</v>
+        <v>1585.259326313971</v>
       </c>
       <c r="O67">
-        <v>224.7864226527907</v>
+        <v>231.4478616418398</v>
       </c>
       <c r="P67">
-        <v>1314.846609215639</v>
+        <v>1353.811464672131</v>
       </c>
       <c r="Q67">
-        <v>3031.846609215639</v>
+        <v>3070.811464672131</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2313075849366203</v>
+        <v>0.2311883200530839</v>
       </c>
       <c r="T67">
         <v>4.281485451572378</v>
       </c>
       <c r="U67">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.146</v>
       </c>
       <c r="W67">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +7337,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.505949507232409</v>
+        <v>2.623009432310739</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +7348,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1160169691338467</v>
+        <v>0.1129316377589979</v>
       </c>
       <c r="C68">
-        <v>8986.41811993911</v>
+        <v>10031.16731148117</v>
       </c>
       <c r="D68">
-        <v>23068.02457809134</v>
+        <v>24112.7737696334</v>
       </c>
       <c r="E68">
         <v>13735.21788519431</v>
@@ -6869,45 +7381,45 @@
         <v>2562</v>
       </c>
       <c r="M68">
-        <v>1084.423928155221</v>
+        <v>991.7674532811988</v>
       </c>
       <c r="N68">
-        <v>1477.576071844779</v>
+        <v>1570.232546718801</v>
       </c>
       <c r="O68">
-        <v>215.7261064893377</v>
+        <v>229.253951820945</v>
       </c>
       <c r="P68">
-        <v>1261.849965355441</v>
+        <v>1340.978594897856</v>
       </c>
       <c r="Q68">
-        <v>2978.849965355441</v>
+        <v>3057.978594897856</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2364556503936667</v>
+        <v>0.2363330757617587</v>
       </c>
       <c r="T68">
         <v>4.400301980641079</v>
       </c>
       <c r="U68">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.146</v>
       </c>
       <c r="W68">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.362544696296377</v>
+        <v>2.583266865154516</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7430,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1159939635398763</v>
+        <v>0.1128625834994166</v>
       </c>
       <c r="C69">
-        <v>8733.999622316707</v>
+        <v>9796.01731918559</v>
       </c>
       <c r="D69">
-        <v>23075.58496619851</v>
+        <v>24137.6026630674</v>
       </c>
       <c r="E69">
         <v>13995.19677092389</v>
@@ -6951,45 +7463,45 @@
         <v>2562</v>
       </c>
       <c r="M69">
-        <v>1100.85459373333</v>
+        <v>1006.794232876368</v>
       </c>
       <c r="N69">
-        <v>1461.14540626667</v>
+        <v>1555.205767123632</v>
       </c>
       <c r="O69">
-        <v>213.3272293149338</v>
+        <v>227.0600420000502</v>
       </c>
       <c r="P69">
-        <v>1247.818176951736</v>
+        <v>1328.145725123582</v>
       </c>
       <c r="Q69">
-        <v>2964.818176951736</v>
+        <v>3045.145725123582</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.241915719817807</v>
+        <v>0.2417896348467168</v>
       </c>
       <c r="T69">
         <v>4.526319511471522</v>
       </c>
       <c r="U69">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V69">
         <v>0.146</v>
       </c>
       <c r="W69">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.327282835157625</v>
+        <v>2.544710643286538</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7512,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1159709579459059</v>
+        <v>0.1127935292398351</v>
       </c>
       <c r="C70">
-        <v>8481.586082050584</v>
+        <v>9560.918512157365</v>
       </c>
       <c r="D70">
-        <v>23083.15031166197</v>
+        <v>24162.48274176875</v>
       </c>
       <c r="E70">
         <v>14255.17565665347</v>
@@ -7033,45 +7545,45 @@
         <v>2562</v>
       </c>
       <c r="M70">
-        <v>1117.28525931144</v>
+        <v>1021.821012471538</v>
       </c>
       <c r="N70">
-        <v>1444.71474068856</v>
+        <v>1540.178987528462</v>
       </c>
       <c r="O70">
-        <v>210.9283521405298</v>
+        <v>224.8661321791554</v>
       </c>
       <c r="P70">
-        <v>1233.786388548031</v>
+        <v>1315.312855349307</v>
       </c>
       <c r="Q70">
-        <v>2950.786388548031</v>
+        <v>3032.312855349307</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2477170435809559</v>
+        <v>0.2475872288744848</v>
       </c>
       <c r="T70">
         <v>4.660213137978866</v>
       </c>
       <c r="U70">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.146</v>
       </c>
       <c r="W70">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.293058087581778</v>
+        <v>2.507288427944089</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7594,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1159479523519355</v>
+        <v>0.1147868849802537</v>
       </c>
       <c r="C71">
-        <v>8229.177504018131</v>
+        <v>8602.771798008569</v>
       </c>
       <c r="D71">
-        <v>23090.72061935909</v>
+        <v>23464.31491334953</v>
       </c>
       <c r="E71">
         <v>14515.15454238304</v>
@@ -7115,37 +7627,37 @@
         <v>2562</v>
       </c>
       <c r="M71">
-        <v>1133.715924889549</v>
+        <v>1099.632692970401</v>
       </c>
       <c r="N71">
-        <v>1428.284075110451</v>
+        <v>1462.367307029599</v>
       </c>
       <c r="O71">
-        <v>208.5294749661259</v>
+        <v>213.5056268263214</v>
       </c>
       <c r="P71">
-        <v>1219.754600144325</v>
+        <v>1248.861680203278</v>
       </c>
       <c r="Q71">
-        <v>2936.754600144325</v>
+        <v>2965.861680203278</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2538926462965661</v>
+        <v>0.2537588612266251</v>
       </c>
       <c r="T71">
         <v>4.802745062970557</v>
       </c>
       <c r="U71">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7665,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.259825361674795</v>
+        <v>2.329868888382497</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7676,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1187346067579651</v>
+        <v>0.1147477207206723</v>
       </c>
       <c r="C72">
-        <v>7086.958194810733</v>
+        <v>8356.121308207974</v>
       </c>
       <c r="D72">
-        <v>22208.48019588127</v>
+        <v>23477.64330927852</v>
       </c>
       <c r="E72">
         <v>14775.13342811262</v>
@@ -7197,45 +7709,45 @@
         <v>2562</v>
       </c>
       <c r="M72">
-        <v>1235.67964387269</v>
+        <v>1115.569398665624</v>
       </c>
       <c r="N72">
-        <v>1326.32035612731</v>
+        <v>1446.430601334376</v>
       </c>
       <c r="O72">
-        <v>193.6427719945873</v>
+        <v>211.1788677948188</v>
       </c>
       <c r="P72">
-        <v>1132.677584132723</v>
+        <v>1235.251733539557</v>
       </c>
       <c r="Q72">
-        <v>2849.677584132723</v>
+        <v>2952.251733539557</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2604799558598836</v>
+        <v>0.2603419357355745</v>
       </c>
       <c r="T72">
         <v>4.954779116295025</v>
       </c>
       <c r="U72">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.146</v>
       </c>
       <c r="W72">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.073352921773921</v>
+        <v>2.29658504711989</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7758,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1187517391639947</v>
+        <v>0.114708556461091</v>
       </c>
       <c r="C73">
-        <v>6821.763741853058</v>
+        <v>8109.485968826561</v>
       </c>
       <c r="D73">
-        <v>22203.26462865318</v>
+        <v>23490.98685562668</v>
       </c>
       <c r="E73">
         <v>15035.1123138422</v>
@@ -7279,45 +7791,45 @@
         <v>2562</v>
       </c>
       <c r="M73">
-        <v>1253.332210213728</v>
+        <v>1131.506104360847</v>
       </c>
       <c r="N73">
-        <v>1308.667789786272</v>
+        <v>1430.493895639153</v>
       </c>
       <c r="O73">
-        <v>191.0654973087956</v>
+        <v>208.8521087633163</v>
       </c>
       <c r="P73">
-        <v>1117.602292477476</v>
+        <v>1221.641786875836</v>
       </c>
       <c r="Q73">
-        <v>2834.602292477476</v>
+        <v>2938.641786875836</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2675215626344644</v>
+        <v>0.2673790153830722</v>
       </c>
       <c r="T73">
         <v>5.117298276745319</v>
       </c>
       <c r="U73">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.146</v>
       </c>
       <c r="W73">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.044150767946119</v>
+        <v>2.264238778850596</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7840,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1187688715700243</v>
+        <v>0.1163910562015096</v>
       </c>
       <c r="C74">
-        <v>6556.571738027829</v>
+        <v>7289.61208487023</v>
       </c>
       <c r="D74">
-        <v>22198.05151055753</v>
+        <v>22931.09185739993</v>
       </c>
       <c r="E74">
         <v>15295.09119957178</v>
@@ -7361,37 +7873,37 @@
         <v>2562</v>
       </c>
       <c r="M74">
-        <v>1270.984776554767</v>
+        <v>1199.854553419154</v>
       </c>
       <c r="N74">
-        <v>1291.015223445233</v>
+        <v>1362.145446580846</v>
       </c>
       <c r="O74">
-        <v>188.4882226230041</v>
+        <v>198.8732352008035</v>
       </c>
       <c r="P74">
-        <v>1102.527000822229</v>
+        <v>1163.272211380043</v>
       </c>
       <c r="Q74">
-        <v>2819.52700082223</v>
+        <v>2880.272211380043</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2750661413215152</v>
+        <v>0.2749187435768198</v>
       </c>
       <c r="T74">
         <v>5.291425948656348</v>
       </c>
       <c r="U74">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.146</v>
       </c>
       <c r="W74">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7911,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.01575978505798</v>
+        <v>2.135258805077017</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7922,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1275138839760538</v>
+        <v>0.1163758039419281</v>
       </c>
       <c r="C75">
-        <v>3920.959405399604</v>
+        <v>7034.588877233698</v>
       </c>
       <c r="D75">
-        <v>19822.41806365888</v>
+        <v>22936.04753549298</v>
       </c>
       <c r="E75">
         <v>15555.07008530136</v>
@@ -7443,45 +7955,45 @@
         <v>2562</v>
       </c>
       <c r="M75">
-        <v>1554.335764111435</v>
+        <v>1216.51919999442</v>
       </c>
       <c r="N75">
-        <v>1007.664235888565</v>
+        <v>1345.48080000558</v>
       </c>
       <c r="O75">
-        <v>147.1189784397305</v>
+        <v>196.4401968008147</v>
       </c>
       <c r="P75">
-        <v>860.5452574488346</v>
+        <v>1149.040603204766</v>
       </c>
       <c r="Q75">
-        <v>2577.545257448834</v>
+        <v>2866.040603204766</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2831695776890883</v>
+        <v>0.2830169701552894</v>
       </c>
       <c r="T75">
         <v>5.478451966634861</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.146</v>
       </c>
       <c r="W75">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.648292511280287</v>
+        <v>2.106008684459524</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +8004,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1276505763820834</v>
+        <v>0.1163605516823467</v>
       </c>
       <c r="C76">
-        <v>3627.876610837451</v>
+        <v>6779.567812020574</v>
       </c>
       <c r="D76">
-        <v>19789.31415482631</v>
+        <v>22941.00535600943</v>
       </c>
       <c r="E76">
         <v>15815.04897103094</v>
@@ -7525,45 +8037,45 @@
         <v>2562</v>
       </c>
       <c r="M76">
-        <v>1575.628034852688</v>
+        <v>1233.183846569686</v>
       </c>
       <c r="N76">
-        <v>986.3719651473125</v>
+        <v>1328.816153430314</v>
       </c>
       <c r="O76">
-        <v>144.0103069115076</v>
+        <v>194.0071584008259</v>
       </c>
       <c r="P76">
-        <v>842.3616582358048</v>
+        <v>1134.808995029488</v>
       </c>
       <c r="Q76">
-        <v>2559.361658235805</v>
+        <v>2851.808995029488</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2918963553157056</v>
+        <v>0.2917381372397951</v>
       </c>
       <c r="T76">
         <v>5.679864601380952</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.146</v>
       </c>
       <c r="W76">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.626018288154877</v>
+        <v>2.077549107642503</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +8086,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1277872687881131</v>
+        <v>0.1163452994227653</v>
       </c>
       <c r="C77">
-        <v>3334.904200558467</v>
+        <v>6524.548890620459</v>
       </c>
       <c r="D77">
-        <v>19756.3206302769</v>
+        <v>22945.9653203389</v>
       </c>
       <c r="E77">
         <v>16075.02785676052</v>
@@ -7607,45 +8119,45 @@
         <v>2562</v>
       </c>
       <c r="M77">
-        <v>1596.92030559394</v>
+        <v>1249.848493144952</v>
       </c>
       <c r="N77">
-        <v>965.0796944060601</v>
+        <v>1312.151506855048</v>
       </c>
       <c r="O77">
-        <v>140.9016353832848</v>
+        <v>191.574120000837</v>
       </c>
       <c r="P77">
-        <v>824.1780590227753</v>
+        <v>1120.577386854211</v>
       </c>
       <c r="Q77">
-        <v>2541.178059022775</v>
+        <v>2837.577386854211</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3013212751524522</v>
+        <v>0.3011569976910614</v>
       </c>
       <c r="T77">
         <v>5.897390246906731</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.146</v>
       </c>
       <c r="W77">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.604338044312812</v>
+        <v>2.049848452873936</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +8168,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1279239611941426</v>
+        <v>0.1163300471631839</v>
       </c>
       <c r="C78">
-        <v>3042.041623370555</v>
+        <v>6269.532114424164</v>
       </c>
       <c r="D78">
-        <v>19723.43693881857</v>
+        <v>22950.92742987218</v>
       </c>
       <c r="E78">
         <v>16335.0067424901</v>
@@ -7689,45 +8201,45 @@
         <v>2562</v>
       </c>
       <c r="M78">
-        <v>1618.212576335192</v>
+        <v>1266.513139720218</v>
       </c>
       <c r="N78">
-        <v>943.7874236648076</v>
+        <v>1295.486860279782</v>
       </c>
       <c r="O78">
-        <v>137.7929638550619</v>
+        <v>189.1410816008482</v>
       </c>
       <c r="P78">
-        <v>805.9944598097458</v>
+        <v>1106.345778678934</v>
       </c>
       <c r="Q78">
-        <v>2522.994459809746</v>
+        <v>2823.345778678934</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3115316049755944</v>
+        <v>0.3113607631799331</v>
       </c>
       <c r="T78">
         <v>6.133043029559659</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.146</v>
       </c>
       <c r="W78">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.583228333203433</v>
+        <v>2.022876762704542</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +8250,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1280606536001722</v>
+        <v>0.1214439189036025</v>
       </c>
       <c r="C79">
-        <v>2749.28833174524</v>
+        <v>4457.966519529095</v>
       </c>
       <c r="D79">
-        <v>19690.66253292284</v>
+        <v>21399.34072070669</v>
       </c>
       <c r="E79">
         <v>16594.98562821968</v>
@@ -7771,45 +8283,45 @@
         <v>2562</v>
       </c>
       <c r="M79">
-        <v>1639.504847076445</v>
+        <v>1439.321105064669</v>
       </c>
       <c r="N79">
-        <v>922.4951529235548</v>
+        <v>1122.678894935331</v>
       </c>
       <c r="O79">
-        <v>134.684292326839</v>
+        <v>163.9111186605583</v>
       </c>
       <c r="P79">
-        <v>787.8108605967158</v>
+        <v>958.7677762747724</v>
       </c>
       <c r="Q79">
-        <v>2504.810860596716</v>
+        <v>2675.767776274773</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3226297895659663</v>
+        <v>0.3224518126243589</v>
       </c>
       <c r="T79">
         <v>6.389187358530231</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.146</v>
       </c>
       <c r="W79">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.562666926278713</v>
+        <v>1.78000585900176</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +8332,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1281973460062018</v>
+        <v>0.1214952786440211</v>
       </c>
       <c r="C80">
-        <v>2456.643781787367</v>
+        <v>4183.468041504824</v>
       </c>
       <c r="D80">
-        <v>19657.99686869454</v>
+        <v>21384.821128412</v>
       </c>
       <c r="E80">
         <v>16854.96451394926</v>
@@ -7853,45 +8365,45 @@
         <v>2562</v>
       </c>
       <c r="M80">
-        <v>1660.797117817698</v>
+        <v>1458.013586948626</v>
       </c>
       <c r="N80">
-        <v>901.2028821823023</v>
+        <v>1103.986413051374</v>
       </c>
       <c r="O80">
-        <v>131.5756207986161</v>
+        <v>161.1820163055006</v>
       </c>
       <c r="P80">
-        <v>769.6272613836862</v>
+        <v>942.8043967458732</v>
       </c>
       <c r="Q80">
-        <v>2486.627261383686</v>
+        <v>2659.804396745873</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3347369000281902</v>
+        <v>0.3345511392910052</v>
       </c>
       <c r="T80">
         <v>6.668617535589036</v>
       </c>
       <c r="U80">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V80">
         <v>0.146</v>
       </c>
       <c r="W80">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.542632734916165</v>
+        <v>1.75718527106584</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8414,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1283340384122315</v>
+        <v>0.1241778123844397</v>
       </c>
       <c r="C81">
-        <v>2164.107433204899</v>
+        <v>3191.579161548732</v>
       </c>
       <c r="D81">
-        <v>19625.43940584165</v>
+        <v>20652.91113418549</v>
       </c>
       <c r="E81">
         <v>17114.94339967884</v>
@@ -7935,37 +8447,37 @@
         <v>2562</v>
       </c>
       <c r="M81">
-        <v>1682.08938855895</v>
+        <v>1556.805563525866</v>
       </c>
       <c r="N81">
-        <v>879.9106114410497</v>
+        <v>1005.194436474134</v>
       </c>
       <c r="O81">
-        <v>128.4669492703933</v>
+        <v>146.7583877252235</v>
       </c>
       <c r="P81">
-        <v>751.4436621706565</v>
+        <v>858.4360487489104</v>
       </c>
       <c r="Q81">
-        <v>2468.443662170656</v>
+        <v>2575.43604874891</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3479970686296736</v>
+        <v>0.3478027827830464</v>
       </c>
       <c r="T81">
         <v>6.974660110462969</v>
       </c>
       <c r="U81">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.146</v>
       </c>
       <c r="W81">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8485,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.523105738271657</v>
+        <v>1.645677572090352</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8496,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.128470730818261</v>
+        <v>0.1242624781248583</v>
       </c>
       <c r="C82">
-        <v>1871.678749279276</v>
+        <v>2909.314540589217</v>
       </c>
       <c r="D82">
-        <v>19592.98960764561</v>
+        <v>20630.62539895555</v>
       </c>
       <c r="E82">
         <v>17374.92228540842</v>
@@ -8017,37 +8529,37 @@
         <v>2562</v>
       </c>
       <c r="M82">
-        <v>1703.381659300203</v>
+        <v>1576.511963064168</v>
       </c>
       <c r="N82">
-        <v>858.6183406997973</v>
+        <v>985.4880369358318</v>
       </c>
       <c r="O82">
-        <v>125.3582777421704</v>
+        <v>143.8812533926314</v>
       </c>
       <c r="P82">
-        <v>733.2600629576268</v>
+        <v>841.6067835432004</v>
       </c>
       <c r="Q82">
-        <v>2450.260062957627</v>
+        <v>2558.6067835432</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3625832540913052</v>
+        <v>0.3623795906242917</v>
       </c>
       <c r="T82">
         <v>7.311306942824292</v>
       </c>
       <c r="U82">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.146</v>
       </c>
       <c r="W82">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8567,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.504066916543261</v>
+        <v>1.625106602439223</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8578,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1641938139824013</v>
+        <v>0.124347143865277</v>
       </c>
       <c r="C83">
-        <v>-4300.112364174474</v>
+        <v>2627.097963089487</v>
       </c>
       <c r="D83">
-        <v>13681.17737992144</v>
+        <v>20608.3877071854</v>
       </c>
       <c r="E83">
         <v>17634.901171138</v>
@@ -8099,45 +8611,45 @@
         <v>2562</v>
       </c>
       <c r="M83">
-        <v>2756.530127502155</v>
+        <v>1596.21836260247</v>
       </c>
       <c r="N83">
-        <v>-194.5301275021548</v>
+        <v>965.7816373975297</v>
       </c>
       <c r="O83">
-        <v>-28.40139861531459</v>
+        <v>141.0041190600393</v>
       </c>
       <c r="P83">
-        <v>-166.1287288868402</v>
+        <v>824.7775183374904</v>
       </c>
       <c r="Q83">
-        <v>1550.87127111316</v>
+        <v>2541.777518337491</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3818557777931625</v>
+        <v>0.3784907992909314</v>
       </c>
       <c r="T83">
-        <v>7.756113713786124</v>
+        <v>7.68339028385523</v>
       </c>
       <c r="U83">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
-        <v>0.135696684853196</v>
+        <v>0.146</v>
       </c>
       <c r="W83">
-        <v>0.1131373039527166</v>
+        <v>0.0647332</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9294293483095615</v>
+        <v>1.605043557964664</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8660,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1650448139824013</v>
+        <v>0.1244318096056956</v>
       </c>
       <c r="C84">
-        <v>-4657.72804903589</v>
+        <v>2344.92927385911</v>
       </c>
       <c r="D84">
-        <v>13583.5405807896</v>
+        <v>20586.1979036846</v>
       </c>
       <c r="E84">
         <v>17894.88005686758</v>
@@ -8181,45 +8693,45 @@
         <v>2562</v>
       </c>
       <c r="M84">
-        <v>2790.561363644157</v>
+        <v>1615.924762140772</v>
       </c>
       <c r="N84">
-        <v>-228.5613636441567</v>
+        <v>946.0752378592276</v>
       </c>
       <c r="O84">
-        <v>-33.36995909204688</v>
+        <v>138.1269847274472</v>
       </c>
       <c r="P84">
-        <v>-195.1914045521098</v>
+        <v>807.9482531317803</v>
       </c>
       <c r="Q84">
-        <v>1521.80859544789</v>
+        <v>2524.94825313178</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.400525543226116</v>
+        <v>0.3963921422538643</v>
       </c>
       <c r="T84">
-        <v>8.187008920107576</v>
+        <v>8.09681621833405</v>
       </c>
       <c r="U84">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
-        <v>0.134041847233035</v>
+        <v>0.146</v>
       </c>
       <c r="W84">
-        <v>0.1133539221971957</v>
+        <v>0.0647332</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.9180948440618839</v>
+        <v>1.585469856038266</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8742,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1658958139824014</v>
+        <v>0.1245164753461141</v>
       </c>
       <c r="C85">
-        <v>-5013.960023453026</v>
+        <v>2062.808318375326</v>
       </c>
       <c r="D85">
-        <v>13487.28749210204</v>
+        <v>20564.0558339304</v>
       </c>
       <c r="E85">
         <v>18154.85894259715</v>
@@ -8263,45 +8775,45 @@
         <v>2562</v>
       </c>
       <c r="M85">
-        <v>2824.592599786159</v>
+        <v>1635.631161679074</v>
       </c>
       <c r="N85">
-        <v>-262.5925997861586</v>
+        <v>926.3688383209255</v>
       </c>
       <c r="O85">
-        <v>-38.33851956877916</v>
+        <v>135.2498503948551</v>
       </c>
       <c r="P85">
-        <v>-224.2540802173795</v>
+        <v>791.1189879260704</v>
       </c>
       <c r="Q85">
-        <v>1492.745919782621</v>
+        <v>2508.118987926071</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4213917516511817</v>
+        <v>0.4163995255653774</v>
       </c>
       <c r="T85">
-        <v>8.668597680113905</v>
+        <v>8.558880498045671</v>
       </c>
       <c r="U85">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
-        <v>0.1324268852181792</v>
+        <v>0.146</v>
       </c>
       <c r="W85">
-        <v>0.1135653207249403</v>
+        <v>0.0647332</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.9070334603984876</v>
+        <v>1.566367809579974</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8824,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1667468139824013</v>
+        <v>0.1246011410865328</v>
       </c>
       <c r="C86">
-        <v>-5368.83749541116</v>
+        <v>1780.734942779443</v>
       </c>
       <c r="D86">
-        <v>13392.38890587349</v>
+        <v>20541.96134406409</v>
       </c>
       <c r="E86">
         <v>18414.83782832673</v>
@@ -8345,45 +8857,45 @@
         <v>2562</v>
       </c>
       <c r="M86">
-        <v>2858.623835928161</v>
+        <v>1655.337561217377</v>
       </c>
       <c r="N86">
-        <v>-296.6238359281606</v>
+        <v>906.6624387826234</v>
       </c>
       <c r="O86">
-        <v>-43.30708004551144</v>
+        <v>132.372716062263</v>
       </c>
       <c r="P86">
-        <v>-253.3167558826491</v>
+        <v>774.2897227203605</v>
       </c>
       <c r="Q86">
-        <v>1463.683244117351</v>
+        <v>2491.28972272036</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4448662361293803</v>
+        <v>0.4389078317908295</v>
       </c>
       <c r="T86">
-        <v>9.210385035121019</v>
+        <v>9.078702812721239</v>
       </c>
       <c r="U86">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
-        <v>0.1308503746798675</v>
+        <v>0.146</v>
       </c>
       <c r="W86">
-        <v>0.1137716859544053</v>
+        <v>0.0647332</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8962354430127913</v>
+        <v>1.547720573751641</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8906,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1675978139824013</v>
+        <v>0.1246858068269514</v>
       </c>
       <c r="C87">
-        <v>-5722.388856592106</v>
+        <v>1498.708993873333</v>
       </c>
       <c r="D87">
-        <v>13298.81643042212</v>
+        <v>20519.91428088756</v>
       </c>
       <c r="E87">
         <v>18674.81671405631</v>
@@ -8427,45 +8939,45 @@
         <v>2562</v>
       </c>
       <c r="M87">
-        <v>2892.655072070162</v>
+        <v>1675.043960755679</v>
       </c>
       <c r="N87">
-        <v>-330.6550720701621</v>
+        <v>886.9560392443213</v>
       </c>
       <c r="O87">
-        <v>-48.27564052224366</v>
+        <v>129.4955817296709</v>
       </c>
       <c r="P87">
-        <v>-282.3794315479184</v>
+        <v>757.4604575146504</v>
       </c>
       <c r="Q87">
-        <v>1434.620568452081</v>
+        <v>2474.46045751465</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.471470651871339</v>
+        <v>0.4644172455130088</v>
       </c>
       <c r="T87">
-        <v>9.824410704129086</v>
+        <v>9.667834769353556</v>
       </c>
       <c r="U87">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
-        <v>0.1293109585071632</v>
+        <v>0.146</v>
       </c>
       <c r="W87">
-        <v>0.1139731955314123</v>
+        <v>0.0647332</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8856914966244057</v>
+        <v>1.529512096413386</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8988,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1684488139824013</v>
+        <v>0.1247704725673699</v>
       </c>
       <c r="C88">
-        <v>-6074.641710693801</v>
+        <v>1216.730319115832</v>
       </c>
       <c r="D88">
-        <v>13206.54246205001</v>
+        <v>20497.91449185964</v>
       </c>
       <c r="E88">
         <v>18934.79559978589</v>
@@ -8509,45 +9021,45 @@
         <v>2562</v>
       </c>
       <c r="M88">
-        <v>2926.686308212164</v>
+        <v>1694.750360293981</v>
       </c>
       <c r="N88">
-        <v>-364.686308212164</v>
+        <v>867.2496397060193</v>
       </c>
       <c r="O88">
-        <v>-53.24420099897594</v>
+        <v>126.6184473970788</v>
       </c>
       <c r="P88">
-        <v>-311.4421072131881</v>
+        <v>740.6311923089404</v>
       </c>
       <c r="Q88">
-        <v>1405.557892786812</v>
+        <v>2457.631192308941</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.5018756984335775</v>
+        <v>0.4935708611954995</v>
       </c>
       <c r="T88">
-        <v>10.52615432585259</v>
+        <v>10.34112843407621</v>
       </c>
       <c r="U88">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
-        <v>0.1278073427105683</v>
+        <v>0.146</v>
       </c>
       <c r="W88">
-        <v>0.1141700188391866</v>
+        <v>0.0647332</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8753927582915637</v>
+        <v>1.511727072036487</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +9070,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1692998139824013</v>
+        <v>0.1354054543077886</v>
       </c>
       <c r="C89">
-        <v>-6425.622900579128</v>
+        <v>-1476.079782320678</v>
       </c>
       <c r="D89">
-        <v>13115.54015789426</v>
+        <v>18065.08327615271</v>
       </c>
       <c r="E89">
         <v>19194.77448551547</v>
@@ -8591,45 +9103,45 @@
         <v>2562</v>
       </c>
       <c r="M89">
-        <v>2960.717544354166</v>
+        <v>2035.634675262605</v>
       </c>
       <c r="N89">
-        <v>-398.717544354166</v>
+        <v>526.3653247373952</v>
       </c>
       <c r="O89">
-        <v>-58.21276147570823</v>
+        <v>76.84933741165969</v>
       </c>
       <c r="P89">
-        <v>-340.5047828784577</v>
+        <v>449.5159873257355</v>
       </c>
       <c r="Q89">
-        <v>1376.495217121542</v>
+        <v>2166.515987325735</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5369584444669296</v>
+        <v>0.5272096485214502</v>
       </c>
       <c r="T89">
-        <v>11.33585850476433</v>
+        <v>11.11800573952541</v>
       </c>
       <c r="U89">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
-        <v>0.1263382927943549</v>
+        <v>0.146</v>
       </c>
       <c r="W89">
-        <v>0.1143623174732189</v>
+        <v>0.07686</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8653307725640745</v>
+        <v>1.258575534762637</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +9152,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1701508139824013</v>
+        <v>0.1584685634060725</v>
       </c>
       <c r="C90">
-        <v>-6775.358534309949</v>
+        <v>-5433.957832397278</v>
       </c>
       <c r="D90">
-        <v>13025.78340989302</v>
+        <v>14367.18411180569</v>
       </c>
       <c r="E90">
         <v>19454.75337124505</v>
@@ -8673,37 +9185,37 @@
         <v>2562</v>
       </c>
       <c r="M90">
-        <v>2994.748780496168</v>
+        <v>2713.347634582472</v>
       </c>
       <c r="N90">
-        <v>-432.7487804961679</v>
+        <v>-151.347634582472</v>
       </c>
       <c r="O90">
-        <v>-63.18132195244051</v>
+        <v>-22.09675464904091</v>
       </c>
       <c r="P90">
-        <v>-369.5674585437274</v>
+        <v>-129.2508799334311</v>
       </c>
       <c r="Q90">
-        <v>1347.432541456273</v>
+        <v>1587.749120066569</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5778883148391738</v>
+        <v>0.5707362267031002</v>
       </c>
       <c r="T90">
-        <v>12.28051338016136</v>
+        <v>12.12323849198846</v>
       </c>
       <c r="U90">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.1249026303762372</v>
+        <v>0.1378562758537053</v>
       </c>
       <c r="W90">
-        <v>0.1145502456837506</v>
+        <v>0.1022502456837506</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +9223,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8554974683303919</v>
+        <v>0.9442210674911321</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +9234,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1710018139824013</v>
+        <v>0.1591965634060725</v>
       </c>
       <c r="C91">
-        <v>-7123.874010119422</v>
+        <v>-5786.173287906666</v>
       </c>
       <c r="D91">
-        <v>12937.24681981312</v>
+        <v>14274.94754202588</v>
       </c>
       <c r="E91">
         <v>19714.73225697463</v>
@@ -8755,37 +9267,37 @@
         <v>2562</v>
       </c>
       <c r="M91">
-        <v>3028.78001663817</v>
+        <v>2744.18113043</v>
       </c>
       <c r="N91">
-        <v>-466.7800166381699</v>
+        <v>-182.1811304299999</v>
       </c>
       <c r="O91">
-        <v>-68.14988242917279</v>
+        <v>-26.59844504277999</v>
       </c>
       <c r="P91">
-        <v>-398.630134208997</v>
+        <v>-155.58268538722</v>
       </c>
       <c r="Q91">
-        <v>1318.369865791003</v>
+        <v>1561.41731461278</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6262599798245532</v>
+        <v>0.6184577018579276</v>
       </c>
       <c r="T91">
-        <v>13.39692368744876</v>
+        <v>13.22535108216923</v>
       </c>
       <c r="U91">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.1234992300349312</v>
+        <v>0.1363073289340007</v>
       </c>
       <c r="W91">
-        <v>0.1147339507884275</v>
+        <v>0.1024339507884275</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +9305,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.845885137225556</v>
+        <v>0.9336118420137037</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +9316,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1718528139824013</v>
+        <v>0.1599245634060725</v>
       </c>
       <c r="C92">
-        <v>-7471.19404037274</v>
+        <v>-6137.21199021244</v>
       </c>
       <c r="D92">
-        <v>12849.90567528938</v>
+        <v>14183.88772544969</v>
       </c>
       <c r="E92">
         <v>19974.71114270421</v>
@@ -8837,37 +9349,37 @@
         <v>2562</v>
       </c>
       <c r="M92">
-        <v>3062.811252780172</v>
+        <v>2775.014626277528</v>
       </c>
       <c r="N92">
-        <v>-500.8112527801718</v>
+        <v>-213.0146262775279</v>
       </c>
       <c r="O92">
-        <v>-73.11844290590508</v>
+        <v>-31.10013543651907</v>
       </c>
       <c r="P92">
-        <v>-427.6928098742667</v>
+        <v>-181.9144908410088</v>
       </c>
       <c r="Q92">
-        <v>1289.307190125733</v>
+        <v>1535.085509158991</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6843059778070085</v>
+        <v>0.6757234720437204</v>
       </c>
       <c r="T92">
-        <v>14.73661605619363</v>
+        <v>14.54788619038616</v>
       </c>
       <c r="U92">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.1221270163678764</v>
+        <v>0.1347928030569563</v>
       </c>
       <c r="W92">
-        <v>0.114913573557445</v>
+        <v>0.102613573557445</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9387,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8364864134786053</v>
+        <v>0.9232383771024404</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9398,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1727038139824013</v>
+        <v>0.1606525634060725</v>
       </c>
       <c r="C93">
-        <v>-7817.342674563843</v>
+        <v>-6487.096316081126</v>
       </c>
       <c r="D93">
-        <v>12763.73592682786</v>
+        <v>14093.98228531058</v>
       </c>
       <c r="E93">
         <v>20234.69002843379</v>
@@ -8919,37 +9431,37 @@
         <v>2562</v>
       </c>
       <c r="M93">
-        <v>3096.842488922174</v>
+        <v>2805.848122125057</v>
       </c>
       <c r="N93">
-        <v>-534.8424889221742</v>
+        <v>-243.8481221250568</v>
       </c>
       <c r="O93">
-        <v>-78.08700338263743</v>
+        <v>-35.60182583025829</v>
       </c>
       <c r="P93">
-        <v>-456.7554855395368</v>
+        <v>-208.2462962947985</v>
       </c>
       <c r="Q93">
-        <v>1260.244514460463</v>
+        <v>1508.753703705202</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7552510864522319</v>
+        <v>0.7457149689374671</v>
       </c>
       <c r="T93">
-        <v>16.37401784021515</v>
+        <v>16.16431798931795</v>
       </c>
       <c r="U93">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.1207849612429546</v>
+        <v>0.1333115634629238</v>
       </c>
       <c r="W93">
-        <v>0.1150892485732972</v>
+        <v>0.1027892485732972</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9469,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8272942550887304</v>
+        <v>0.9130929004309848</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9480,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1735548139824014</v>
+        <v>0.1613805634060725</v>
       </c>
       <c r="C94">
-        <v>-8162.343321392987</v>
+        <v>-6835.84807850674</v>
       </c>
       <c r="D94">
-        <v>12678.7141657283</v>
+        <v>14005.20940861454</v>
       </c>
       <c r="E94">
         <v>20494.66891416337</v>
@@ -9001,37 +9513,37 @@
         <v>2562</v>
       </c>
       <c r="M94">
-        <v>3130.873725064176</v>
+        <v>2836.681617972585</v>
       </c>
       <c r="N94">
-        <v>-568.8737250641757</v>
+        <v>-274.6816179725847</v>
       </c>
       <c r="O94">
-        <v>-83.05556385936964</v>
+        <v>-40.10351622399737</v>
       </c>
       <c r="P94">
-        <v>-485.8181612048061</v>
+        <v>-234.5781017485874</v>
       </c>
       <c r="Q94">
-        <v>1231.181838795194</v>
+        <v>1482.421898251413</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8439324722587611</v>
+        <v>0.8332043400546508</v>
       </c>
       <c r="T94">
-        <v>18.42077007024205</v>
+        <v>18.18485773798271</v>
       </c>
       <c r="U94">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.1194720812294443</v>
+        <v>0.1318625247296311</v>
       </c>
       <c r="W94">
-        <v>0.1152611045670657</v>
+        <v>0.1029611045670658</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9551,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8183019262290704</v>
+        <v>0.9031679776002133</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9562,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1744058139824013</v>
+        <v>0.1621085634060725</v>
       </c>
       <c r="C95">
-        <v>-8506.218769967783</v>
+        <v>-7183.48854435467</v>
       </c>
       <c r="D95">
-        <v>12594.81760288308</v>
+        <v>13917.54782849619</v>
       </c>
       <c r="E95">
         <v>20754.64779989295</v>
@@ -9083,37 +9595,37 @@
         <v>2562</v>
       </c>
       <c r="M95">
-        <v>3164.904961206178</v>
+        <v>2867.515113820113</v>
       </c>
       <c r="N95">
-        <v>-602.9049612061776</v>
+        <v>-305.5151138201127</v>
       </c>
       <c r="O95">
-        <v>-88.02412433610193</v>
+        <v>-44.60520661773645</v>
       </c>
       <c r="P95">
-        <v>-514.8808368700757</v>
+        <v>-260.9099072023762</v>
       </c>
       <c r="Q95">
-        <v>1202.119163129924</v>
+        <v>1456.090092797624</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9579513968671556</v>
+        <v>0.9456906743481727</v>
       </c>
       <c r="T95">
-        <v>21.0523086517052</v>
+        <v>20.78269455769453</v>
       </c>
       <c r="U95">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1181874351947191</v>
+        <v>0.1304446481196351</v>
       </c>
       <c r="W95">
-        <v>0.1154292647330113</v>
+        <v>0.1031292647330113</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9633,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.809502980785747</v>
+        <v>0.8934564939701034</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9644,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1752568139824013</v>
+        <v>0.1628365634060725</v>
       </c>
       <c r="C96">
-        <v>-8848.991210168046</v>
+        <v>-7530.038451346987</v>
       </c>
       <c r="D96">
-        <v>12512.0240484124</v>
+        <v>13830.97680723346</v>
       </c>
       <c r="E96">
         <v>21014.62668562253</v>
@@ -9165,37 +9677,37 @@
         <v>2562</v>
       </c>
       <c r="M96">
-        <v>3198.93619734818</v>
+        <v>2898.348609667641</v>
       </c>
       <c r="N96">
-        <v>-636.9361973481796</v>
+        <v>-336.3486096676406</v>
       </c>
       <c r="O96">
-        <v>-92.99268481283421</v>
+        <v>-49.10689701147553</v>
       </c>
       <c r="P96">
-        <v>-543.9435125353453</v>
+        <v>-287.2417126561651</v>
       </c>
       <c r="Q96">
-        <v>1173.056487464655</v>
+        <v>1429.758287343835</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.109976629678349</v>
+        <v>1.095672453406201</v>
       </c>
       <c r="T96">
-        <v>24.56102676032274</v>
+        <v>24.24647698397695</v>
       </c>
       <c r="U96">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.1169301220543497</v>
+        <v>0.1290569390970858</v>
       </c>
       <c r="W96">
-        <v>0.1155938470230856</v>
+        <v>0.1032938470230856</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9715,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8008912469476008</v>
+        <v>0.8839516376512726</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9726,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2598648272962839</v>
+        <v>0.1635645634060726</v>
       </c>
       <c r="C97">
-        <v>-14054.28274086792</v>
+        <v>-7875.518024417863</v>
       </c>
       <c r="D97">
-        <v>7566.711403442103</v>
+        <v>13745.47611989216</v>
       </c>
       <c r="E97">
         <v>21274.60557135211</v>
@@ -9247,45 +9759,45 @@
         <v>2562</v>
       </c>
       <c r="M97">
-        <v>5329.827136342103</v>
+        <v>2929.182105515169</v>
       </c>
       <c r="N97">
-        <v>-2767.827136342103</v>
+        <v>-367.182105515169</v>
       </c>
       <c r="O97">
-        <v>-404.102761905947</v>
+        <v>-53.60858740521468</v>
       </c>
       <c r="P97">
-        <v>-2363.724374436156</v>
+        <v>-313.5735181099544</v>
       </c>
       <c r="Q97">
-        <v>-646.7243744361558</v>
+        <v>1403.426481890046</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.384852221891669</v>
+        <v>1.305646944087443</v>
       </c>
       <c r="T97">
-        <v>30.90511155586229</v>
+        <v>29.09577238077235</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.07018088775327795</v>
+        <v>0.127698445001327</v>
       </c>
       <c r="W97">
-        <v>0.2006549644228426</v>
+        <v>0.1034549644228426</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4806910120087531</v>
+        <v>0.8746468835707328</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9808,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2615648272962839</v>
+        <v>0.1642925634060726</v>
       </c>
       <c r="C98">
-        <v>-14373.87935737892</v>
+        <v>-8219.946991465949</v>
       </c>
       <c r="D98">
-        <v>7507.093672660672</v>
+        <v>13661.02603857365</v>
       </c>
       <c r="E98">
         <v>21534.58445708168</v>
@@ -9329,45 +9841,45 @@
         <v>2562</v>
       </c>
       <c r="M98">
-        <v>5385.930579882545</v>
+        <v>2960.015601362697</v>
       </c>
       <c r="N98">
-        <v>-2823.930579882545</v>
+        <v>-398.0156013626965</v>
       </c>
       <c r="O98">
-        <v>-412.2938646628516</v>
+        <v>-58.11027779895369</v>
       </c>
       <c r="P98">
-        <v>-2411.636715219694</v>
+        <v>-339.9053235637429</v>
       </c>
       <c r="Q98">
-        <v>-694.6367152196935</v>
+        <v>1377.094676436257</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.719615277364583</v>
+        <v>1.6206086801093</v>
       </c>
       <c r="T98">
-        <v>38.63138944482778</v>
+        <v>36.36971547596536</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.06944983683918131</v>
+        <v>0.1263682528658965</v>
       </c>
       <c r="W98">
-        <v>0.2008127252101047</v>
+        <v>0.1036127252101047</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4756838139669953</v>
+        <v>0.8655359785335378</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9890,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2632648272962839</v>
+        <v>0.1650205634060725</v>
       </c>
       <c r="C99">
-        <v>-14692.54386782397</v>
+        <v>-8563.344598529759</v>
       </c>
       <c r="D99">
-        <v>7448.408047945208</v>
+        <v>13577.60731723942</v>
       </c>
       <c r="E99">
         <v>21794.56334281126</v>
@@ -9411,45 +9923,45 @@
         <v>2562</v>
       </c>
       <c r="M99">
-        <v>5442.03402342299</v>
+        <v>2990.849097210225</v>
       </c>
       <c r="N99">
-        <v>-2880.03402342299</v>
+        <v>-428.849097210225</v>
       </c>
       <c r="O99">
-        <v>-420.4849674197565</v>
+        <v>-62.61196819269284</v>
       </c>
       <c r="P99">
-        <v>-2459.549056003233</v>
+        <v>-366.2371290175321</v>
       </c>
       <c r="Q99">
-        <v>-742.5490560032331</v>
+        <v>1350.762870982468</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.277553703152777</v>
+        <v>2.1455449068124</v>
       </c>
       <c r="T99">
-        <v>51.50851925977037</v>
+        <v>48.49295396795382</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.0687338591398083</v>
+        <v>0.1250654873724336</v>
       </c>
       <c r="W99">
-        <v>0.2009672331976294</v>
+        <v>0.1037672331976294</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4707798571219747</v>
+        <v>0.8566129272084497</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9972,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2649648272962838</v>
+        <v>0.1657485634060725</v>
       </c>
       <c r="C100">
-        <v>-15010.2979624578</v>
+        <v>-8905.729624410324</v>
       </c>
       <c r="D100">
-        <v>7390.632839040958</v>
+        <v>13495.20117708843</v>
       </c>
       <c r="E100">
         <v>22054.54222854084</v>
@@ -9493,45 +10005,45 @@
         <v>2562</v>
       </c>
       <c r="M100">
-        <v>5498.137466963432</v>
+        <v>3021.682593057753</v>
       </c>
       <c r="N100">
-        <v>-2936.137466963432</v>
+        <v>-459.6825930577529</v>
       </c>
       <c r="O100">
-        <v>-428.6760701766611</v>
+        <v>-67.11365858643192</v>
       </c>
       <c r="P100">
-        <v>-2507.461396786771</v>
+        <v>-392.568934471321</v>
       </c>
       <c r="Q100">
-        <v>-790.4613967867713</v>
+        <v>1324.431065528679</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.393430554729165</v>
+        <v>3.195417360218598</v>
       </c>
       <c r="T100">
-        <v>77.26277888965554</v>
+        <v>72.73943095193071</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.06803249323021841</v>
+        <v>0.1237893089298578</v>
       </c>
       <c r="W100">
-        <v>0.2011185879609189</v>
+        <v>0.1039185879609189</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4659759810288934</v>
+        <v>0.8478719789716289</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +10054,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2666648272962838</v>
+        <v>0.1664765634060725</v>
       </c>
       <c r="C101">
-        <v>-15327.16266373426</v>
+        <v>-9247.120394764603</v>
       </c>
       <c r="D101">
-        <v>7333.747023494079</v>
+        <v>13413.78929246373</v>
       </c>
       <c r="E101">
         <v>22314.52111427042</v>
@@ -9575,45 +10087,45 @@
         <v>2562</v>
       </c>
       <c r="M101">
-        <v>5554.240910503876</v>
+        <v>3052.516088905281</v>
       </c>
       <c r="N101">
-        <v>-2992.240910503876</v>
+        <v>-490.5160889052809</v>
       </c>
       <c r="O101">
-        <v>-436.8671729335659</v>
+        <v>-71.61534898017101</v>
       </c>
       <c r="P101">
-        <v>-2555.37373757031</v>
+        <v>-418.9007399251099</v>
       </c>
       <c r="Q101">
-        <v>-838.3737375703099</v>
+        <v>1298.09926007489</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.74106110945833</v>
+        <v>6.345034720437199</v>
       </c>
       <c r="T101">
-        <v>154.5255577793111</v>
+        <v>145.4788619038615</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V101">
-        <v>0.06734529632890307</v>
+        <v>0.1225389118699603</v>
       </c>
       <c r="W101">
-        <v>0.2012668850522227</v>
+        <v>0.1040668850522227</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4612691529376923</v>
+        <v>0.8393076155476731</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_semiconductor.xlsx
@@ -1796,7 +1796,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1933,22 +1933,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1174892188913704</v>
+        <v>0.117356114631789</v>
       </c>
       <c r="C2">
-        <v>25656.82468075896</v>
+        <v>25438.84738861891</v>
       </c>
       <c r="D2">
-        <v>22579.82468075896</v>
+        <v>22621.82627434849</v>
       </c>
       <c r="E2">
-        <v>-3423.388572957917</v>
+        <v>-3163.409687228338</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>259.9788857295792</v>
       </c>
       <c r="G2">
         <v>3077</v>
@@ -1969,28 +1969,28 @@
         <v>2562</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>13.07693795219783</v>
       </c>
       <c r="N2">
-        <v>2562</v>
+        <v>2548.923062047802</v>
       </c>
       <c r="O2">
-        <v>374.052</v>
+        <v>372.1427670589791</v>
       </c>
       <c r="P2">
-        <v>2187.948</v>
+        <v>2176.780294988823</v>
       </c>
       <c r="Q2">
-        <v>3904.948</v>
+        <v>3893.780294988823</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1174892188913704</v>
+        <v>0.118107628920999</v>
       </c>
       <c r="T2">
-        <v>1.655640159154051</v>
+        <v>1.669922145981501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>195.9174241986371</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2015,22 +2015,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.117356114631789</v>
+        <v>0.1172230103722076</v>
       </c>
       <c r="C3">
-        <v>25438.84738861891</v>
+        <v>25221.02664521537</v>
       </c>
       <c r="D3">
-        <v>22621.82627434849</v>
+        <v>22663.98441667453</v>
       </c>
       <c r="E3">
-        <v>-3163.409687228338</v>
+        <v>-2903.430801498759</v>
       </c>
       <c r="F3">
-        <v>259.9788857295792</v>
+        <v>519.9577714591584</v>
       </c>
       <c r="G3">
         <v>3077</v>
@@ -2051,28 +2051,28 @@
         <v>2562</v>
       </c>
       <c r="M3">
-        <v>13.07693795219783</v>
+        <v>26.15387590439567</v>
       </c>
       <c r="N3">
-        <v>2548.923062047802</v>
+        <v>2535.846124095604</v>
       </c>
       <c r="O3">
-        <v>372.1427670589791</v>
+        <v>370.2335341179582</v>
       </c>
       <c r="P3">
-        <v>2176.780294988823</v>
+        <v>2165.612589977646</v>
       </c>
       <c r="Q3">
-        <v>3893.780294988823</v>
+        <v>3882.612589977646</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.118107628920999</v>
+        <v>0.1187386595634772</v>
       </c>
       <c r="T3">
-        <v>1.669922145981501</v>
+        <v>1.684495601927879</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>195.9174241986371</v>
+        <v>97.95871209931857</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2097,22 +2097,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1172230103722076</v>
+        <v>0.1170899061126262</v>
       </c>
       <c r="C4">
-        <v>25221.02664521537</v>
+        <v>25003.3633274174</v>
       </c>
       <c r="D4">
-        <v>22663.98441667453</v>
+        <v>22706.29998460614</v>
       </c>
       <c r="E4">
-        <v>-2903.430801498759</v>
+        <v>-2643.45191576918</v>
       </c>
       <c r="F4">
-        <v>519.9577714591584</v>
+        <v>779.9366571887374</v>
       </c>
       <c r="G4">
         <v>3077</v>
@@ -2133,28 +2133,28 @@
         <v>2562</v>
       </c>
       <c r="M4">
-        <v>26.15387590439567</v>
+        <v>39.23081385659349</v>
       </c>
       <c r="N4">
-        <v>2535.846124095604</v>
+        <v>2522.769186143406</v>
       </c>
       <c r="O4">
-        <v>370.2335341179582</v>
+        <v>368.3243011769373</v>
       </c>
       <c r="P4">
-        <v>2165.612589977646</v>
+        <v>2154.444884966469</v>
       </c>
       <c r="Q4">
-        <v>3882.612589977646</v>
+        <v>3871.444884966469</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1187386595634772</v>
+        <v>0.1193827011470373</v>
       </c>
       <c r="T4">
-        <v>1.684495601927879</v>
+        <v>1.699369541502017</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>97.95871209931857</v>
+        <v>65.30580806621238</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2179,22 +2179,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1170899061126262</v>
+        <v>0.1169568018530448</v>
       </c>
       <c r="C5">
-        <v>25003.3633274174</v>
+        <v>24785.858318655</v>
       </c>
       <c r="D5">
-        <v>22706.29998460614</v>
+        <v>22748.77386157331</v>
       </c>
       <c r="E5">
-        <v>-2643.45191576918</v>
+        <v>-2383.4730300396</v>
       </c>
       <c r="F5">
-        <v>779.9366571887374</v>
+        <v>1039.915542918317</v>
       </c>
       <c r="G5">
         <v>3077</v>
@@ -2215,28 +2215,28 @@
         <v>2562</v>
       </c>
       <c r="M5">
-        <v>39.23081385659349</v>
+        <v>52.30775180879133</v>
       </c>
       <c r="N5">
-        <v>2522.769186143406</v>
+        <v>2509.692248191209</v>
       </c>
       <c r="O5">
-        <v>368.3243011769373</v>
+        <v>366.4150682359165</v>
       </c>
       <c r="P5">
-        <v>2154.444884966469</v>
+        <v>2143.277179955292</v>
       </c>
       <c r="Q5">
-        <v>3871.444884966469</v>
+        <v>3860.277179955292</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1193827011470373</v>
+        <v>0.1200401602635883</v>
       </c>
       <c r="T5">
-        <v>1.699369541502017</v>
+        <v>1.714553354817283</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.30580806621238</v>
+        <v>48.97935604965929</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2261,22 +2261,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1169568018530448</v>
+        <v>0.1168236975934634</v>
       </c>
       <c r="C6">
-        <v>24785.858318655</v>
+        <v>24568.5125089807</v>
       </c>
       <c r="D6">
-        <v>22748.77386157331</v>
+        <v>22791.40693762859</v>
       </c>
       <c r="E6">
-        <v>-2383.4730300396</v>
+        <v>-2123.494144310022</v>
       </c>
       <c r="F6">
-        <v>1039.915542918317</v>
+        <v>1299.894428647896</v>
       </c>
       <c r="G6">
         <v>3077</v>
@@ -2297,28 +2297,28 @@
         <v>2562</v>
       </c>
       <c r="M6">
-        <v>52.30775180879133</v>
+        <v>65.38468976098916</v>
       </c>
       <c r="N6">
-        <v>2509.692248191209</v>
+        <v>2496.615310239011</v>
       </c>
       <c r="O6">
-        <v>366.4150682359165</v>
+        <v>364.5058352948956</v>
       </c>
       <c r="P6">
-        <v>2143.277179955292</v>
+        <v>2132.109474944115</v>
       </c>
       <c r="Q6">
-        <v>3860.277179955292</v>
+        <v>3849.109474944115</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1200401602635883</v>
+        <v>0.1207114606246983</v>
       </c>
       <c r="T6">
-        <v>1.714553354817283</v>
+        <v>1.730056827360239</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.97935604965929</v>
+        <v>39.18348483972743</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2343,22 +2343,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1168236975934634</v>
+        <v>0.116690593333882</v>
       </c>
       <c r="C7">
-        <v>24568.5125089807</v>
+        <v>24351.32679513167</v>
       </c>
       <c r="D7">
-        <v>22791.40693762859</v>
+        <v>22834.20010950915</v>
       </c>
       <c r="E7">
-        <v>-2123.494144310022</v>
+        <v>-1863.515258580442</v>
       </c>
       <c r="F7">
-        <v>1299.894428647896</v>
+        <v>1559.873314377475</v>
       </c>
       <c r="G7">
         <v>3077</v>
@@ -2379,28 +2379,28 @@
         <v>2562</v>
       </c>
       <c r="M7">
-        <v>65.38468976098916</v>
+        <v>78.46162771318699</v>
       </c>
       <c r="N7">
-        <v>2496.615310239011</v>
+        <v>2483.538372286813</v>
       </c>
       <c r="O7">
-        <v>364.5058352948956</v>
+        <v>362.5966023538747</v>
       </c>
       <c r="P7">
-        <v>2132.109474944115</v>
+        <v>2120.941769932939</v>
       </c>
       <c r="Q7">
-        <v>3849.109474944115</v>
+        <v>3837.941769932939</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1207114606246983</v>
+        <v>0.1213970439722149</v>
       </c>
       <c r="T7">
-        <v>1.730056827360239</v>
+        <v>1.74589016102113</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.18348483972743</v>
+        <v>32.6529040331062</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2425,22 +2425,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.116690593333882</v>
+        <v>0.1165574890743006</v>
       </c>
       <c r="C8">
-        <v>24351.32679513167</v>
+        <v>24134.30208059263</v>
       </c>
       <c r="D8">
-        <v>22834.20010950915</v>
+        <v>22877.15428069968</v>
       </c>
       <c r="E8">
-        <v>-1863.515258580443</v>
+        <v>-1603.536372850863</v>
       </c>
       <c r="F8">
-        <v>1559.873314377475</v>
+        <v>1819.852200107054</v>
       </c>
       <c r="G8">
         <v>3077</v>
@@ -2461,28 +2461,28 @@
         <v>2562</v>
       </c>
       <c r="M8">
-        <v>78.46162771318699</v>
+        <v>91.53856566538481</v>
       </c>
       <c r="N8">
-        <v>2483.538372286813</v>
+        <v>2470.461434334615</v>
       </c>
       <c r="O8">
-        <v>362.5966023538747</v>
+        <v>360.6873694128538</v>
       </c>
       <c r="P8">
-        <v>2120.941769932939</v>
+        <v>2109.774064921761</v>
       </c>
       <c r="Q8">
-        <v>3837.941769932939</v>
+        <v>3826.774064921761</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1213970439722149</v>
+        <v>0.122097371047635</v>
       </c>
       <c r="T8">
-        <v>1.74589016102113</v>
+        <v>1.76206399648118</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.6529040331062</v>
+        <v>27.98820345694817</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2507,22 +2507,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1165574890743006</v>
+        <v>0.1164243848147192</v>
       </c>
       <c r="C9">
-        <v>24134.30208059262</v>
+        <v>23917.43927565937</v>
       </c>
       <c r="D9">
-        <v>22877.15428069968</v>
+        <v>22920.270361496</v>
       </c>
       <c r="E9">
-        <v>-1603.536372850863</v>
+        <v>-1343.557487121284</v>
       </c>
       <c r="F9">
-        <v>1819.852200107054</v>
+        <v>2079.831085836634</v>
       </c>
       <c r="G9">
         <v>3077</v>
@@ -2543,28 +2543,28 @@
         <v>2562</v>
       </c>
       <c r="M9">
-        <v>91.53856566538484</v>
+        <v>104.6155036175827</v>
       </c>
       <c r="N9">
-        <v>2470.461434334615</v>
+        <v>2457.384496382417</v>
       </c>
       <c r="O9">
-        <v>360.6873694128538</v>
+        <v>358.7781364718329</v>
       </c>
       <c r="P9">
-        <v>2109.774064921761</v>
+        <v>2098.606359910584</v>
       </c>
       <c r="Q9">
-        <v>3826.774064921761</v>
+        <v>3815.606359910584</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.122097371047635</v>
+        <v>0.1228129226246948</v>
       </c>
       <c r="T9">
-        <v>1.76206399648118</v>
+        <v>1.778589437059926</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.98820345694816</v>
+        <v>24.48967802482964</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2589,22 +2589,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1164243848147192</v>
+        <v>0.1162912805551378</v>
       </c>
       <c r="C10">
-        <v>23917.43927565937</v>
+        <v>23700.73929750313</v>
       </c>
       <c r="D10">
-        <v>22920.270361496</v>
+        <v>22963.54926906934</v>
       </c>
       <c r="E10">
-        <v>-1343.557487121284</v>
+        <v>-1083.578601391705</v>
       </c>
       <c r="F10">
-        <v>2079.831085836634</v>
+        <v>2339.809971566212</v>
       </c>
       <c r="G10">
         <v>3077</v>
@@ -2625,28 +2625,28 @@
         <v>2562</v>
       </c>
       <c r="M10">
-        <v>104.6155036175827</v>
+        <v>117.6924415697805</v>
       </c>
       <c r="N10">
-        <v>2457.384496382417</v>
+        <v>2444.30755843022</v>
       </c>
       <c r="O10">
-        <v>358.7781364718329</v>
+        <v>356.868903530812</v>
       </c>
       <c r="P10">
-        <v>2098.606359910584</v>
+        <v>2087.438654899408</v>
       </c>
       <c r="Q10">
-        <v>3815.606359910584</v>
+        <v>3804.438654899408</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1228129226246948</v>
+        <v>0.1235442006100415</v>
       </c>
       <c r="T10">
-        <v>1.778589437059926</v>
+        <v>1.795478074134909</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.48967802482964</v>
+        <v>21.76860268873746</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2671,22 +2671,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1162912805551378</v>
+        <v>0.1161581762955564</v>
       </c>
       <c r="C11">
-        <v>23700.73929750313</v>
+        <v>23484.2030702356</v>
       </c>
       <c r="D11">
-        <v>22963.54926906934</v>
+        <v>23006.9919275314</v>
       </c>
       <c r="E11">
-        <v>-1083.578601391705</v>
+        <v>-823.5997156621261</v>
       </c>
       <c r="F11">
-        <v>2339.809971566212</v>
+        <v>2599.788857295791</v>
       </c>
       <c r="G11">
         <v>3077</v>
@@ -2707,28 +2707,28 @@
         <v>2562</v>
       </c>
       <c r="M11">
-        <v>117.6924415697805</v>
+        <v>130.7693795219783</v>
       </c>
       <c r="N11">
-        <v>2444.30755843022</v>
+        <v>2431.230620478022</v>
       </c>
       <c r="O11">
-        <v>356.868903530812</v>
+        <v>354.9596705897911</v>
       </c>
       <c r="P11">
-        <v>2087.438654899408</v>
+        <v>2076.27094988823</v>
       </c>
       <c r="Q11">
-        <v>3804.438654899408</v>
+        <v>3793.27094988823</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1235442006100415</v>
+        <v>0.1242917292172849</v>
       </c>
       <c r="T11">
-        <v>1.795478074134909</v>
+        <v>1.812742014256002</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.76860268873746</v>
+        <v>19.59174241986372</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2753,22 +2753,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1161581762955564</v>
+        <v>0.116025072035975</v>
       </c>
       <c r="C12">
-        <v>23484.2030702356</v>
+        <v>23267.83152497468</v>
       </c>
       <c r="D12">
-        <v>23006.9919275314</v>
+        <v>23050.59926800006</v>
       </c>
       <c r="E12">
-        <v>-823.5997156621256</v>
+        <v>-563.6208299325467</v>
       </c>
       <c r="F12">
-        <v>2599.788857295792</v>
+        <v>2859.767743025371</v>
       </c>
       <c r="G12">
         <v>3077</v>
@@ -2789,28 +2789,28 @@
         <v>2562</v>
       </c>
       <c r="M12">
-        <v>130.7693795219783</v>
+        <v>143.8463174741761</v>
       </c>
       <c r="N12">
-        <v>2431.230620478022</v>
+        <v>2418.153682525824</v>
       </c>
       <c r="O12">
-        <v>354.9596705897911</v>
+        <v>353.0504376487703</v>
       </c>
       <c r="P12">
-        <v>2076.27094988823</v>
+        <v>2065.103244877054</v>
       </c>
       <c r="Q12">
-        <v>3793.27094988823</v>
+        <v>3782.103244877054</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1242917292172849</v>
+        <v>0.1250560562201966</v>
       </c>
       <c r="T12">
-        <v>1.812742014256002</v>
+        <v>1.830393908087683</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.59174241986371</v>
+        <v>17.81067492714883</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.116025072035975</v>
+        <v>0.1158919677763936</v>
       </c>
       <c r="C13">
-        <v>23267.83152497468</v>
+        <v>23051.62559991105</v>
       </c>
       <c r="D13">
-        <v>23050.59926800006</v>
+        <v>23094.372228666</v>
       </c>
       <c r="E13">
-        <v>-563.6208299325467</v>
+        <v>-303.6419442029678</v>
       </c>
       <c r="F13">
-        <v>2859.767743025371</v>
+        <v>3119.74662875495</v>
       </c>
       <c r="G13">
         <v>3077</v>
@@ -2871,28 +2871,28 @@
         <v>2562</v>
       </c>
       <c r="M13">
-        <v>143.8463174741761</v>
+        <v>156.923255426374</v>
       </c>
       <c r="N13">
-        <v>2418.153682525824</v>
+        <v>2405.076744573626</v>
       </c>
       <c r="O13">
-        <v>353.0504376487703</v>
+        <v>351.1412047077494</v>
       </c>
       <c r="P13">
-        <v>2065.103244877054</v>
+        <v>2053.935539865877</v>
       </c>
       <c r="Q13">
-        <v>3782.103244877054</v>
+        <v>3770.935539865877</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1250560562201966</v>
+        <v>0.1258377542913564</v>
       </c>
       <c r="T13">
-        <v>1.830393908087683</v>
+        <v>1.848446981324628</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.81067492714883</v>
+        <v>16.3264520165531</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2917,22 +2917,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1158919677763936</v>
+        <v>0.1157588635168122</v>
       </c>
       <c r="C14">
-        <v>23051.62559991105</v>
+        <v>22835.5862403754</v>
       </c>
       <c r="D14">
-        <v>23094.372228666</v>
+        <v>23138.31175485993</v>
       </c>
       <c r="E14">
-        <v>-303.6419442029678</v>
+        <v>-43.66305847338799</v>
       </c>
       <c r="F14">
-        <v>3119.74662875495</v>
+        <v>3379.725514484529</v>
       </c>
       <c r="G14">
         <v>3077</v>
@@ -2953,28 +2953,28 @@
         <v>2562</v>
       </c>
       <c r="M14">
-        <v>156.923255426374</v>
+        <v>170.0001933785718</v>
       </c>
       <c r="N14">
-        <v>2405.076744573626</v>
+        <v>2391.999806621428</v>
       </c>
       <c r="O14">
-        <v>351.1412047077494</v>
+        <v>349.2319717667285</v>
       </c>
       <c r="P14">
-        <v>2053.935539865877</v>
+        <v>2042.767834854699</v>
       </c>
       <c r="Q14">
-        <v>3770.935539865877</v>
+        <v>3759.7678348547</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1258377542913564</v>
+        <v>0.1266374224331175</v>
       </c>
       <c r="T14">
-        <v>1.848446981324628</v>
+        <v>1.866915067739434</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.3264520165531</v>
+        <v>15.07057109220286</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2999,22 +2999,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1157588635168122</v>
+        <v>0.1156257592572308</v>
       </c>
       <c r="C15">
-        <v>22835.5862403754</v>
+        <v>22619.7143989065</v>
       </c>
       <c r="D15">
-        <v>23138.31175485993</v>
+        <v>23182.41879912061</v>
       </c>
       <c r="E15">
-        <v>-43.66305847338799</v>
+        <v>216.3158272561914</v>
       </c>
       <c r="F15">
-        <v>3379.725514484529</v>
+        <v>3639.704400214109</v>
       </c>
       <c r="G15">
         <v>3077</v>
@@ -3035,28 +3035,28 @@
         <v>2562</v>
       </c>
       <c r="M15">
-        <v>170.0001933785718</v>
+        <v>183.0771313307697</v>
       </c>
       <c r="N15">
-        <v>2391.999806621428</v>
+        <v>2378.92286866923</v>
       </c>
       <c r="O15">
-        <v>349.2319717667285</v>
+        <v>347.3227388257076</v>
       </c>
       <c r="P15">
-        <v>2042.767834854699</v>
+        <v>2031.600129843523</v>
       </c>
       <c r="Q15">
-        <v>3759.7678348547</v>
+        <v>3748.600129843523</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1266374224331175</v>
+        <v>0.1274556875084079</v>
       </c>
       <c r="T15">
-        <v>1.866915067739434</v>
+        <v>1.88581264453598</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.07057109220286</v>
+        <v>13.99410172847408</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3081,22 +3081,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1156257592572308</v>
+        <v>0.1154926549976494</v>
       </c>
       <c r="C16">
-        <v>22619.7143989065</v>
+        <v>22404.01103532005</v>
       </c>
       <c r="D16">
-        <v>23182.41879912061</v>
+        <v>23226.69432126374</v>
       </c>
       <c r="E16">
-        <v>216.3158272561914</v>
+        <v>476.2947129857707</v>
       </c>
       <c r="F16">
-        <v>3639.704400214109</v>
+        <v>3899.683285943688</v>
       </c>
       <c r="G16">
         <v>3077</v>
@@ -3117,28 +3117,28 @@
         <v>2562</v>
       </c>
       <c r="M16">
-        <v>183.0771313307697</v>
+        <v>196.1540692829675</v>
       </c>
       <c r="N16">
-        <v>2378.92286866923</v>
+        <v>2365.845930717032</v>
       </c>
       <c r="O16">
-        <v>347.3227388257076</v>
+        <v>345.4135058846867</v>
       </c>
       <c r="P16">
-        <v>2031.600129843523</v>
+        <v>2020.432424832346</v>
       </c>
       <c r="Q16">
-        <v>3748.600129843523</v>
+        <v>3737.432424832346</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1274556875084079</v>
+        <v>0.1282932058795875</v>
       </c>
       <c r="T16">
-        <v>1.88581264453598</v>
+        <v>1.905154870198327</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.99410172847408</v>
+        <v>13.06116161324247</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3163,22 +3163,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1154926549976494</v>
+        <v>0.115359550738068</v>
       </c>
       <c r="C17">
-        <v>22404.01103532005</v>
+        <v>22188.47711677834</v>
       </c>
       <c r="D17">
-        <v>23226.69432126374</v>
+        <v>23271.1392884516</v>
       </c>
       <c r="E17">
-        <v>476.2947129857698</v>
+        <v>736.2735987153496</v>
       </c>
       <c r="F17">
-        <v>3899.683285943687</v>
+        <v>4159.662171673267</v>
       </c>
       <c r="G17">
         <v>3077</v>
@@ -3199,28 +3199,28 @@
         <v>2562</v>
       </c>
       <c r="M17">
-        <v>196.1540692829675</v>
+        <v>209.2310072351653</v>
       </c>
       <c r="N17">
-        <v>2365.845930717032</v>
+        <v>2352.768992764835</v>
       </c>
       <c r="O17">
-        <v>345.4135058846867</v>
+        <v>343.5042729436659</v>
       </c>
       <c r="P17">
-        <v>2020.432424832346</v>
+        <v>2009.264719821169</v>
       </c>
       <c r="Q17">
-        <v>3737.432424832346</v>
+        <v>3726.264719821169</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1282932058795875</v>
+        <v>0.1291506651643667</v>
       </c>
       <c r="T17">
-        <v>1.905154870198327</v>
+        <v>1.924957625043111</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.06116161324248</v>
+        <v>12.24483901241482</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3245,22 +3245,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.115359550738068</v>
+        <v>0.1152264464784866</v>
       </c>
       <c r="C18">
-        <v>22188.47711677834</v>
+        <v>21973.11361786054</v>
       </c>
       <c r="D18">
-        <v>23271.1392884516</v>
+        <v>23315.75467526339</v>
       </c>
       <c r="E18">
-        <v>736.2735987153496</v>
+        <v>996.2524844449285</v>
       </c>
       <c r="F18">
-        <v>4159.662171673267</v>
+        <v>4419.641057402846</v>
       </c>
       <c r="G18">
         <v>3077</v>
@@ -3281,28 +3281,28 @@
         <v>2562</v>
       </c>
       <c r="M18">
-        <v>209.2310072351653</v>
+        <v>222.3079451873631</v>
       </c>
       <c r="N18">
-        <v>2352.768992764835</v>
+        <v>2339.692054812637</v>
       </c>
       <c r="O18">
-        <v>343.5042729436659</v>
+        <v>341.595040002645</v>
       </c>
       <c r="P18">
-        <v>2009.264719821169</v>
+        <v>1998.097014809992</v>
       </c>
       <c r="Q18">
-        <v>3726.264719821169</v>
+        <v>3715.097014809992</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1291506651643667</v>
+        <v>0.1300287861186585</v>
       </c>
       <c r="T18">
-        <v>1.924957625043111</v>
+        <v>1.945237554703431</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.24483901241482</v>
+        <v>11.52455436462571</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3327,22 +3327,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1152264464784866</v>
+        <v>0.1150933422189052</v>
       </c>
       <c r="C19">
-        <v>21973.11361786054</v>
+        <v>21757.92152063408</v>
       </c>
       <c r="D19">
-        <v>23315.75467526339</v>
+        <v>23360.54146376651</v>
       </c>
       <c r="E19">
-        <v>996.2524844449285</v>
+        <v>1256.231370174508</v>
       </c>
       <c r="F19">
-        <v>4419.641057402846</v>
+        <v>4679.619943132426</v>
       </c>
       <c r="G19">
         <v>3077</v>
@@ -3363,28 +3363,28 @@
         <v>2562</v>
       </c>
       <c r="M19">
-        <v>222.3079451873631</v>
+        <v>235.384883139561</v>
       </c>
       <c r="N19">
-        <v>2339.692054812637</v>
+        <v>2326.615116860439</v>
       </c>
       <c r="O19">
-        <v>341.595040002645</v>
+        <v>339.6858070616241</v>
       </c>
       <c r="P19">
-        <v>1998.097014809992</v>
+        <v>1986.929309798815</v>
       </c>
       <c r="Q19">
-        <v>3715.097014809992</v>
+        <v>3703.929309798815</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1300287861186585</v>
+        <v>0.1309283246572014</v>
       </c>
       <c r="T19">
-        <v>1.945237554703431</v>
+        <v>1.966012116794492</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.52455436462571</v>
+        <v>10.88430134436873</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3409,22 +3409,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1150933422189052</v>
+        <v>0.1149602379593238</v>
       </c>
       <c r="C20">
-        <v>21757.92152063408</v>
+        <v>21542.90181472663</v>
       </c>
       <c r="D20">
-        <v>23360.5414637665</v>
+        <v>23405.50064358864</v>
       </c>
       <c r="E20">
-        <v>1256.231370174507</v>
+        <v>1516.210255904086</v>
       </c>
       <c r="F20">
-        <v>4679.619943132425</v>
+        <v>4939.598828862004</v>
       </c>
       <c r="G20">
         <v>3077</v>
@@ -3445,28 +3445,28 @@
         <v>2562</v>
       </c>
       <c r="M20">
-        <v>235.384883139561</v>
+        <v>248.4618210917588</v>
       </c>
       <c r="N20">
-        <v>2326.615116860439</v>
+        <v>2313.538178908241</v>
       </c>
       <c r="O20">
-        <v>339.6858070616241</v>
+        <v>337.7765741206032</v>
       </c>
       <c r="P20">
-        <v>1986.929309798815</v>
+        <v>1975.761604787638</v>
       </c>
       <c r="Q20">
-        <v>3703.929309798815</v>
+        <v>3692.761604787638</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1309283246572014</v>
+        <v>0.1318500740238565</v>
       </c>
       <c r="T20">
-        <v>1.966012116794492</v>
+        <v>1.987299631035948</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.88430134436873</v>
+        <v>10.31144337887564</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3491,22 +3491,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1149602379593238</v>
+        <v>0.1148271336997424</v>
       </c>
       <c r="C21">
-        <v>21542.90181472663</v>
+        <v>21328.05549739905</v>
       </c>
       <c r="D21">
-        <v>23405.50064358864</v>
+        <v>23450.63321199064</v>
       </c>
       <c r="E21">
-        <v>1516.210255904086</v>
+        <v>1776.189141633666</v>
       </c>
       <c r="F21">
-        <v>4939.598828862004</v>
+        <v>5199.577714591584</v>
       </c>
       <c r="G21">
         <v>3077</v>
@@ -3527,28 +3527,28 @@
         <v>2562</v>
       </c>
       <c r="M21">
-        <v>248.4618210917588</v>
+        <v>261.5387590439566</v>
       </c>
       <c r="N21">
-        <v>2313.538178908241</v>
+        <v>2300.461240956043</v>
       </c>
       <c r="O21">
-        <v>337.7765741206032</v>
+        <v>335.8673411795823</v>
       </c>
       <c r="P21">
-        <v>1975.761604787638</v>
+        <v>1964.593899776461</v>
       </c>
       <c r="Q21">
-        <v>3692.761604787638</v>
+        <v>3681.593899776461</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1318500740238565</v>
+        <v>0.132794867124678</v>
       </c>
       <c r="T21">
-        <v>1.987299631035948</v>
+        <v>2.009119333133441</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.31144337887564</v>
+        <v>9.795871209931857</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3573,22 +3573,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1148271336997424</v>
+        <v>0.114694029440161</v>
       </c>
       <c r="C22">
-        <v>21328.05549739905</v>
+        <v>21113.38357361902</v>
       </c>
       <c r="D22">
-        <v>23450.63321199064</v>
+        <v>23495.94017394018</v>
       </c>
       <c r="E22">
-        <v>1776.189141633666</v>
+        <v>2036.168027363245</v>
       </c>
       <c r="F22">
-        <v>5199.577714591584</v>
+        <v>5459.556600321162</v>
       </c>
       <c r="G22">
         <v>3077</v>
@@ -3609,28 +3609,28 @@
         <v>2562</v>
       </c>
       <c r="M22">
-        <v>261.5387590439566</v>
+        <v>274.6156969961544</v>
       </c>
       <c r="N22">
-        <v>2300.461240956043</v>
+        <v>2287.384303003846</v>
       </c>
       <c r="O22">
-        <v>335.8673411795823</v>
+        <v>333.9581082385615</v>
       </c>
       <c r="P22">
-        <v>1964.593899776461</v>
+        <v>1953.426194765284</v>
       </c>
       <c r="Q22">
-        <v>3681.593899776461</v>
+        <v>3670.426194765284</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.132794867124678</v>
+        <v>0.1337635790381785</v>
       </c>
       <c r="T22">
-        <v>2.009119333133441</v>
+        <v>2.03149143275239</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.795871209931857</v>
+        <v>9.329401152316056</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3655,22 +3655,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.114694029440161</v>
+        <v>0.1145609251805796</v>
       </c>
       <c r="C23">
-        <v>21113.38357361903</v>
+        <v>20898.88705613577</v>
       </c>
       <c r="D23">
-        <v>23495.94017394019</v>
+        <v>23541.42254218651</v>
       </c>
       <c r="E23">
-        <v>2036.168027363245</v>
+        <v>2296.146913092824</v>
       </c>
       <c r="F23">
-        <v>5459.556600321162</v>
+        <v>5719.535486050741</v>
       </c>
       <c r="G23">
         <v>3077</v>
@@ -3691,28 +3691,28 @@
         <v>2562</v>
       </c>
       <c r="M23">
-        <v>274.6156969961544</v>
+        <v>287.6926349483523</v>
       </c>
       <c r="N23">
-        <v>2287.384303003846</v>
+        <v>2274.307365051648</v>
       </c>
       <c r="O23">
-        <v>333.9581082385615</v>
+        <v>332.0488752975405</v>
       </c>
       <c r="P23">
-        <v>1953.426194765284</v>
+        <v>1942.258489754107</v>
       </c>
       <c r="Q23">
-        <v>3670.426194765284</v>
+        <v>3659.258489754107</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1337635790381785</v>
+        <v>0.1347571297186918</v>
       </c>
       <c r="T23">
-        <v>2.03149143275239</v>
+        <v>2.054437175951312</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.329401152316056</v>
+        <v>8.905337463574416</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3737,22 +3737,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1145609251805796</v>
+        <v>0.1147224509209982</v>
       </c>
       <c r="C24">
-        <v>20898.88705613577</v>
+        <v>20583.73680525854</v>
       </c>
       <c r="D24">
-        <v>23541.42254218651</v>
+        <v>23486.25117703886</v>
       </c>
       <c r="E24">
-        <v>2296.146913092824</v>
+        <v>2556.125798822404</v>
       </c>
       <c r="F24">
-        <v>5719.535486050741</v>
+        <v>5979.514371780321</v>
       </c>
       <c r="G24">
         <v>3077</v>
@@ -3773,45 +3773,45 @@
         <v>2562</v>
       </c>
       <c r="M24">
-        <v>287.6926349483523</v>
+        <v>309.7388444582206</v>
       </c>
       <c r="N24">
-        <v>2274.307365051648</v>
+        <v>2252.261155541779</v>
       </c>
       <c r="O24">
-        <v>332.0488752975405</v>
+        <v>328.8301287090998</v>
       </c>
       <c r="P24">
-        <v>1942.258489754107</v>
+        <v>1923.431026832679</v>
       </c>
       <c r="Q24">
-        <v>3659.258489754107</v>
+        <v>3640.431026832679</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1347571297186918</v>
+        <v>0.1357764869103872</v>
       </c>
       <c r="T24">
-        <v>2.054437175951312</v>
+        <v>2.077978912480076</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.905337463574416</v>
+        <v>8.271484335396549</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3819,22 +3819,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1147224509209982</v>
+        <v>0.1146021566614168</v>
       </c>
       <c r="C25">
-        <v>20583.73680525854</v>
+        <v>20364.82147527748</v>
       </c>
       <c r="D25">
-        <v>23486.25117703886</v>
+        <v>23527.31473278738</v>
       </c>
       <c r="E25">
-        <v>2556.125798822404</v>
+        <v>2816.104684551983</v>
       </c>
       <c r="F25">
-        <v>5979.514371780321</v>
+        <v>6239.4932575099</v>
       </c>
       <c r="G25">
         <v>3077</v>
@@ -3855,28 +3855,28 @@
         <v>2562</v>
       </c>
       <c r="M25">
-        <v>309.7388444582206</v>
+        <v>323.2057507390128</v>
       </c>
       <c r="N25">
-        <v>2252.261155541779</v>
+        <v>2238.794249260987</v>
       </c>
       <c r="O25">
-        <v>328.8301287090998</v>
+        <v>326.8639603921041</v>
       </c>
       <c r="P25">
-        <v>1923.431026832679</v>
+        <v>1911.930288868883</v>
       </c>
       <c r="Q25">
-        <v>3640.431026832679</v>
+        <v>3628.930288868883</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1357764869103872</v>
+        <v>0.1368226692913379</v>
       </c>
       <c r="T25">
-        <v>2.077978912480076</v>
+        <v>2.102140168391176</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.271484335396549</v>
+        <v>7.926839154755026</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1146021566614168</v>
+        <v>0.1144818624018354</v>
       </c>
       <c r="C26">
-        <v>20364.82147527748</v>
+        <v>20146.04998851388</v>
       </c>
       <c r="D26">
-        <v>23527.31473278738</v>
+        <v>23568.52213175336</v>
       </c>
       <c r="E26">
-        <v>2816.104684551982</v>
+        <v>3076.083570281562</v>
       </c>
       <c r="F26">
-        <v>6239.493257509899</v>
+        <v>6499.472143239479</v>
       </c>
       <c r="G26">
         <v>3077</v>
@@ -3937,28 +3937,28 @@
         <v>2562</v>
       </c>
       <c r="M26">
-        <v>323.2057507390128</v>
+        <v>336.672657019805</v>
       </c>
       <c r="N26">
-        <v>2238.794249260987</v>
+        <v>2225.327342980195</v>
       </c>
       <c r="O26">
-        <v>326.8639603921041</v>
+        <v>324.8977920751084</v>
       </c>
       <c r="P26">
-        <v>1911.930288868883</v>
+        <v>1900.429550905086</v>
       </c>
       <c r="Q26">
-        <v>3628.930288868883</v>
+        <v>3617.429550905086</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1368226692913379</v>
+        <v>0.1378967498691138</v>
       </c>
       <c r="T26">
-        <v>2.102140168391176</v>
+        <v>2.126945724459905</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.926839154755027</v>
+        <v>7.609765588564825</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3983,22 +3983,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1144818624018354</v>
+        <v>0.114361568142254</v>
       </c>
       <c r="C27">
-        <v>20146.04998851388</v>
+        <v>19927.42310210534</v>
       </c>
       <c r="D27">
-        <v>23568.52213175336</v>
+        <v>23609.8741310744</v>
       </c>
       <c r="E27">
-        <v>3076.083570281562</v>
+        <v>3336.062456011141</v>
       </c>
       <c r="F27">
-        <v>6499.472143239479</v>
+        <v>6759.451028969059</v>
       </c>
       <c r="G27">
         <v>3077</v>
@@ -4019,28 +4019,28 @@
         <v>2562</v>
       </c>
       <c r="M27">
-        <v>336.672657019805</v>
+        <v>350.1395633005972</v>
       </c>
       <c r="N27">
-        <v>2225.327342980195</v>
+        <v>2211.860436699403</v>
       </c>
       <c r="O27">
-        <v>324.8977920751084</v>
+        <v>322.9316237581128</v>
       </c>
       <c r="P27">
-        <v>1900.429550905086</v>
+        <v>1888.92881294129</v>
       </c>
       <c r="Q27">
-        <v>3617.429550905086</v>
+        <v>3605.92881294129</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1378967498691138</v>
+        <v>0.1389998596516946</v>
       </c>
       <c r="T27">
-        <v>2.126945724459905</v>
+        <v>2.152421700962924</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.609765588564825</v>
+        <v>7.317082296696947</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4065,22 +4065,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.114361568142254</v>
+        <v>0.1142412738826726</v>
       </c>
       <c r="C28">
-        <v>19927.42310210534</v>
+        <v>19708.94157851247</v>
       </c>
       <c r="D28">
-        <v>23609.8741310744</v>
+        <v>23651.37149321111</v>
       </c>
       <c r="E28">
-        <v>3336.062456011141</v>
+        <v>3596.04134174072</v>
       </c>
       <c r="F28">
-        <v>6759.451028969059</v>
+        <v>7019.429914698638</v>
       </c>
       <c r="G28">
         <v>3077</v>
@@ -4101,28 +4101,28 @@
         <v>2562</v>
       </c>
       <c r="M28">
-        <v>350.1395633005972</v>
+        <v>363.6064695813894</v>
       </c>
       <c r="N28">
-        <v>2211.860436699403</v>
+        <v>2198.393530418611</v>
       </c>
       <c r="O28">
-        <v>322.9316237581128</v>
+        <v>320.9654554411171</v>
       </c>
       <c r="P28">
-        <v>1888.92881294129</v>
+        <v>1877.428074977493</v>
       </c>
       <c r="Q28">
-        <v>3605.92881294129</v>
+        <v>3594.428074977493</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1389998596516946</v>
+        <v>0.1401331916200994</v>
       </c>
       <c r="T28">
-        <v>2.152421700962924</v>
+        <v>2.17859564942493</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.317082296696947</v>
+        <v>7.046079248671134</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4147,22 +4147,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1142412738826726</v>
+        <v>0.1141209796230912</v>
       </c>
       <c r="C29">
-        <v>19708.94157851247</v>
+        <v>19490.60618556588</v>
       </c>
       <c r="D29">
-        <v>23651.37149321111</v>
+        <v>23693.01498599409</v>
       </c>
       <c r="E29">
-        <v>3596.04134174072</v>
+        <v>3856.0202274703</v>
       </c>
       <c r="F29">
-        <v>7019.429914698638</v>
+        <v>7279.408800428218</v>
       </c>
       <c r="G29">
         <v>3077</v>
@@ -4183,28 +4183,28 @@
         <v>2562</v>
       </c>
       <c r="M29">
-        <v>363.6064695813894</v>
+        <v>377.0733758621816</v>
       </c>
       <c r="N29">
-        <v>2198.393530418611</v>
+        <v>2184.926624137818</v>
       </c>
       <c r="O29">
-        <v>320.9654554411171</v>
+        <v>318.9992871241215</v>
       </c>
       <c r="P29">
-        <v>1877.428074977493</v>
+        <v>1865.927337013697</v>
       </c>
       <c r="Q29">
-        <v>3594.428074977493</v>
+        <v>3582.927337013697</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1401331916200994</v>
+        <v>0.1412980050320711</v>
       </c>
       <c r="T29">
-        <v>2.17859564942493</v>
+        <v>2.205496652010881</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.046079248671134</v>
+        <v>6.794433561218593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4229,22 +4229,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1141209796230912</v>
+        <v>0.1144217073635098</v>
       </c>
       <c r="C30">
-        <v>19490.60618556588</v>
+        <v>19126.79504129604</v>
       </c>
       <c r="D30">
-        <v>23693.01498599409</v>
+        <v>23589.18272745384</v>
       </c>
       <c r="E30">
-        <v>3856.0202274703</v>
+        <v>4115.99911319988</v>
       </c>
       <c r="F30">
-        <v>7279.408800428218</v>
+        <v>7539.387686157796</v>
       </c>
       <c r="G30">
         <v>3077</v>
@@ -4265,45 +4265,45 @@
         <v>2562</v>
       </c>
       <c r="M30">
-        <v>377.0733758621816</v>
+        <v>403.3572412094421</v>
       </c>
       <c r="N30">
-        <v>2184.926624137818</v>
+        <v>2158.642758790558</v>
       </c>
       <c r="O30">
-        <v>318.9992871241215</v>
+        <v>315.1618427834214</v>
       </c>
       <c r="P30">
-        <v>1865.927337013697</v>
+        <v>1843.480916007136</v>
       </c>
       <c r="Q30">
-        <v>3582.927337013697</v>
+        <v>3560.480916007136</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1412980050320711</v>
+        <v>0.1424956300894504</v>
       </c>
       <c r="T30">
-        <v>2.205496652010881</v>
+        <v>2.233155429317562</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.794433561218593</v>
+        <v>6.351689614689943</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4311,22 +4311,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1144217073635098</v>
+        <v>0.1143159311039284</v>
       </c>
       <c r="C31">
-        <v>19126.79504129604</v>
+        <v>18903.23360586291</v>
       </c>
       <c r="D31">
-        <v>23589.18272745384</v>
+        <v>23625.60017775029</v>
       </c>
       <c r="E31">
-        <v>4115.999113199878</v>
+        <v>4375.977998929457</v>
       </c>
       <c r="F31">
-        <v>7539.387686157796</v>
+        <v>7799.366571887374</v>
       </c>
       <c r="G31">
         <v>3077</v>
@@ -4347,28 +4347,28 @@
         <v>2562</v>
       </c>
       <c r="M31">
-        <v>403.3572412094421</v>
+        <v>417.2661115959745</v>
       </c>
       <c r="N31">
-        <v>2158.642758790558</v>
+        <v>2144.733888404025</v>
       </c>
       <c r="O31">
-        <v>315.1618427834214</v>
+        <v>313.1311477069877</v>
       </c>
       <c r="P31">
-        <v>1843.480916007136</v>
+        <v>1831.602740697038</v>
       </c>
       <c r="Q31">
-        <v>3560.480916007136</v>
+        <v>3548.602740697038</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1424956300894504</v>
+        <v>0.143727473005612</v>
       </c>
       <c r="T31">
-        <v>2.233155429317562</v>
+        <v>2.261604457404434</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.351689614689944</v>
+        <v>6.139966627533614</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4393,22 +4393,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1143159311039284</v>
+        <v>0.114210154844347</v>
       </c>
       <c r="C32">
-        <v>18903.23360586291</v>
+        <v>18679.78478826216</v>
       </c>
       <c r="D32">
-        <v>23625.60017775029</v>
+        <v>23662.13024587912</v>
       </c>
       <c r="E32">
-        <v>4375.977998929457</v>
+        <v>4635.956884659037</v>
       </c>
       <c r="F32">
-        <v>7799.366571887374</v>
+        <v>8059.345457616954</v>
       </c>
       <c r="G32">
         <v>3077</v>
@@ -4429,28 +4429,28 @@
         <v>2562</v>
       </c>
       <c r="M32">
-        <v>417.2661115959745</v>
+        <v>431.1749819825071</v>
       </c>
       <c r="N32">
-        <v>2144.733888404025</v>
+        <v>2130.825018017493</v>
       </c>
       <c r="O32">
-        <v>313.1311477069877</v>
+        <v>311.1004526305539</v>
       </c>
       <c r="P32">
-        <v>1831.602740697038</v>
+        <v>1819.724565386939</v>
       </c>
       <c r="Q32">
-        <v>3548.602740697038</v>
+        <v>3536.724565386939</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.143727473005612</v>
+        <v>0.1449950215135464</v>
       </c>
       <c r="T32">
-        <v>2.261604457404434</v>
+        <v>2.290878095001072</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.139966627533614</v>
+        <v>5.941903187935754</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4475,22 +4475,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.114210154844347</v>
+        <v>0.1141043785847656</v>
       </c>
       <c r="C33">
-        <v>18679.78478826216</v>
+        <v>18456.44911169422</v>
       </c>
       <c r="D33">
-        <v>23662.13024587912</v>
+        <v>23698.77345504075</v>
       </c>
       <c r="E33">
-        <v>4635.956884659037</v>
+        <v>4895.935770388616</v>
       </c>
       <c r="F33">
-        <v>8059.345457616954</v>
+        <v>8319.324343346534</v>
       </c>
       <c r="G33">
         <v>3077</v>
@@ -4511,28 +4511,28 @@
         <v>2562</v>
       </c>
       <c r="M33">
-        <v>431.1749819825071</v>
+        <v>445.0838523690396</v>
       </c>
       <c r="N33">
-        <v>2130.825018017493</v>
+        <v>2116.91614763096</v>
       </c>
       <c r="O33">
-        <v>311.1004526305539</v>
+        <v>309.0697575541202</v>
       </c>
       <c r="P33">
-        <v>1819.724565386939</v>
+        <v>1807.84639007684</v>
       </c>
       <c r="Q33">
-        <v>3536.724565386939</v>
+        <v>3524.84639007684</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1449950215135464</v>
+        <v>0.1462998508599494</v>
       </c>
       <c r="T33">
-        <v>2.290878095001072</v>
+        <v>2.321012721938786</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.941903187935754</v>
+        <v>5.756218713312761</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4557,22 +4557,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1141043785847656</v>
+        <v>0.1142240583251842</v>
       </c>
       <c r="C34">
-        <v>18456.44911169422</v>
+        <v>18155.01897146788</v>
       </c>
       <c r="D34">
-        <v>23698.77345504075</v>
+        <v>23657.32220054399</v>
       </c>
       <c r="E34">
-        <v>4895.935770388616</v>
+        <v>5155.914656118195</v>
       </c>
       <c r="F34">
-        <v>8319.324343346534</v>
+        <v>8579.303229076113</v>
       </c>
       <c r="G34">
         <v>3077</v>
@@ -4593,45 +4593,45 @@
         <v>2562</v>
       </c>
       <c r="M34">
-        <v>445.0838523690396</v>
+        <v>465.856165338833</v>
       </c>
       <c r="N34">
-        <v>2116.91614763096</v>
+        <v>2096.143834661167</v>
       </c>
       <c r="O34">
-        <v>309.0697575541202</v>
+        <v>306.0369998605304</v>
       </c>
       <c r="P34">
-        <v>1807.84639007684</v>
+        <v>1790.106834800637</v>
       </c>
       <c r="Q34">
-        <v>3524.84639007684</v>
+        <v>3507.106834800637</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1462998508599494</v>
+        <v>0.1476436303360958</v>
       </c>
       <c r="T34">
-        <v>2.321012721938786</v>
+        <v>2.352046889979118</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.756218713312761</v>
+        <v>5.499551558229504</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4639,22 +4639,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1142240583251842</v>
+        <v>0.1141251140656028</v>
       </c>
       <c r="C35">
-        <v>18155.01897146788</v>
+        <v>17929.29917569114</v>
       </c>
       <c r="D35">
-        <v>23657.32220054399</v>
+        <v>23691.58129049683</v>
       </c>
       <c r="E35">
-        <v>5155.914656118195</v>
+        <v>5415.893541847774</v>
       </c>
       <c r="F35">
-        <v>8579.303229076113</v>
+        <v>8839.282114805692</v>
       </c>
       <c r="G35">
         <v>3077</v>
@@ -4675,28 +4675,28 @@
         <v>2562</v>
       </c>
       <c r="M35">
-        <v>465.856165338833</v>
+        <v>479.9730188339491</v>
       </c>
       <c r="N35">
-        <v>2096.143834661167</v>
+        <v>2082.026981166051</v>
       </c>
       <c r="O35">
-        <v>306.0369998605304</v>
+        <v>303.9759392502434</v>
       </c>
       <c r="P35">
-        <v>1790.106834800637</v>
+        <v>1778.051041915808</v>
       </c>
       <c r="Q35">
-        <v>3507.106834800637</v>
+        <v>3495.051041915808</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1476436303360958</v>
+        <v>0.1490281304024285</v>
       </c>
       <c r="T35">
-        <v>2.352046889979118</v>
+        <v>2.384021487354007</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.499551558229504</v>
+        <v>5.337800041810989</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4721,22 +4721,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1141251140656028</v>
+        <v>0.1140261698060214</v>
       </c>
       <c r="C36">
-        <v>17929.29917569114</v>
+        <v>17703.67874765845</v>
       </c>
       <c r="D36">
-        <v>23691.58129049683</v>
+        <v>23725.93974819372</v>
       </c>
       <c r="E36">
-        <v>5415.893541847774</v>
+        <v>5675.872427577353</v>
       </c>
       <c r="F36">
-        <v>8839.282114805692</v>
+        <v>9099.261000535271</v>
       </c>
       <c r="G36">
         <v>3077</v>
@@ -4757,28 +4757,28 @@
         <v>2562</v>
       </c>
       <c r="M36">
-        <v>479.9730188339491</v>
+        <v>494.0898723290652</v>
       </c>
       <c r="N36">
-        <v>2082.026981166051</v>
+        <v>2067.910127670935</v>
       </c>
       <c r="O36">
-        <v>303.9759392502434</v>
+        <v>301.9148786399564</v>
       </c>
       <c r="P36">
-        <v>1778.051041915808</v>
+        <v>1765.995249030978</v>
       </c>
       <c r="Q36">
-        <v>3495.051041915808</v>
+        <v>3482.995249030978</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1490281304024285</v>
+        <v>0.1504552304708021</v>
       </c>
       <c r="T36">
-        <v>2.384021487354007</v>
+        <v>2.416979918494276</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.337800041810989</v>
+        <v>5.185291469187818</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4803,22 +4803,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1140261698060214</v>
+        <v>0.11392722554644</v>
       </c>
       <c r="C37">
-        <v>17703.67874765845</v>
+        <v>17478.15812031865</v>
       </c>
       <c r="D37">
-        <v>23725.93974819372</v>
+        <v>23760.39800658351</v>
       </c>
       <c r="E37">
-        <v>5675.872427577353</v>
+        <v>5935.851313306934</v>
       </c>
       <c r="F37">
-        <v>9099.261000535271</v>
+        <v>9359.239886264852</v>
       </c>
       <c r="G37">
         <v>3077</v>
@@ -4839,28 +4839,28 @@
         <v>2562</v>
       </c>
       <c r="M37">
-        <v>494.0898723290652</v>
+        <v>508.2067258241814</v>
       </c>
       <c r="N37">
-        <v>2067.910127670935</v>
+        <v>2053.793274175819</v>
       </c>
       <c r="O37">
-        <v>301.9148786399564</v>
+        <v>299.8538180296695</v>
       </c>
       <c r="P37">
-        <v>1765.995249030978</v>
+        <v>1753.939456146149</v>
       </c>
       <c r="Q37">
-        <v>3482.995249030978</v>
+        <v>3470.939456146149</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1504552304708021</v>
+        <v>0.1519269274163124</v>
       </c>
       <c r="T37">
-        <v>2.416979918494276</v>
+        <v>2.450968300607679</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.185291469187818</v>
+        <v>5.041255595043712</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4885,22 +4885,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.11392722554644</v>
+        <v>0.1138282812868586</v>
       </c>
       <c r="C38">
-        <v>17478.15812031865</v>
+        <v>17252.73772913941</v>
       </c>
       <c r="D38">
-        <v>23760.3980065835</v>
+        <v>23794.95650113383</v>
       </c>
       <c r="E38">
-        <v>5935.851313306932</v>
+        <v>6195.830199036511</v>
       </c>
       <c r="F38">
-        <v>9359.23988626485</v>
+        <v>9619.218771994429</v>
       </c>
       <c r="G38">
         <v>3077</v>
@@ -4921,28 +4921,28 @@
         <v>2562</v>
       </c>
       <c r="M38">
-        <v>508.2067258241814</v>
+        <v>522.3235793192974</v>
       </c>
       <c r="N38">
-        <v>2053.793274175819</v>
+        <v>2039.676420680702</v>
       </c>
       <c r="O38">
-        <v>299.8538180296695</v>
+        <v>297.7927574193826</v>
       </c>
       <c r="P38">
-        <v>1753.939456146149</v>
+        <v>1741.88366326132</v>
       </c>
       <c r="Q38">
-        <v>3470.939456146149</v>
+        <v>3458.88366326132</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1519269274163124</v>
+        <v>0.1534453448997755</v>
       </c>
       <c r="T38">
-        <v>2.450968300607679</v>
+        <v>2.48603567897865</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.041255595043712</v>
+        <v>4.905005443826315</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1138282812868586</v>
+        <v>0.1137293370272772</v>
       </c>
       <c r="C39">
-        <v>17252.73772913941</v>
+        <v>17027.41801212556</v>
       </c>
       <c r="D39">
-        <v>23794.95650113383</v>
+        <v>23829.61566984957</v>
       </c>
       <c r="E39">
-        <v>6195.830199036511</v>
+        <v>6455.80908476609</v>
       </c>
       <c r="F39">
-        <v>9619.218771994429</v>
+        <v>9879.197657724008</v>
       </c>
       <c r="G39">
         <v>3077</v>
@@ -5003,28 +5003,28 @@
         <v>2562</v>
       </c>
       <c r="M39">
-        <v>522.3235793192974</v>
+        <v>536.4404328144136</v>
       </c>
       <c r="N39">
-        <v>2039.676420680702</v>
+        <v>2025.559567185586</v>
       </c>
       <c r="O39">
-        <v>297.7927574193826</v>
+        <v>295.7316968090956</v>
       </c>
       <c r="P39">
-        <v>1741.88366326132</v>
+        <v>1729.827870376491</v>
       </c>
       <c r="Q39">
-        <v>3458.88366326132</v>
+        <v>3446.827870376491</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1534453448997755</v>
+        <v>0.1550127435923825</v>
       </c>
       <c r="T39">
-        <v>2.48603567897865</v>
+        <v>2.522234263103523</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.905005443826315</v>
+        <v>4.775926353199306</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5049,22 +5049,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1137293370272772</v>
+        <v>0.1136303927676958</v>
       </c>
       <c r="C40">
-        <v>17027.41801212556</v>
+        <v>16802.19940983762</v>
       </c>
       <c r="D40">
-        <v>23829.61566984957</v>
+        <v>23864.3759532912</v>
       </c>
       <c r="E40">
-        <v>6455.80908476609</v>
+        <v>6715.78797049567</v>
       </c>
       <c r="F40">
-        <v>9879.197657724008</v>
+        <v>10139.17654345359</v>
       </c>
       <c r="G40">
         <v>3077</v>
@@ -5085,28 +5085,28 @@
         <v>2562</v>
       </c>
       <c r="M40">
-        <v>536.4404328144136</v>
+        <v>550.5572863095299</v>
       </c>
       <c r="N40">
-        <v>2025.559567185586</v>
+        <v>2011.44271369047</v>
       </c>
       <c r="O40">
-        <v>295.7316968090956</v>
+        <v>293.6706361988086</v>
       </c>
       <c r="P40">
-        <v>1729.827870376491</v>
+        <v>1717.772077491662</v>
       </c>
       <c r="Q40">
-        <v>3446.827870376491</v>
+        <v>3434.772077491662</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1550127435923825</v>
+        <v>0.1566315324060586</v>
       </c>
       <c r="T40">
-        <v>2.522234263103523</v>
+        <v>2.559619686052164</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.775926353199306</v>
+        <v>4.653466703117272</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5131,22 +5131,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1136303927676958</v>
+        <v>0.1135314485081144</v>
       </c>
       <c r="C41">
-        <v>16802.19940983762</v>
+        <v>16577.08236541043</v>
       </c>
       <c r="D41">
-        <v>23864.3759532912</v>
+        <v>23899.2377945936</v>
       </c>
       <c r="E41">
-        <v>6715.78797049567</v>
+        <v>6975.766856225249</v>
       </c>
       <c r="F41">
-        <v>10139.17654345359</v>
+        <v>10399.15542918317</v>
       </c>
       <c r="G41">
         <v>3077</v>
@@ -5167,28 +5167,28 @@
         <v>2562</v>
       </c>
       <c r="M41">
-        <v>550.5572863095299</v>
+        <v>564.674139804646</v>
       </c>
       <c r="N41">
-        <v>2011.44271369047</v>
+        <v>1997.325860195354</v>
       </c>
       <c r="O41">
-        <v>293.6706361988086</v>
+        <v>291.6095755885216</v>
       </c>
       <c r="P41">
-        <v>1717.772077491662</v>
+        <v>1705.716284606832</v>
       </c>
       <c r="Q41">
-        <v>3434.772077491662</v>
+        <v>3422.716284606832</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1566315324060586</v>
+        <v>0.1583042808468573</v>
       </c>
       <c r="T41">
-        <v>2.559619686052164</v>
+        <v>2.598251289765758</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.653466703117272</v>
+        <v>4.537130035539341</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5213,22 +5213,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1135314485081144</v>
+        <v>0.113432504248533</v>
       </c>
       <c r="C42">
-        <v>16577.08236541043</v>
+        <v>16352.067324572</v>
       </c>
       <c r="D42">
-        <v>23899.2377945936</v>
+        <v>23934.20163948474</v>
       </c>
       <c r="E42">
-        <v>6975.766856225249</v>
+        <v>7235.745741954828</v>
       </c>
       <c r="F42">
-        <v>10399.15542918317</v>
+        <v>10659.13431491275</v>
       </c>
       <c r="G42">
         <v>3077</v>
@@ -5249,28 +5249,28 @@
         <v>2562</v>
       </c>
       <c r="M42">
-        <v>564.674139804646</v>
+        <v>578.7909932997621</v>
       </c>
       <c r="N42">
-        <v>1997.325860195354</v>
+        <v>1983.209006700238</v>
       </c>
       <c r="O42">
-        <v>291.6095755885216</v>
+        <v>289.5485149782347</v>
       </c>
       <c r="P42">
-        <v>1705.716284606832</v>
+        <v>1693.660491722003</v>
       </c>
       <c r="Q42">
-        <v>3422.716284606832</v>
+        <v>3410.660491722003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1583042808468573</v>
+        <v>0.1600337326246322</v>
       </c>
       <c r="T42">
-        <v>2.598251289765758</v>
+        <v>2.638192439367949</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.537130035539341</v>
+        <v>4.426468327355455</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5295,22 +5295,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.113432504248533</v>
+        <v>0.1133335599889516</v>
       </c>
       <c r="C43">
-        <v>16352.067324572</v>
+        <v>16127.15473566252</v>
       </c>
       <c r="D43">
-        <v>23934.20163948474</v>
+        <v>23969.26793630484</v>
       </c>
       <c r="E43">
-        <v>7235.745741954828</v>
+        <v>7495.724627684407</v>
       </c>
       <c r="F43">
-        <v>10659.13431491275</v>
+        <v>10919.11320064232</v>
       </c>
       <c r="G43">
         <v>3077</v>
@@ -5331,28 +5331,28 @@
         <v>2562</v>
       </c>
       <c r="M43">
-        <v>578.7909932997621</v>
+        <v>592.9078467948783</v>
       </c>
       <c r="N43">
-        <v>1983.209006700238</v>
+        <v>1969.092153205122</v>
       </c>
       <c r="O43">
-        <v>289.5485149782347</v>
+        <v>287.4874543679477</v>
       </c>
       <c r="P43">
-        <v>1693.660491722003</v>
+        <v>1681.604698837174</v>
       </c>
       <c r="Q43">
-        <v>3410.660491722003</v>
+        <v>3398.604698837174</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1600337326246322</v>
+        <v>0.1618228206706062</v>
       </c>
       <c r="T43">
-        <v>2.638192439367949</v>
+        <v>2.679510869990906</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.426468327355455</v>
+        <v>4.321076224323181</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5377,22 +5377,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1133335599889516</v>
+        <v>0.1136018357293702</v>
       </c>
       <c r="C44">
-        <v>16127.15473566252</v>
+        <v>15772.335156702</v>
       </c>
       <c r="D44">
-        <v>23969.26793630484</v>
+        <v>23874.4272430739</v>
       </c>
       <c r="E44">
-        <v>7495.724627684407</v>
+        <v>7755.703513413986</v>
       </c>
       <c r="F44">
-        <v>10919.11320064232</v>
+        <v>11179.0920863719</v>
       </c>
       <c r="G44">
         <v>3077</v>
@@ -5413,45 +5413,45 @@
         <v>2562</v>
       </c>
       <c r="M44">
-        <v>592.9078467948783</v>
+        <v>618.2037923763663</v>
       </c>
       <c r="N44">
-        <v>1969.092153205122</v>
+        <v>1943.796207623634</v>
       </c>
       <c r="O44">
-        <v>287.4874543679477</v>
+        <v>283.7942463130505</v>
       </c>
       <c r="P44">
-        <v>1681.604698837174</v>
+        <v>1660.001961310583</v>
       </c>
       <c r="Q44">
-        <v>3398.604698837174</v>
+        <v>3377.001961310583</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1618228206706062</v>
+        <v>0.1636746837357371</v>
       </c>
       <c r="T44">
-        <v>2.679510869990905</v>
+        <v>2.722279070109404</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.321076224323181</v>
+        <v>4.144264450646136</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5459,22 +5459,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1136018357293702</v>
+        <v>0.1135114314697888</v>
       </c>
       <c r="C45">
-        <v>15772.335156702</v>
+        <v>15544.23198044997</v>
       </c>
       <c r="D45">
-        <v>23874.4272430739</v>
+        <v>23906.30295255145</v>
       </c>
       <c r="E45">
-        <v>7755.703513413986</v>
+        <v>8015.682399143565</v>
       </c>
       <c r="F45">
-        <v>11179.0920863719</v>
+        <v>11439.07097210148</v>
       </c>
       <c r="G45">
         <v>3077</v>
@@ -5495,28 +5495,28 @@
         <v>2562</v>
       </c>
       <c r="M45">
-        <v>618.2037923763663</v>
+        <v>632.580624757212</v>
       </c>
       <c r="N45">
-        <v>1943.796207623634</v>
+        <v>1929.419375242788</v>
       </c>
       <c r="O45">
-        <v>283.7942463130505</v>
+        <v>281.695228785447</v>
       </c>
       <c r="P45">
-        <v>1660.001961310583</v>
+        <v>1647.724146457341</v>
       </c>
       <c r="Q45">
-        <v>3377.001961310583</v>
+        <v>3364.724146457341</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1636746837357371</v>
+        <v>0.1655926847674799</v>
       </c>
       <c r="T45">
-        <v>2.722279070109404</v>
+        <v>2.76657470594642</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.144264450646136</v>
+        <v>4.050076622222361</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5541,22 +5541,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1135114314697888</v>
+        <v>0.1134210272102074</v>
       </c>
       <c r="C46">
-        <v>15544.23198044997</v>
+        <v>15316.21403508048</v>
       </c>
       <c r="D46">
-        <v>23906.30295255145</v>
+        <v>23938.26389291155</v>
       </c>
       <c r="E46">
-        <v>8015.682399143565</v>
+        <v>8275.661284873144</v>
       </c>
       <c r="F46">
-        <v>11439.07097210148</v>
+        <v>11699.04985783106</v>
       </c>
       <c r="G46">
         <v>3077</v>
@@ -5577,28 +5577,28 @@
         <v>2562</v>
       </c>
       <c r="M46">
-        <v>632.580624757212</v>
+        <v>646.9574571380577</v>
       </c>
       <c r="N46">
-        <v>1929.419375242788</v>
+        <v>1915.042542861942</v>
       </c>
       <c r="O46">
-        <v>281.695228785447</v>
+        <v>279.5962112578435</v>
       </c>
       <c r="P46">
-        <v>1647.724146457341</v>
+        <v>1635.446331604099</v>
       </c>
       <c r="Q46">
-        <v>3364.724146457341</v>
+        <v>3352.446331604099</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1655926847674799</v>
+        <v>0.1675804312912861</v>
       </c>
       <c r="T46">
-        <v>2.76657470594642</v>
+        <v>2.81248109217751</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.050076622222361</v>
+        <v>3.960074919506309</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5623,22 +5623,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1134210272102074</v>
+        <v>0.113330622950626</v>
       </c>
       <c r="C47">
-        <v>15316.21403508048</v>
+        <v>15088.28166289314</v>
       </c>
       <c r="D47">
-        <v>23938.26389291155</v>
+        <v>23970.31040645378</v>
       </c>
       <c r="E47">
-        <v>8275.661284873144</v>
+        <v>8535.640170602725</v>
       </c>
       <c r="F47">
-        <v>11699.04985783106</v>
+        <v>11959.02874356064</v>
       </c>
       <c r="G47">
         <v>3077</v>
@@ -5659,28 +5659,28 @@
         <v>2562</v>
       </c>
       <c r="M47">
-        <v>646.9574571380577</v>
+        <v>661.3342895189036</v>
       </c>
       <c r="N47">
-        <v>1915.042542861942</v>
+        <v>1900.665710481097</v>
       </c>
       <c r="O47">
-        <v>279.5962112578435</v>
+        <v>277.4971937302401</v>
       </c>
       <c r="P47">
-        <v>1635.446331604099</v>
+        <v>1623.168516750856</v>
       </c>
       <c r="Q47">
-        <v>3352.446331604099</v>
+        <v>3340.168516750857</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1675804312912861</v>
+        <v>0.1696417980567148</v>
       </c>
       <c r="T47">
-        <v>2.81248109217751</v>
+        <v>2.860087714935676</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.960074919506309</v>
+        <v>3.873986334299649</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5705,22 +5705,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.113330622950626</v>
+        <v>0.1132402186910446</v>
       </c>
       <c r="C48">
-        <v>15088.28166289314</v>
+        <v>14860.43520802295</v>
       </c>
       <c r="D48">
-        <v>23970.31040645378</v>
+        <v>24002.44283731317</v>
       </c>
       <c r="E48">
-        <v>8535.640170602725</v>
+        <v>8795.619056332303</v>
       </c>
       <c r="F48">
-        <v>11959.02874356064</v>
+        <v>12219.00762929022</v>
       </c>
       <c r="G48">
         <v>3077</v>
@@ -5741,28 +5741,28 @@
         <v>2562</v>
       </c>
       <c r="M48">
-        <v>661.3342895189036</v>
+        <v>675.7111218997493</v>
       </c>
       <c r="N48">
-        <v>1900.665710481097</v>
+        <v>1886.288878100251</v>
       </c>
       <c r="O48">
-        <v>277.4971937302401</v>
+        <v>275.3981762026366</v>
       </c>
       <c r="P48">
-        <v>1623.168516750856</v>
+        <v>1610.890701897614</v>
       </c>
       <c r="Q48">
-        <v>3340.168516750857</v>
+        <v>3327.890701897614</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1696417980567148</v>
+        <v>0.1717809522472539</v>
       </c>
       <c r="T48">
-        <v>2.860087714935676</v>
+        <v>2.909490814024341</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.873986334299649</v>
+        <v>3.791561093144337</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5787,22 +5787,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1132402186910446</v>
+        <v>0.1131498144314632</v>
       </c>
       <c r="C49">
-        <v>14860.43520802295</v>
+        <v>14632.67501645266</v>
       </c>
       <c r="D49">
-        <v>24002.44283731317</v>
+        <v>24034.66153147246</v>
       </c>
       <c r="E49">
-        <v>8795.619056332303</v>
+        <v>9055.597942061882</v>
       </c>
       <c r="F49">
-        <v>12219.00762929022</v>
+        <v>12478.9865150198</v>
       </c>
       <c r="G49">
         <v>3077</v>
@@ -5823,28 +5823,28 @@
         <v>2562</v>
       </c>
       <c r="M49">
-        <v>675.7111218997493</v>
+        <v>690.087954280595</v>
       </c>
       <c r="N49">
-        <v>1886.288878100251</v>
+        <v>1871.912045719405</v>
       </c>
       <c r="O49">
-        <v>275.3981762026366</v>
+        <v>273.2991586750331</v>
       </c>
       <c r="P49">
-        <v>1610.890701897614</v>
+        <v>1598.612887044372</v>
       </c>
       <c r="Q49">
-        <v>3327.890701897614</v>
+        <v>3315.612887044372</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1717809522472539</v>
+        <v>0.1740023815989676</v>
       </c>
       <c r="T49">
-        <v>2.909490814024341</v>
+        <v>2.960794032308722</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.791561093144337</v>
+        <v>3.712570237037164</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5869,22 +5869,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1131498144314632</v>
+        <v>0.1130594101718818</v>
       </c>
       <c r="C50">
-        <v>14632.67501645267</v>
+        <v>14405.00143602519</v>
       </c>
       <c r="D50">
-        <v>24034.66153147247</v>
+        <v>24066.96683677457</v>
       </c>
       <c r="E50">
-        <v>9055.597942061881</v>
+        <v>9315.576827791461</v>
       </c>
       <c r="F50">
-        <v>12478.9865150198</v>
+        <v>12738.96540074938</v>
       </c>
       <c r="G50">
         <v>3077</v>
@@ -5905,28 +5905,28 @@
         <v>2562</v>
       </c>
       <c r="M50">
-        <v>690.0879542805949</v>
+        <v>704.4647866614407</v>
       </c>
       <c r="N50">
-        <v>1871.912045719405</v>
+        <v>1857.535213338559</v>
       </c>
       <c r="O50">
-        <v>273.2991586750331</v>
+        <v>271.2001411474296</v>
       </c>
       <c r="P50">
-        <v>1598.612887044372</v>
+        <v>1586.33507219113</v>
       </c>
       <c r="Q50">
-        <v>3315.612887044372</v>
+        <v>3303.33507219113</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1740023815989676</v>
+        <v>0.1763109258272192</v>
       </c>
       <c r="T50">
-        <v>2.960794032308722</v>
+        <v>3.014109141506217</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.712570237037164</v>
+        <v>3.636803497505793</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5951,22 +5951,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1130594101718818</v>
+        <v>0.1129690059123004</v>
       </c>
       <c r="C51">
-        <v>14405.00143602519</v>
+        <v>14177.41481645613</v>
       </c>
       <c r="D51">
-        <v>24066.96683677457</v>
+        <v>24099.35910293509</v>
       </c>
       <c r="E51">
-        <v>9315.576827791461</v>
+        <v>9575.55571352104</v>
       </c>
       <c r="F51">
-        <v>12738.96540074938</v>
+        <v>12998.94428647896</v>
       </c>
       <c r="G51">
         <v>3077</v>
@@ -5987,28 +5987,28 @@
         <v>2562</v>
       </c>
       <c r="M51">
-        <v>704.4647866614407</v>
+        <v>718.8416190422864</v>
       </c>
       <c r="N51">
-        <v>1857.535213338559</v>
+        <v>1843.158380957714</v>
       </c>
       <c r="O51">
-        <v>271.2001411474296</v>
+        <v>269.1011236198262</v>
       </c>
       <c r="P51">
-        <v>1586.33507219113</v>
+        <v>1574.057257337887</v>
       </c>
       <c r="Q51">
-        <v>3303.33507219113</v>
+        <v>3291.057257337888</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1763109258272192</v>
+        <v>0.1787118118246007</v>
       </c>
       <c r="T51">
-        <v>3.014109141506217</v>
+        <v>3.069556855071612</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.636803497505793</v>
+        <v>3.564067427555678</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1129690059123004</v>
+        <v>0.112878601652719</v>
       </c>
       <c r="C52">
-        <v>14177.41481645613</v>
+        <v>13949.91550934637</v>
       </c>
       <c r="D52">
-        <v>24099.35910293509</v>
+        <v>24131.83868155491</v>
       </c>
       <c r="E52">
-        <v>9575.55571352104</v>
+        <v>9835.534599250619</v>
       </c>
       <c r="F52">
-        <v>12998.94428647896</v>
+        <v>13258.92317220854</v>
       </c>
       <c r="G52">
         <v>3077</v>
@@ -6069,28 +6069,28 @@
         <v>2562</v>
       </c>
       <c r="M52">
-        <v>718.8416190422864</v>
+        <v>733.2184514231321</v>
       </c>
       <c r="N52">
-        <v>1843.158380957714</v>
+        <v>1828.781548576868</v>
       </c>
       <c r="O52">
-        <v>269.1011236198262</v>
+        <v>267.0021060922227</v>
       </c>
       <c r="P52">
-        <v>1574.057257337887</v>
+        <v>1561.779442484645</v>
       </c>
       <c r="Q52">
-        <v>3291.057257337888</v>
+        <v>3278.779442484645</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1787118118246007</v>
+        <v>0.1812106931688142</v>
       </c>
       <c r="T52">
-        <v>3.069556855071612</v>
+        <v>3.127267740619267</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.564067427555678</v>
+        <v>3.494183752505566</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6115,22 +6115,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.112878601652719</v>
+        <v>0.1127881973931376</v>
       </c>
       <c r="C53">
-        <v>13949.91550934637</v>
+        <v>13722.50386819482</v>
       </c>
       <c r="D53">
-        <v>24131.83868155491</v>
+        <v>24164.40592613294</v>
       </c>
       <c r="E53">
-        <v>9835.534599250619</v>
+        <v>10095.5134849802</v>
       </c>
       <c r="F53">
-        <v>13258.92317220854</v>
+        <v>13518.90205793812</v>
       </c>
       <c r="G53">
         <v>3077</v>
@@ -6151,28 +6151,28 @@
         <v>2562</v>
       </c>
       <c r="M53">
-        <v>733.2184514231321</v>
+        <v>747.595283803978</v>
       </c>
       <c r="N53">
-        <v>1828.781548576868</v>
+        <v>1814.404716196022</v>
       </c>
       <c r="O53">
-        <v>267.0021060922227</v>
+        <v>264.9030885646192</v>
       </c>
       <c r="P53">
-        <v>1561.779442484645</v>
+        <v>1549.501627631403</v>
       </c>
       <c r="Q53">
-        <v>3278.779442484645</v>
+        <v>3266.501627631403</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1812106931688142</v>
+        <v>0.1838136945690366</v>
       </c>
       <c r="T53">
-        <v>3.127267740619267</v>
+        <v>3.187383246398075</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.494183752505566</v>
+        <v>3.426987911111228</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6197,22 +6197,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1127881973931376</v>
+        <v>0.1126977931335562</v>
       </c>
       <c r="C54">
-        <v>13722.50386819482</v>
+        <v>13495.18024841124</v>
       </c>
       <c r="D54">
-        <v>24164.40592613294</v>
+        <v>24197.06119207894</v>
       </c>
       <c r="E54">
-        <v>10095.5134849802</v>
+        <v>10355.49237070978</v>
       </c>
       <c r="F54">
-        <v>13518.90205793812</v>
+        <v>13778.8809436677</v>
       </c>
       <c r="G54">
         <v>3077</v>
@@ -6233,28 +6233,28 @@
         <v>2562</v>
       </c>
       <c r="M54">
-        <v>747.595283803978</v>
+        <v>761.9721161848237</v>
       </c>
       <c r="N54">
-        <v>1814.404716196022</v>
+        <v>1800.027883815176</v>
       </c>
       <c r="O54">
-        <v>264.9030885646192</v>
+        <v>262.8040710370157</v>
       </c>
       <c r="P54">
-        <v>1549.501627631403</v>
+        <v>1537.22381277816</v>
       </c>
       <c r="Q54">
-        <v>3266.501627631403</v>
+        <v>3254.22381277816</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1838136945690366</v>
+        <v>0.1865274619862897</v>
       </c>
       <c r="T54">
-        <v>3.187383246398075</v>
+        <v>3.250056858805769</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.426987911111228</v>
+        <v>3.362327761844978</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6279,22 +6279,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1126977931335562</v>
+        <v>0.1126073888739748</v>
       </c>
       <c r="C55">
-        <v>13495.18024841124</v>
+        <v>13267.94500732915</v>
       </c>
       <c r="D55">
-        <v>24197.06119207894</v>
+        <v>24229.80483672642</v>
       </c>
       <c r="E55">
-        <v>10355.49237070978</v>
+        <v>10615.47125643936</v>
       </c>
       <c r="F55">
-        <v>13778.8809436677</v>
+        <v>14038.85982939728</v>
       </c>
       <c r="G55">
         <v>3077</v>
@@ -6315,28 +6315,28 @@
         <v>2562</v>
       </c>
       <c r="M55">
-        <v>761.9721161848237</v>
+        <v>776.3489485656694</v>
       </c>
       <c r="N55">
-        <v>1800.027883815176</v>
+        <v>1785.651051434331</v>
       </c>
       <c r="O55">
-        <v>262.8040710370157</v>
+        <v>260.7050535094123</v>
       </c>
       <c r="P55">
-        <v>1537.22381277816</v>
+        <v>1524.945997924918</v>
       </c>
       <c r="Q55">
-        <v>3254.22381277816</v>
+        <v>3241.945997924919</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1865274619862897</v>
+        <v>0.1893592192912495</v>
       </c>
       <c r="T55">
-        <v>3.250056858805769</v>
+        <v>3.315455410883361</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.362327761844978</v>
+        <v>3.300062432921923</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6361,22 +6361,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1126073888739748</v>
+        <v>0.1125169846143934</v>
       </c>
       <c r="C56">
-        <v>13267.94500732915</v>
+        <v>13040.79850421887</v>
       </c>
       <c r="D56">
-        <v>24229.80483672642</v>
+        <v>24262.63721934572</v>
       </c>
       <c r="E56">
-        <v>10615.47125643936</v>
+        <v>10875.45014216894</v>
       </c>
       <c r="F56">
-        <v>14038.85982939728</v>
+        <v>14298.83871512685</v>
       </c>
       <c r="G56">
         <v>3077</v>
@@ -6397,28 +6397,28 @@
         <v>2562</v>
       </c>
       <c r="M56">
-        <v>776.3489485656694</v>
+        <v>790.7257809465151</v>
       </c>
       <c r="N56">
-        <v>1785.651051434331</v>
+        <v>1771.274219053485</v>
       </c>
       <c r="O56">
-        <v>260.7050535094123</v>
+        <v>258.6060359818088</v>
       </c>
       <c r="P56">
-        <v>1524.945997924918</v>
+        <v>1512.668183071676</v>
       </c>
       <c r="Q56">
-        <v>3241.945997924919</v>
+        <v>3229.668183071676</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1893592192912495</v>
+        <v>0.1923168324764297</v>
       </c>
       <c r="T56">
-        <v>3.315455410883361</v>
+        <v>3.383760565275514</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.300062432921923</v>
+        <v>3.240061297777888</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6443,22 +6443,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1125169846143934</v>
+        <v>0.112426580354812</v>
       </c>
       <c r="C57">
-        <v>13040.79850421887</v>
+        <v>12813.74110030069</v>
       </c>
       <c r="D57">
-        <v>24262.63721934572</v>
+        <v>24295.55870115713</v>
       </c>
       <c r="E57">
-        <v>10875.45014216894</v>
+        <v>11135.42902789852</v>
       </c>
       <c r="F57">
-        <v>14298.83871512685</v>
+        <v>14558.81760085644</v>
       </c>
       <c r="G57">
         <v>3077</v>
@@ -6479,28 +6479,28 @@
         <v>2562</v>
       </c>
       <c r="M57">
-        <v>790.7257809465151</v>
+        <v>805.1026133273609</v>
       </c>
       <c r="N57">
-        <v>1771.274219053485</v>
+        <v>1756.897386672639</v>
       </c>
       <c r="O57">
-        <v>258.6060359818088</v>
+        <v>256.5070184542053</v>
       </c>
       <c r="P57">
-        <v>1512.668183071676</v>
+        <v>1500.390368218434</v>
       </c>
       <c r="Q57">
-        <v>3229.668183071676</v>
+        <v>3217.390368218434</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1923168324764297</v>
+        <v>0.1954088826245727</v>
       </c>
       <c r="T57">
-        <v>3.383760565275514</v>
+        <v>3.455170499412765</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.240061297777888</v>
+        <v>3.182203060317569</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6525,22 +6525,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.112426580354812</v>
+        <v>0.1123361760952306</v>
       </c>
       <c r="C58">
-        <v>12813.74110030069</v>
+        <v>12586.7731587581</v>
       </c>
       <c r="D58">
-        <v>24295.55870115713</v>
+        <v>24328.56964534411</v>
       </c>
       <c r="E58">
-        <v>11135.42902789852</v>
+        <v>11395.4079136281</v>
       </c>
       <c r="F58">
-        <v>14558.81760085644</v>
+        <v>14818.79648658601</v>
       </c>
       <c r="G58">
         <v>3077</v>
@@ -6561,28 +6561,28 @@
         <v>2562</v>
       </c>
       <c r="M58">
-        <v>805.1026133273609</v>
+        <v>819.4794457082066</v>
       </c>
       <c r="N58">
-        <v>1756.897386672639</v>
+        <v>1742.520554291793</v>
       </c>
       <c r="O58">
-        <v>256.5070184542053</v>
+        <v>254.4080009266018</v>
       </c>
       <c r="P58">
-        <v>1500.390368218434</v>
+        <v>1488.112553365192</v>
       </c>
       <c r="Q58">
-        <v>3217.390368218434</v>
+        <v>3205.112553365192</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1954088826245727</v>
+        <v>0.1986447490586757</v>
       </c>
       <c r="T58">
-        <v>3.455170499412765</v>
+        <v>3.529901825835468</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.182203060317569</v>
+        <v>3.126374936452348</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6607,22 +6607,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1123361760952306</v>
+        <v>0.1122457718356492</v>
       </c>
       <c r="C59">
-        <v>12586.7731587581</v>
+        <v>12359.89504475109</v>
       </c>
       <c r="D59">
-        <v>24328.56964534411</v>
+        <v>24361.67041706668</v>
       </c>
       <c r="E59">
-        <v>11395.4079136281</v>
+        <v>11655.38679935768</v>
       </c>
       <c r="F59">
-        <v>14818.79648658601</v>
+        <v>15078.77537231559</v>
       </c>
       <c r="G59">
         <v>3077</v>
@@ -6643,28 +6643,28 @@
         <v>2562</v>
       </c>
       <c r="M59">
-        <v>819.4794457082066</v>
+        <v>833.8562780890524</v>
       </c>
       <c r="N59">
-        <v>1742.520554291793</v>
+        <v>1728.143721910948</v>
       </c>
       <c r="O59">
-        <v>254.4080009266018</v>
+        <v>252.3089833989983</v>
       </c>
       <c r="P59">
-        <v>1488.112553365192</v>
+        <v>1475.834738511949</v>
       </c>
       <c r="Q59">
-        <v>3205.112553365192</v>
+        <v>3192.834738511949</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1986447490586757</v>
+        <v>0.2020347043705933</v>
       </c>
       <c r="T59">
-        <v>3.529901825835468</v>
+        <v>3.60819178684973</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.126374936452348</v>
+        <v>3.072471920306618</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6689,22 +6689,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1122457718356492</v>
+        <v>0.1121553675760678</v>
       </c>
       <c r="C60">
-        <v>12359.89504475109</v>
+        <v>12133.10712542972</v>
       </c>
       <c r="D60">
-        <v>24361.67041706668</v>
+        <v>24394.86138347489</v>
       </c>
       <c r="E60">
-        <v>11655.38679935767</v>
+        <v>11915.36568508725</v>
       </c>
       <c r="F60">
-        <v>15078.77537231559</v>
+        <v>15338.75425804517</v>
       </c>
       <c r="G60">
         <v>3077</v>
@@ -6725,28 +6725,28 @@
         <v>2562</v>
       </c>
       <c r="M60">
-        <v>833.8562780890522</v>
+        <v>848.233110469898</v>
       </c>
       <c r="N60">
-        <v>1728.143721910948</v>
+        <v>1713.766889530102</v>
       </c>
       <c r="O60">
-        <v>252.3089833989984</v>
+        <v>250.2099658713949</v>
       </c>
       <c r="P60">
-        <v>1475.834738511949</v>
+        <v>1463.556923658707</v>
       </c>
       <c r="Q60">
-        <v>3192.83473851195</v>
+        <v>3180.556923658707</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2020347043705932</v>
+        <v>0.2055900233562628</v>
       </c>
       <c r="T60">
-        <v>3.608191786849729</v>
+        <v>3.690300770352491</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.072471920306619</v>
+        <v>3.020396125047184</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6771,22 +6771,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1121553675760678</v>
+        <v>0.1133459633164864</v>
       </c>
       <c r="C61">
-        <v>12133.10712542972</v>
+        <v>11443.13336472619</v>
       </c>
       <c r="D61">
-        <v>24394.86138347489</v>
+        <v>23964.86650850094</v>
       </c>
       <c r="E61">
-        <v>11915.36568508725</v>
+        <v>12175.34457081683</v>
       </c>
       <c r="F61">
-        <v>15338.75425804517</v>
+        <v>15598.73314377475</v>
       </c>
       <c r="G61">
         <v>3077</v>
@@ -6807,45 +6807,45 @@
         <v>2562</v>
       </c>
       <c r="M61">
-        <v>848.233110469898</v>
+        <v>901.6067757101805</v>
       </c>
       <c r="N61">
-        <v>1713.766889530102</v>
+        <v>1660.393224289819</v>
       </c>
       <c r="O61">
-        <v>250.2099658713949</v>
+        <v>242.4174107463136</v>
       </c>
       <c r="P61">
-        <v>1463.556923658707</v>
+        <v>1417.975813543506</v>
       </c>
       <c r="Q61">
-        <v>3180.556923658707</v>
+        <v>3134.975813543506</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2055900233562628</v>
+        <v>0.2093231082912159</v>
       </c>
       <c r="T61">
-        <v>3.690300770352491</v>
+        <v>3.776515203030391</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.146</v>
       </c>
       <c r="W61">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.020396125047184</v>
+        <v>2.841593551669968</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6853,22 +6853,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1133459633164864</v>
+        <v>0.113276909056905</v>
       </c>
       <c r="C62">
-        <v>11443.13336472619</v>
+        <v>11207.67955188214</v>
       </c>
       <c r="D62">
-        <v>23964.86650850094</v>
+        <v>23989.39158138647</v>
       </c>
       <c r="E62">
-        <v>12175.34457081683</v>
+        <v>12435.32345654641</v>
       </c>
       <c r="F62">
-        <v>15598.73314377475</v>
+        <v>15858.71202950433</v>
       </c>
       <c r="G62">
         <v>3077</v>
@@ -6889,28 +6889,28 @@
         <v>2562</v>
       </c>
       <c r="M62">
-        <v>901.6067757101805</v>
+        <v>916.6335553053502</v>
       </c>
       <c r="N62">
-        <v>1660.393224289819</v>
+        <v>1645.36644469465</v>
       </c>
       <c r="O62">
-        <v>242.4174107463136</v>
+        <v>240.2235009254188</v>
       </c>
       <c r="P62">
-        <v>1417.975813543506</v>
+        <v>1405.142943769231</v>
       </c>
       <c r="Q62">
-        <v>3134.975813543506</v>
+        <v>3122.142943769231</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2093231082912159</v>
+        <v>0.2132476334792435</v>
       </c>
       <c r="T62">
-        <v>3.776515203030391</v>
+        <v>3.867150888666133</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.841593551669968</v>
+        <v>2.795010050822919</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6935,22 +6935,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.113276909056905</v>
+        <v>0.1132078547973236</v>
       </c>
       <c r="C63">
-        <v>11207.67955188214</v>
+        <v>10972.27598721035</v>
       </c>
       <c r="D63">
-        <v>23989.39158138647</v>
+        <v>24013.96690244426</v>
       </c>
       <c r="E63">
-        <v>12435.32345654641</v>
+        <v>12695.30234227599</v>
       </c>
       <c r="F63">
-        <v>15858.71202950433</v>
+        <v>16118.69091523391</v>
       </c>
       <c r="G63">
         <v>3077</v>
@@ -6971,28 +6971,28 @@
         <v>2562</v>
       </c>
       <c r="M63">
-        <v>916.6335553053502</v>
+        <v>931.66033490052</v>
       </c>
       <c r="N63">
-        <v>1645.36644469465</v>
+        <v>1630.33966509948</v>
       </c>
       <c r="O63">
-        <v>240.2235009254188</v>
+        <v>238.0295911045241</v>
       </c>
       <c r="P63">
-        <v>1405.142943769231</v>
+        <v>1392.310073994956</v>
       </c>
       <c r="Q63">
-        <v>3122.142943769231</v>
+        <v>3109.310073994956</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2132476334792435</v>
+        <v>0.2173787126245357</v>
       </c>
       <c r="T63">
-        <v>3.867150888666133</v>
+        <v>3.96255687354586</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.795010050822919</v>
+        <v>2.749929243551581</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7017,22 +7017,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1132078547973236</v>
+        <v>0.1131388005377421</v>
       </c>
       <c r="C64">
-        <v>10972.27598721035</v>
+        <v>10736.92282529555</v>
       </c>
       <c r="D64">
-        <v>24013.96690244426</v>
+        <v>24038.59262625904</v>
       </c>
       <c r="E64">
-        <v>12695.30234227599</v>
+        <v>12955.28122800557</v>
       </c>
       <c r="F64">
-        <v>16118.69091523391</v>
+        <v>16378.66980096349</v>
       </c>
       <c r="G64">
         <v>3077</v>
@@ -7053,28 +7053,28 @@
         <v>2562</v>
       </c>
       <c r="M64">
-        <v>931.66033490052</v>
+        <v>946.6871144956897</v>
       </c>
       <c r="N64">
-        <v>1630.33966509948</v>
+        <v>1615.31288550431</v>
       </c>
       <c r="O64">
-        <v>238.0295911045241</v>
+        <v>235.8356812836293</v>
       </c>
       <c r="P64">
-        <v>1392.310073994956</v>
+        <v>1379.477204220681</v>
       </c>
       <c r="Q64">
-        <v>3109.310073994956</v>
+        <v>3096.477204220681</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2173787126245357</v>
+        <v>0.221733093345249</v>
       </c>
       <c r="T64">
-        <v>3.96255687354586</v>
+        <v>4.063119938689356</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.749929243551581</v>
+        <v>2.706279573019017</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7099,22 +7099,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1131388005377421</v>
+        <v>0.1130697462781608</v>
       </c>
       <c r="C65">
-        <v>10736.92282529555</v>
+        <v>10501.62022135721</v>
       </c>
       <c r="D65">
-        <v>24038.59262625904</v>
+        <v>24063.26890805028</v>
       </c>
       <c r="E65">
-        <v>12955.28122800557</v>
+        <v>13215.26011373515</v>
       </c>
       <c r="F65">
-        <v>16378.66980096349</v>
+        <v>16638.64868669307</v>
       </c>
       <c r="G65">
         <v>3077</v>
@@ -7135,28 +7135,28 @@
         <v>2562</v>
       </c>
       <c r="M65">
-        <v>946.6871144956897</v>
+        <v>961.7138940908594</v>
       </c>
       <c r="N65">
-        <v>1615.31288550431</v>
+        <v>1600.286105909141</v>
       </c>
       <c r="O65">
-        <v>235.8356812836293</v>
+        <v>233.6417714627345</v>
       </c>
       <c r="P65">
-        <v>1379.477204220681</v>
+        <v>1366.644334446406</v>
       </c>
       <c r="Q65">
-        <v>3096.477204220681</v>
+        <v>3083.644334446406</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.221733093345249</v>
+        <v>0.2263293841060021</v>
       </c>
       <c r="T65">
-        <v>4.063119938689356</v>
+        <v>4.16926984078527</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.706279573019017</v>
+        <v>2.663993954690595</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7181,22 +7181,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1130697462781608</v>
+        <v>0.1130006920185794</v>
       </c>
       <c r="C66">
-        <v>10501.62022135721</v>
+        <v>10266.36833125282</v>
       </c>
       <c r="D66">
-        <v>24063.26890805028</v>
+        <v>24087.99590367547</v>
       </c>
       <c r="E66">
-        <v>13215.26011373515</v>
+        <v>13475.23899946473</v>
       </c>
       <c r="F66">
-        <v>16638.64868669307</v>
+        <v>16898.62757242265</v>
       </c>
       <c r="G66">
         <v>3077</v>
@@ -7217,28 +7217,28 @@
         <v>2562</v>
       </c>
       <c r="M66">
-        <v>961.7138940908594</v>
+        <v>976.740673686029</v>
       </c>
       <c r="N66">
-        <v>1600.286105909141</v>
+        <v>1585.259326313971</v>
       </c>
       <c r="O66">
-        <v>233.6417714627345</v>
+        <v>231.4478616418398</v>
       </c>
       <c r="P66">
-        <v>1366.644334446406</v>
+        <v>1353.811464672131</v>
       </c>
       <c r="Q66">
-        <v>3083.644334446406</v>
+        <v>3070.811464672131</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2263293841060021</v>
+        <v>0.2311883200530839</v>
       </c>
       <c r="T66">
-        <v>4.16926984078527</v>
+        <v>4.281485451572378</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.663993954690595</v>
+        <v>2.623009432310739</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7263,22 +7263,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1130006920185794</v>
+        <v>0.1129316377589979</v>
       </c>
       <c r="C67">
-        <v>10266.36833125282</v>
+        <v>10031.16731148117</v>
       </c>
       <c r="D67">
-        <v>24087.99590367547</v>
+        <v>24112.7737696334</v>
       </c>
       <c r="E67">
-        <v>13475.23899946473</v>
+        <v>13735.21788519431</v>
       </c>
       <c r="F67">
-        <v>16898.62757242265</v>
+        <v>17158.60645815223</v>
       </c>
       <c r="G67">
         <v>3077</v>
@@ -7299,28 +7299,28 @@
         <v>2562</v>
       </c>
       <c r="M67">
-        <v>976.740673686029</v>
+        <v>991.7674532811988</v>
       </c>
       <c r="N67">
-        <v>1585.259326313971</v>
+        <v>1570.232546718801</v>
       </c>
       <c r="O67">
-        <v>231.4478616418398</v>
+        <v>229.253951820945</v>
       </c>
       <c r="P67">
-        <v>1353.811464672131</v>
+        <v>1340.978594897856</v>
       </c>
       <c r="Q67">
-        <v>3070.811464672131</v>
+        <v>3057.978594897856</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2311883200530839</v>
+        <v>0.2363330757617587</v>
       </c>
       <c r="T67">
-        <v>4.281485451572378</v>
+        <v>4.400301980641079</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.623009432310739</v>
+        <v>2.583266865154516</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7345,22 +7345,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1129316377589979</v>
+        <v>0.1128625834994166</v>
       </c>
       <c r="C68">
-        <v>10031.16731148117</v>
+        <v>9796.01731918559</v>
       </c>
       <c r="D68">
-        <v>24112.7737696334</v>
+        <v>24137.6026630674</v>
       </c>
       <c r="E68">
-        <v>13735.21788519431</v>
+        <v>13995.19677092389</v>
       </c>
       <c r="F68">
-        <v>17158.60645815223</v>
+        <v>17418.5853438818</v>
       </c>
       <c r="G68">
         <v>3077</v>
@@ -7381,28 +7381,28 @@
         <v>2562</v>
       </c>
       <c r="M68">
-        <v>991.7674532811988</v>
+        <v>1006.794232876368</v>
       </c>
       <c r="N68">
-        <v>1570.232546718801</v>
+        <v>1555.205767123632</v>
       </c>
       <c r="O68">
-        <v>229.253951820945</v>
+        <v>227.0600420000502</v>
       </c>
       <c r="P68">
-        <v>1340.978594897856</v>
+        <v>1328.145725123582</v>
       </c>
       <c r="Q68">
-        <v>3057.978594897856</v>
+        <v>3045.145725123582</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2363330757617587</v>
+        <v>0.2417896348467168</v>
       </c>
       <c r="T68">
-        <v>4.400301980641079</v>
+        <v>4.526319511471522</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.583266865154516</v>
+        <v>2.544710643286538</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7427,22 +7427,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1128625834994166</v>
+        <v>0.1127935292398351</v>
       </c>
       <c r="C69">
-        <v>9796.01731918559</v>
+        <v>9560.918512157365</v>
       </c>
       <c r="D69">
-        <v>24137.6026630674</v>
+        <v>24162.48274176875</v>
       </c>
       <c r="E69">
-        <v>13995.19677092389</v>
+        <v>14255.17565665347</v>
       </c>
       <c r="F69">
-        <v>17418.5853438818</v>
+        <v>17678.56422961138</v>
       </c>
       <c r="G69">
         <v>3077</v>
@@ -7463,28 +7463,28 @@
         <v>2562</v>
       </c>
       <c r="M69">
-        <v>1006.794232876368</v>
+        <v>1021.821012471538</v>
       </c>
       <c r="N69">
-        <v>1555.205767123632</v>
+        <v>1540.178987528462</v>
       </c>
       <c r="O69">
-        <v>227.0600420000502</v>
+        <v>224.8661321791554</v>
       </c>
       <c r="P69">
-        <v>1328.145725123582</v>
+        <v>1315.312855349307</v>
       </c>
       <c r="Q69">
-        <v>3045.145725123582</v>
+        <v>3032.312855349307</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2417896348467168</v>
+        <v>0.2475872288744848</v>
       </c>
       <c r="T69">
-        <v>4.526319511471522</v>
+        <v>4.660213137978866</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.544710643286538</v>
+        <v>2.507288427944089</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7509,22 +7509,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1127935292398351</v>
+        <v>0.1147868849802537</v>
       </c>
       <c r="C70">
-        <v>9560.918512157365</v>
+        <v>8602.771798008569</v>
       </c>
       <c r="D70">
-        <v>24162.48274176875</v>
+        <v>23464.31491334953</v>
       </c>
       <c r="E70">
-        <v>14255.17565665347</v>
+        <v>14515.15454238304</v>
       </c>
       <c r="F70">
-        <v>17678.56422961138</v>
+        <v>17938.54311534096</v>
       </c>
       <c r="G70">
         <v>3077</v>
@@ -7545,45 +7545,45 @@
         <v>2562</v>
       </c>
       <c r="M70">
-        <v>1021.821012471538</v>
+        <v>1099.632692970401</v>
       </c>
       <c r="N70">
-        <v>1540.178987528462</v>
+        <v>1462.367307029599</v>
       </c>
       <c r="O70">
-        <v>224.8661321791554</v>
+        <v>213.5056268263214</v>
       </c>
       <c r="P70">
-        <v>1315.312855349307</v>
+        <v>1248.861680203278</v>
       </c>
       <c r="Q70">
-        <v>3032.312855349307</v>
+        <v>2965.861680203278</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2475872288744848</v>
+        <v>0.2537588612266251</v>
       </c>
       <c r="T70">
-        <v>4.660213137978866</v>
+        <v>4.802745062970557</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.146</v>
       </c>
       <c r="W70">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.507288427944089</v>
+        <v>2.329868888382497</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7591,22 +7591,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1147868849802537</v>
+        <v>0.1147477207206723</v>
       </c>
       <c r="C71">
-        <v>8602.771798008569</v>
+        <v>8356.121308207974</v>
       </c>
       <c r="D71">
-        <v>23464.31491334953</v>
+        <v>23477.64330927852</v>
       </c>
       <c r="E71">
-        <v>14515.15454238304</v>
+        <v>14775.13342811262</v>
       </c>
       <c r="F71">
-        <v>17938.54311534096</v>
+        <v>18198.52200107054</v>
       </c>
       <c r="G71">
         <v>3077</v>
@@ -7627,28 +7627,28 @@
         <v>2562</v>
       </c>
       <c r="M71">
-        <v>1099.632692970401</v>
+        <v>1115.569398665624</v>
       </c>
       <c r="N71">
-        <v>1462.367307029599</v>
+        <v>1446.430601334376</v>
       </c>
       <c r="O71">
-        <v>213.5056268263214</v>
+        <v>211.1788677948188</v>
       </c>
       <c r="P71">
-        <v>1248.861680203278</v>
+        <v>1235.251733539557</v>
       </c>
       <c r="Q71">
-        <v>2965.861680203278</v>
+        <v>2952.251733539557</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2537588612266251</v>
+        <v>0.2603419357355745</v>
       </c>
       <c r="T71">
-        <v>4.802745062970557</v>
+        <v>4.954779116295025</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.329868888382497</v>
+        <v>2.29658504711989</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7673,22 +7673,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1147477207206723</v>
+        <v>0.1147085564610909</v>
       </c>
       <c r="C72">
-        <v>8356.121308207974</v>
+        <v>8109.485968826561</v>
       </c>
       <c r="D72">
-        <v>23477.64330927852</v>
+        <v>23490.98685562668</v>
       </c>
       <c r="E72">
-        <v>14775.13342811262</v>
+        <v>15035.11231384221</v>
       </c>
       <c r="F72">
-        <v>18198.52200107054</v>
+        <v>18458.50088680012</v>
       </c>
       <c r="G72">
         <v>3077</v>
@@ -7709,28 +7709,28 @@
         <v>2562</v>
       </c>
       <c r="M72">
-        <v>1115.569398665624</v>
+        <v>1131.506104360848</v>
       </c>
       <c r="N72">
-        <v>1446.430601334376</v>
+        <v>1430.493895639152</v>
       </c>
       <c r="O72">
-        <v>211.1788677948188</v>
+        <v>208.8521087633162</v>
       </c>
       <c r="P72">
-        <v>1235.251733539557</v>
+        <v>1221.641786875836</v>
       </c>
       <c r="Q72">
-        <v>2952.251733539557</v>
+        <v>2938.641786875836</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2603419357355745</v>
+        <v>0.2673790153830723</v>
       </c>
       <c r="T72">
-        <v>4.954779116295025</v>
+        <v>5.117298276745321</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.29658504711989</v>
+        <v>2.264238778850595</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7755,22 +7755,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.114708556461091</v>
+        <v>0.1163910562015096</v>
       </c>
       <c r="C73">
-        <v>8109.485968826561</v>
+        <v>7289.61208487023</v>
       </c>
       <c r="D73">
-        <v>23490.98685562668</v>
+        <v>22931.09185739993</v>
       </c>
       <c r="E73">
-        <v>15035.1123138422</v>
+        <v>15295.09119957178</v>
       </c>
       <c r="F73">
-        <v>18458.50088680012</v>
+        <v>18718.4797725297</v>
       </c>
       <c r="G73">
         <v>3077</v>
@@ -7791,45 +7791,45 @@
         <v>2562</v>
       </c>
       <c r="M73">
-        <v>1131.506104360847</v>
+        <v>1199.854553419154</v>
       </c>
       <c r="N73">
-        <v>1430.493895639153</v>
+        <v>1362.145446580846</v>
       </c>
       <c r="O73">
-        <v>208.8521087633163</v>
+        <v>198.8732352008035</v>
       </c>
       <c r="P73">
-        <v>1221.641786875836</v>
+        <v>1163.272211380043</v>
       </c>
       <c r="Q73">
-        <v>2938.641786875836</v>
+        <v>2880.272211380043</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2673790153830722</v>
+        <v>0.2749187435768198</v>
       </c>
       <c r="T73">
-        <v>5.117298276745319</v>
+        <v>5.291425948656348</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.146</v>
       </c>
       <c r="W73">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.264238778850596</v>
+        <v>2.135258805077017</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7837,22 +7837,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1163910562015096</v>
+        <v>0.1163758039419281</v>
       </c>
       <c r="C74">
-        <v>7289.61208487023</v>
+        <v>7034.588877233698</v>
       </c>
       <c r="D74">
-        <v>22931.09185739993</v>
+        <v>22936.04753549298</v>
       </c>
       <c r="E74">
-        <v>15295.09119957178</v>
+        <v>15555.07008530136</v>
       </c>
       <c r="F74">
-        <v>18718.4797725297</v>
+        <v>18978.45865825928</v>
       </c>
       <c r="G74">
         <v>3077</v>
@@ -7873,28 +7873,28 @@
         <v>2562</v>
       </c>
       <c r="M74">
-        <v>1199.854553419154</v>
+        <v>1216.51919999442</v>
       </c>
       <c r="N74">
-        <v>1362.145446580846</v>
+        <v>1345.48080000558</v>
       </c>
       <c r="O74">
-        <v>198.8732352008035</v>
+        <v>196.4401968008147</v>
       </c>
       <c r="P74">
-        <v>1163.272211380043</v>
+        <v>1149.040603204766</v>
       </c>
       <c r="Q74">
-        <v>2880.272211380043</v>
+        <v>2866.040603204766</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2749187435768198</v>
+        <v>0.2830169701552894</v>
       </c>
       <c r="T74">
-        <v>5.291425948656348</v>
+        <v>5.478451966634861</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.135258805077017</v>
+        <v>2.106008684459524</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7919,22 +7919,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1163758039419281</v>
+        <v>0.1163605516823467</v>
       </c>
       <c r="C75">
-        <v>7034.588877233698</v>
+        <v>6779.567812020574</v>
       </c>
       <c r="D75">
-        <v>22936.04753549298</v>
+        <v>22941.00535600943</v>
       </c>
       <c r="E75">
-        <v>15555.07008530136</v>
+        <v>15815.04897103094</v>
       </c>
       <c r="F75">
-        <v>18978.45865825928</v>
+        <v>19238.43754398886</v>
       </c>
       <c r="G75">
         <v>3077</v>
@@ -7955,28 +7955,28 @@
         <v>2562</v>
       </c>
       <c r="M75">
-        <v>1216.51919999442</v>
+        <v>1233.183846569686</v>
       </c>
       <c r="N75">
-        <v>1345.48080000558</v>
+        <v>1328.816153430314</v>
       </c>
       <c r="O75">
-        <v>196.4401968008147</v>
+        <v>194.0071584008259</v>
       </c>
       <c r="P75">
-        <v>1149.040603204766</v>
+        <v>1134.808995029488</v>
       </c>
       <c r="Q75">
-        <v>2866.040603204766</v>
+        <v>2851.808995029488</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2830169701552894</v>
+        <v>0.2917381372397951</v>
       </c>
       <c r="T75">
-        <v>5.478451966634861</v>
+        <v>5.679864601380952</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.106008684459524</v>
+        <v>2.077549107642503</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8001,22 +8001,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1163605516823467</v>
+        <v>0.1163452994227653</v>
       </c>
       <c r="C76">
-        <v>6779.567812020574</v>
+        <v>6524.548890620459</v>
       </c>
       <c r="D76">
-        <v>22941.00535600943</v>
+        <v>22945.9653203389</v>
       </c>
       <c r="E76">
-        <v>15815.04897103094</v>
+        <v>16075.02785676052</v>
       </c>
       <c r="F76">
-        <v>19238.43754398886</v>
+        <v>19498.41642971844</v>
       </c>
       <c r="G76">
         <v>3077</v>
@@ -8037,28 +8037,28 @@
         <v>2562</v>
       </c>
       <c r="M76">
-        <v>1233.183846569686</v>
+        <v>1249.848493144952</v>
       </c>
       <c r="N76">
-        <v>1328.816153430314</v>
+        <v>1312.151506855048</v>
       </c>
       <c r="O76">
-        <v>194.0071584008259</v>
+        <v>191.574120000837</v>
       </c>
       <c r="P76">
-        <v>1134.808995029488</v>
+        <v>1120.577386854211</v>
       </c>
       <c r="Q76">
-        <v>2851.808995029488</v>
+        <v>2837.577386854211</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2917381372397951</v>
+        <v>0.3011569976910614</v>
       </c>
       <c r="T76">
-        <v>5.679864601380952</v>
+        <v>5.897390246906731</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.077549107642503</v>
+        <v>2.049848452873936</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8083,22 +8083,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1163452994227653</v>
+        <v>0.1163300471631839</v>
       </c>
       <c r="C77">
-        <v>6524.548890620459</v>
+        <v>6269.532114424164</v>
       </c>
       <c r="D77">
-        <v>22945.9653203389</v>
+        <v>22950.92742987218</v>
       </c>
       <c r="E77">
-        <v>16075.02785676052</v>
+        <v>16335.0067424901</v>
       </c>
       <c r="F77">
-        <v>19498.41642971844</v>
+        <v>19758.39531544802</v>
       </c>
       <c r="G77">
         <v>3077</v>
@@ -8119,28 +8119,28 @@
         <v>2562</v>
       </c>
       <c r="M77">
-        <v>1249.848493144952</v>
+        <v>1266.513139720218</v>
       </c>
       <c r="N77">
-        <v>1312.151506855048</v>
+        <v>1295.486860279782</v>
       </c>
       <c r="O77">
-        <v>191.574120000837</v>
+        <v>189.1410816008482</v>
       </c>
       <c r="P77">
-        <v>1120.577386854211</v>
+        <v>1106.345778678934</v>
       </c>
       <c r="Q77">
-        <v>2837.577386854211</v>
+        <v>2823.345778678934</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3011569976910614</v>
+        <v>0.3113607631799331</v>
       </c>
       <c r="T77">
-        <v>5.897390246906731</v>
+        <v>6.133043029559659</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.049848452873936</v>
+        <v>2.022876762704542</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8165,22 +8165,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1163300471631839</v>
+        <v>0.1214439189036025</v>
       </c>
       <c r="C78">
-        <v>6269.532114424164</v>
+        <v>4457.966519529095</v>
       </c>
       <c r="D78">
-        <v>22950.92742987218</v>
+        <v>21399.34072070669</v>
       </c>
       <c r="E78">
-        <v>16335.0067424901</v>
+        <v>16594.98562821968</v>
       </c>
       <c r="F78">
-        <v>19758.39531544802</v>
+        <v>20018.3742011776</v>
       </c>
       <c r="G78">
         <v>3077</v>
@@ -8201,45 +8201,45 @@
         <v>2562</v>
       </c>
       <c r="M78">
-        <v>1266.513139720218</v>
+        <v>1439.321105064669</v>
       </c>
       <c r="N78">
-        <v>1295.486860279782</v>
+        <v>1122.678894935331</v>
       </c>
       <c r="O78">
-        <v>189.1410816008482</v>
+        <v>163.9111186605583</v>
       </c>
       <c r="P78">
-        <v>1106.345778678934</v>
+        <v>958.7677762747724</v>
       </c>
       <c r="Q78">
-        <v>2823.345778678934</v>
+        <v>2675.767776274773</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3113607631799331</v>
+        <v>0.3224518126243589</v>
       </c>
       <c r="T78">
-        <v>6.133043029559659</v>
+        <v>6.389187358530231</v>
       </c>
       <c r="U78">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.146</v>
       </c>
       <c r="W78">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.022876762704542</v>
+        <v>1.78000585900176</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8247,22 +8247,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1214439189036025</v>
+        <v>0.1214952786440211</v>
       </c>
       <c r="C79">
-        <v>4457.966519529095</v>
+        <v>4183.468041504824</v>
       </c>
       <c r="D79">
-        <v>21399.34072070669</v>
+        <v>21384.821128412</v>
       </c>
       <c r="E79">
-        <v>16594.98562821968</v>
+        <v>16854.96451394926</v>
       </c>
       <c r="F79">
-        <v>20018.3742011776</v>
+        <v>20278.35308690718</v>
       </c>
       <c r="G79">
         <v>3077</v>
@@ -8283,28 +8283,28 @@
         <v>2562</v>
       </c>
       <c r="M79">
-        <v>1439.321105064669</v>
+        <v>1458.013586948626</v>
       </c>
       <c r="N79">
-        <v>1122.678894935331</v>
+        <v>1103.986413051374</v>
       </c>
       <c r="O79">
-        <v>163.9111186605583</v>
+        <v>161.1820163055006</v>
       </c>
       <c r="P79">
-        <v>958.7677762747724</v>
+        <v>942.8043967458732</v>
       </c>
       <c r="Q79">
-        <v>2675.767776274773</v>
+        <v>2659.804396745873</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3224518126243589</v>
+        <v>0.3345511392910052</v>
       </c>
       <c r="T79">
-        <v>6.389187358530231</v>
+        <v>6.668617535589036</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.78000585900176</v>
+        <v>1.75718527106584</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8329,22 +8329,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1214952786440211</v>
+        <v>0.1241778123844397</v>
       </c>
       <c r="C80">
-        <v>4183.468041504824</v>
+        <v>3191.579161548732</v>
       </c>
       <c r="D80">
-        <v>21384.821128412</v>
+        <v>20652.91113418549</v>
       </c>
       <c r="E80">
-        <v>16854.96451394926</v>
+        <v>17114.94339967884</v>
       </c>
       <c r="F80">
-        <v>20278.35308690718</v>
+        <v>20538.33197263676</v>
       </c>
       <c r="G80">
         <v>3077</v>
@@ -8365,45 +8365,45 @@
         <v>2562</v>
       </c>
       <c r="M80">
-        <v>1458.013586948626</v>
+        <v>1556.805563525866</v>
       </c>
       <c r="N80">
-        <v>1103.986413051374</v>
+        <v>1005.194436474134</v>
       </c>
       <c r="O80">
-        <v>161.1820163055006</v>
+        <v>146.7583877252235</v>
       </c>
       <c r="P80">
-        <v>942.8043967458732</v>
+        <v>858.4360487489104</v>
       </c>
       <c r="Q80">
-        <v>2659.804396745873</v>
+        <v>2575.43604874891</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3345511392910052</v>
+        <v>0.3478027827830464</v>
       </c>
       <c r="T80">
-        <v>6.668617535589036</v>
+        <v>6.974660110462969</v>
       </c>
       <c r="U80">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.146</v>
       </c>
       <c r="W80">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.75718527106584</v>
+        <v>1.645677572090352</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8411,22 +8411,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1241778123844397</v>
+        <v>0.1242624781248583</v>
       </c>
       <c r="C81">
-        <v>3191.579161548732</v>
+        <v>2909.314540589217</v>
       </c>
       <c r="D81">
-        <v>20652.91113418549</v>
+        <v>20630.62539895555</v>
       </c>
       <c r="E81">
-        <v>17114.94339967884</v>
+        <v>17374.92228540842</v>
       </c>
       <c r="F81">
-        <v>20538.33197263676</v>
+        <v>20798.31085836633</v>
       </c>
       <c r="G81">
         <v>3077</v>
@@ -8447,28 +8447,28 @@
         <v>2562</v>
       </c>
       <c r="M81">
-        <v>1556.805563525866</v>
+        <v>1576.511963064168</v>
       </c>
       <c r="N81">
-        <v>1005.194436474134</v>
+        <v>985.4880369358318</v>
       </c>
       <c r="O81">
-        <v>146.7583877252235</v>
+        <v>143.8812533926314</v>
       </c>
       <c r="P81">
-        <v>858.4360487489104</v>
+        <v>841.6067835432004</v>
       </c>
       <c r="Q81">
-        <v>2575.43604874891</v>
+        <v>2558.6067835432</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3478027827830464</v>
+        <v>0.3623795906242917</v>
       </c>
       <c r="T81">
-        <v>6.974660110462969</v>
+        <v>7.311306942824292</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.645677572090352</v>
+        <v>1.625106602439223</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8493,22 +8493,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1242624781248583</v>
+        <v>0.124347143865277</v>
       </c>
       <c r="C82">
-        <v>2909.314540589217</v>
+        <v>2627.097963089487</v>
       </c>
       <c r="D82">
-        <v>20630.62539895555</v>
+        <v>20608.3877071854</v>
       </c>
       <c r="E82">
-        <v>17374.92228540842</v>
+        <v>17634.901171138</v>
       </c>
       <c r="F82">
-        <v>20798.31085836633</v>
+        <v>21058.28974409591</v>
       </c>
       <c r="G82">
         <v>3077</v>
@@ -8529,28 +8529,28 @@
         <v>2562</v>
       </c>
       <c r="M82">
-        <v>1576.511963064168</v>
+        <v>1596.21836260247</v>
       </c>
       <c r="N82">
-        <v>985.4880369358318</v>
+        <v>965.7816373975297</v>
       </c>
       <c r="O82">
-        <v>143.8812533926314</v>
+        <v>141.0041190600393</v>
       </c>
       <c r="P82">
-        <v>841.6067835432004</v>
+        <v>824.7775183374904</v>
       </c>
       <c r="Q82">
-        <v>2558.6067835432</v>
+        <v>2541.777518337491</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3623795906242917</v>
+        <v>0.3784907992909314</v>
       </c>
       <c r="T82">
-        <v>7.311306942824292</v>
+        <v>7.68339028385523</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.625106602439223</v>
+        <v>1.605043557964664</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8575,22 +8575,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.124347143865277</v>
+        <v>0.1244318096056956</v>
       </c>
       <c r="C83">
-        <v>2627.097963089487</v>
+        <v>2344.92927385911</v>
       </c>
       <c r="D83">
-        <v>20608.3877071854</v>
+        <v>20586.1979036846</v>
       </c>
       <c r="E83">
-        <v>17634.901171138</v>
+        <v>17894.88005686758</v>
       </c>
       <c r="F83">
-        <v>21058.28974409591</v>
+        <v>21318.26862982549</v>
       </c>
       <c r="G83">
         <v>3077</v>
@@ -8611,28 +8611,28 @@
         <v>2562</v>
       </c>
       <c r="M83">
-        <v>1596.21836260247</v>
+        <v>1615.924762140772</v>
       </c>
       <c r="N83">
-        <v>965.7816373975297</v>
+        <v>946.0752378592276</v>
       </c>
       <c r="O83">
-        <v>141.0041190600393</v>
+        <v>138.1269847274472</v>
       </c>
       <c r="P83">
-        <v>824.7775183374904</v>
+        <v>807.9482531317803</v>
       </c>
       <c r="Q83">
-        <v>2541.777518337491</v>
+        <v>2524.94825313178</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3784907992909314</v>
+        <v>0.3963921422538643</v>
       </c>
       <c r="T83">
-        <v>7.68339028385523</v>
+        <v>8.09681621833405</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.605043557964664</v>
+        <v>1.585469856038266</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8657,22 +8657,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1244318096056956</v>
+        <v>0.1245164753461141</v>
       </c>
       <c r="C84">
-        <v>2344.92927385911</v>
+        <v>2062.808318375326</v>
       </c>
       <c r="D84">
-        <v>20586.1979036846</v>
+        <v>20564.0558339304</v>
       </c>
       <c r="E84">
-        <v>17894.88005686758</v>
+        <v>18154.85894259715</v>
       </c>
       <c r="F84">
-        <v>21318.26862982549</v>
+        <v>21578.24751555507</v>
       </c>
       <c r="G84">
         <v>3077</v>
@@ -8693,28 +8693,28 @@
         <v>2562</v>
       </c>
       <c r="M84">
-        <v>1615.924762140772</v>
+        <v>1635.631161679074</v>
       </c>
       <c r="N84">
-        <v>946.0752378592276</v>
+        <v>926.3688383209255</v>
       </c>
       <c r="O84">
-        <v>138.1269847274472</v>
+        <v>135.2498503948551</v>
       </c>
       <c r="P84">
-        <v>807.9482531317803</v>
+        <v>791.1189879260704</v>
       </c>
       <c r="Q84">
-        <v>2524.94825313178</v>
+        <v>2508.118987926071</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3963921422538643</v>
+        <v>0.4163995255653774</v>
       </c>
       <c r="T84">
-        <v>8.09681621833405</v>
+        <v>8.558880498045671</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.585469856038266</v>
+        <v>1.566367809579974</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8739,22 +8739,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1245164753461141</v>
+        <v>0.1246011410865328</v>
       </c>
       <c r="C85">
-        <v>2062.808318375326</v>
+        <v>1780.734942779443</v>
       </c>
       <c r="D85">
-        <v>20564.0558339304</v>
+        <v>20541.96134406409</v>
       </c>
       <c r="E85">
-        <v>18154.85894259715</v>
+        <v>18414.83782832673</v>
       </c>
       <c r="F85">
-        <v>21578.24751555507</v>
+        <v>21838.22640128465</v>
       </c>
       <c r="G85">
         <v>3077</v>
@@ -8775,28 +8775,28 @@
         <v>2562</v>
       </c>
       <c r="M85">
-        <v>1635.631161679074</v>
+        <v>1655.337561217377</v>
       </c>
       <c r="N85">
-        <v>926.3688383209255</v>
+        <v>906.6624387826234</v>
       </c>
       <c r="O85">
-        <v>135.2498503948551</v>
+        <v>132.372716062263</v>
       </c>
       <c r="P85">
-        <v>791.1189879260704</v>
+        <v>774.2897227203605</v>
       </c>
       <c r="Q85">
-        <v>2508.118987926071</v>
+        <v>2491.28972272036</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4163995255653774</v>
+        <v>0.4389078317908298</v>
       </c>
       <c r="T85">
-        <v>8.558880498045671</v>
+        <v>9.078702812721247</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.566367809579974</v>
+        <v>1.547720573751641</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8821,22 +8821,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1246011410865328</v>
+        <v>0.1246858068269514</v>
       </c>
       <c r="C86">
-        <v>1780.734942779443</v>
+        <v>1498.708993873333</v>
       </c>
       <c r="D86">
-        <v>20541.96134406409</v>
+        <v>20519.91428088756</v>
       </c>
       <c r="E86">
-        <v>18414.83782832673</v>
+        <v>18674.81671405631</v>
       </c>
       <c r="F86">
-        <v>21838.22640128465</v>
+        <v>22098.20528701423</v>
       </c>
       <c r="G86">
         <v>3077</v>
@@ -8857,28 +8857,28 @@
         <v>2562</v>
       </c>
       <c r="M86">
-        <v>1655.337561217377</v>
+        <v>1675.043960755679</v>
       </c>
       <c r="N86">
-        <v>906.6624387826234</v>
+        <v>886.9560392443213</v>
       </c>
       <c r="O86">
-        <v>132.372716062263</v>
+        <v>129.4955817296709</v>
       </c>
       <c r="P86">
-        <v>774.2897227203605</v>
+        <v>757.4604575146504</v>
       </c>
       <c r="Q86">
-        <v>2491.28972272036</v>
+        <v>2474.46045751465</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4389078317908295</v>
+        <v>0.4644172455130088</v>
       </c>
       <c r="T86">
-        <v>9.078702812721239</v>
+        <v>9.667834769353556</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.547720573751641</v>
+        <v>1.529512096413386</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1246858068269514</v>
+        <v>0.1247704725673699</v>
       </c>
       <c r="C87">
-        <v>1498.708993873333</v>
+        <v>1216.730319115832</v>
       </c>
       <c r="D87">
-        <v>20519.91428088756</v>
+        <v>20497.91449185964</v>
       </c>
       <c r="E87">
-        <v>18674.81671405631</v>
+        <v>18934.79559978589</v>
       </c>
       <c r="F87">
-        <v>22098.20528701423</v>
+        <v>22358.18417274381</v>
       </c>
       <c r="G87">
         <v>3077</v>
@@ -8939,28 +8939,28 @@
         <v>2562</v>
       </c>
       <c r="M87">
-        <v>1675.043960755679</v>
+        <v>1694.750360293981</v>
       </c>
       <c r="N87">
-        <v>886.9560392443213</v>
+        <v>867.2496397060193</v>
       </c>
       <c r="O87">
-        <v>129.4955817296709</v>
+        <v>126.6184473970788</v>
       </c>
       <c r="P87">
-        <v>757.4604575146504</v>
+        <v>740.6311923089404</v>
       </c>
       <c r="Q87">
-        <v>2474.46045751465</v>
+        <v>2457.631192308941</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4644172455130088</v>
+        <v>0.4935708611954995</v>
       </c>
       <c r="T87">
-        <v>9.667834769353556</v>
+        <v>10.34112843407621</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.529512096413386</v>
+        <v>1.511727072036487</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8985,22 +8985,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1247704725673699</v>
+        <v>0.1354054543077886</v>
       </c>
       <c r="C88">
-        <v>1216.730319115832</v>
+        <v>-1476.079782320678</v>
       </c>
       <c r="D88">
-        <v>20497.91449185964</v>
+        <v>18065.08327615271</v>
       </c>
       <c r="E88">
-        <v>18934.79559978589</v>
+        <v>19194.77448551547</v>
       </c>
       <c r="F88">
-        <v>22358.18417274381</v>
+        <v>22618.16305847339</v>
       </c>
       <c r="G88">
         <v>3077</v>
@@ -9021,45 +9021,45 @@
         <v>2562</v>
       </c>
       <c r="M88">
-        <v>1694.750360293981</v>
+        <v>2035.634675262605</v>
       </c>
       <c r="N88">
-        <v>867.2496397060193</v>
+        <v>526.3653247373952</v>
       </c>
       <c r="O88">
-        <v>126.6184473970788</v>
+        <v>76.84933741165969</v>
       </c>
       <c r="P88">
-        <v>740.6311923089404</v>
+        <v>449.5159873257355</v>
       </c>
       <c r="Q88">
-        <v>2457.631192308941</v>
+        <v>2166.515987325735</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4935708611954995</v>
+        <v>0.5272096485214502</v>
       </c>
       <c r="T88">
-        <v>10.34112843407621</v>
+        <v>11.11800573952541</v>
       </c>
       <c r="U88">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V88">
         <v>0.146</v>
       </c>
       <c r="W88">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.511727072036487</v>
+        <v>1.258575534762637</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9067,22 +9067,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1354054543077886</v>
+        <v>0.1584685634060725</v>
       </c>
       <c r="C89">
-        <v>-1476.079782320678</v>
+        <v>-5433.957832397278</v>
       </c>
       <c r="D89">
-        <v>18065.08327615271</v>
+        <v>14367.18411180569</v>
       </c>
       <c r="E89">
-        <v>19194.77448551547</v>
+        <v>19454.75337124505</v>
       </c>
       <c r="F89">
-        <v>22618.16305847339</v>
+        <v>22878.14194420297</v>
       </c>
       <c r="G89">
         <v>3077</v>
@@ -9103,45 +9103,45 @@
         <v>2562</v>
       </c>
       <c r="M89">
-        <v>2035.634675262605</v>
+        <v>2713.347634582472</v>
       </c>
       <c r="N89">
-        <v>526.3653247373952</v>
+        <v>-151.347634582472</v>
       </c>
       <c r="O89">
-        <v>76.84933741165969</v>
+        <v>-22.09675464904091</v>
       </c>
       <c r="P89">
-        <v>449.5159873257355</v>
+        <v>-129.2508799334311</v>
       </c>
       <c r="Q89">
-        <v>2166.515987325735</v>
+        <v>1587.749120066569</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5272096485214502</v>
+        <v>0.5707362267031002</v>
       </c>
       <c r="T89">
-        <v>11.11800573952541</v>
+        <v>12.12323849198846</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.146</v>
+        <v>0.1378562758537053</v>
       </c>
       <c r="W89">
-        <v>0.07686</v>
+        <v>0.1022502456837506</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.258575534762637</v>
+        <v>0.9442210674911321</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9149,22 +9149,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1584685634060725</v>
+        <v>0.1591965634060725</v>
       </c>
       <c r="C90">
-        <v>-5433.957832397278</v>
+        <v>-5786.173287906666</v>
       </c>
       <c r="D90">
-        <v>14367.18411180569</v>
+        <v>14274.94754202588</v>
       </c>
       <c r="E90">
-        <v>19454.75337124505</v>
+        <v>19714.73225697463</v>
       </c>
       <c r="F90">
-        <v>22878.14194420297</v>
+        <v>23138.12082993254</v>
       </c>
       <c r="G90">
         <v>3077</v>
@@ -9185,37 +9185,37 @@
         <v>2562</v>
       </c>
       <c r="M90">
-        <v>2713.347634582472</v>
+        <v>2744.18113043</v>
       </c>
       <c r="N90">
-        <v>-151.347634582472</v>
+        <v>-182.1811304299999</v>
       </c>
       <c r="O90">
-        <v>-22.09675464904091</v>
+        <v>-26.59844504277999</v>
       </c>
       <c r="P90">
-        <v>-129.2508799334311</v>
+        <v>-155.58268538722</v>
       </c>
       <c r="Q90">
-        <v>1587.749120066569</v>
+        <v>1561.41731461278</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5707362267031002</v>
+        <v>0.6184577018579276</v>
       </c>
       <c r="T90">
-        <v>12.12323849198846</v>
+        <v>13.22535108216923</v>
       </c>
       <c r="U90">
         <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.1378562758537053</v>
+        <v>0.1363073289340007</v>
       </c>
       <c r="W90">
-        <v>0.1022502456837506</v>
+        <v>0.1024339507884275</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9442210674911321</v>
+        <v>0.9336118420137037</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9231,22 +9231,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1591965634060725</v>
+        <v>0.1599245634060725</v>
       </c>
       <c r="C91">
-        <v>-5786.173287906666</v>
+        <v>-6137.21199021244</v>
       </c>
       <c r="D91">
-        <v>14274.94754202588</v>
+        <v>14183.88772544969</v>
       </c>
       <c r="E91">
-        <v>19714.73225697463</v>
+        <v>19974.71114270421</v>
       </c>
       <c r="F91">
-        <v>23138.12082993254</v>
+        <v>23398.09971566212</v>
       </c>
       <c r="G91">
         <v>3077</v>
@@ -9267,37 +9267,37 @@
         <v>2562</v>
       </c>
       <c r="M91">
-        <v>2744.18113043</v>
+        <v>2775.014626277528</v>
       </c>
       <c r="N91">
-        <v>-182.1811304299999</v>
+        <v>-213.0146262775279</v>
       </c>
       <c r="O91">
-        <v>-26.59844504277999</v>
+        <v>-31.10013543651907</v>
       </c>
       <c r="P91">
-        <v>-155.58268538722</v>
+        <v>-181.9144908410088</v>
       </c>
       <c r="Q91">
-        <v>1561.41731461278</v>
+        <v>1535.085509158991</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6184577018579276</v>
+        <v>0.6757234720437204</v>
       </c>
       <c r="T91">
-        <v>13.22535108216923</v>
+        <v>14.54788619038616</v>
       </c>
       <c r="U91">
         <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.1363073289340007</v>
+        <v>0.1347928030569563</v>
       </c>
       <c r="W91">
-        <v>0.1024339507884275</v>
+        <v>0.102613573557445</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9336118420137037</v>
+        <v>0.9232383771024404</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9313,22 +9313,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1599245634060725</v>
+        <v>0.1606525634060725</v>
       </c>
       <c r="C92">
-        <v>-6137.21199021244</v>
+        <v>-6487.096316081126</v>
       </c>
       <c r="D92">
-        <v>14183.88772544969</v>
+        <v>14093.98228531058</v>
       </c>
       <c r="E92">
-        <v>19974.71114270421</v>
+        <v>20234.69002843379</v>
       </c>
       <c r="F92">
-        <v>23398.09971566212</v>
+        <v>23658.07860139171</v>
       </c>
       <c r="G92">
         <v>3077</v>
@@ -9349,37 +9349,37 @@
         <v>2562</v>
       </c>
       <c r="M92">
-        <v>2775.014626277528</v>
+        <v>2805.848122125057</v>
       </c>
       <c r="N92">
-        <v>-213.0146262775279</v>
+        <v>-243.8481221250568</v>
       </c>
       <c r="O92">
-        <v>-31.10013543651907</v>
+        <v>-35.60182583025829</v>
       </c>
       <c r="P92">
-        <v>-181.9144908410088</v>
+        <v>-208.2462962947985</v>
       </c>
       <c r="Q92">
-        <v>1535.085509158991</v>
+        <v>1508.753703705202</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6757234720437204</v>
+        <v>0.7457149689374671</v>
       </c>
       <c r="T92">
-        <v>14.54788619038616</v>
+        <v>16.16431798931795</v>
       </c>
       <c r="U92">
         <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.1347928030569563</v>
+        <v>0.1333115634629238</v>
       </c>
       <c r="W92">
-        <v>0.102613573557445</v>
+        <v>0.1027892485732972</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9232383771024404</v>
+        <v>0.9130929004309848</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9395,22 +9395,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1606525634060725</v>
+        <v>0.1613805634060725</v>
       </c>
       <c r="C93">
-        <v>-6487.096316081126</v>
+        <v>-6835.84807850674</v>
       </c>
       <c r="D93">
-        <v>14093.98228531058</v>
+        <v>14005.20940861454</v>
       </c>
       <c r="E93">
-        <v>20234.69002843379</v>
+        <v>20494.66891416337</v>
       </c>
       <c r="F93">
-        <v>23658.07860139171</v>
+        <v>23918.05748712128</v>
       </c>
       <c r="G93">
         <v>3077</v>
@@ -9431,37 +9431,37 @@
         <v>2562</v>
       </c>
       <c r="M93">
-        <v>2805.848122125057</v>
+        <v>2836.681617972585</v>
       </c>
       <c r="N93">
-        <v>-243.8481221250568</v>
+        <v>-274.6816179725847</v>
       </c>
       <c r="O93">
-        <v>-35.60182583025829</v>
+        <v>-40.10351622399737</v>
       </c>
       <c r="P93">
-        <v>-208.2462962947985</v>
+        <v>-234.5781017485874</v>
       </c>
       <c r="Q93">
-        <v>1508.753703705202</v>
+        <v>1482.421898251413</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7457149689374671</v>
+        <v>0.8332043400546508</v>
       </c>
       <c r="T93">
-        <v>16.16431798931795</v>
+        <v>18.18485773798271</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.1333115634629238</v>
+        <v>0.1318625247296311</v>
       </c>
       <c r="W93">
-        <v>0.1027892485732972</v>
+        <v>0.1029611045670658</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9130929004309848</v>
+        <v>0.9031679776002133</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9477,22 +9477,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1613805634060725</v>
+        <v>0.1621085634060725</v>
       </c>
       <c r="C94">
-        <v>-6835.84807850674</v>
+        <v>-7183.48854435467</v>
       </c>
       <c r="D94">
-        <v>14005.20940861454</v>
+        <v>13917.54782849619</v>
       </c>
       <c r="E94">
-        <v>20494.66891416337</v>
+        <v>20754.64779989295</v>
       </c>
       <c r="F94">
-        <v>23918.05748712128</v>
+        <v>24178.03637285086</v>
       </c>
       <c r="G94">
         <v>3077</v>
@@ -9513,37 +9513,37 @@
         <v>2562</v>
       </c>
       <c r="M94">
-        <v>2836.681617972585</v>
+        <v>2867.515113820113</v>
       </c>
       <c r="N94">
-        <v>-274.6816179725847</v>
+        <v>-305.5151138201127</v>
       </c>
       <c r="O94">
-        <v>-40.10351622399737</v>
+        <v>-44.60520661773645</v>
       </c>
       <c r="P94">
-        <v>-234.5781017485874</v>
+        <v>-260.9099072023762</v>
       </c>
       <c r="Q94">
-        <v>1482.421898251413</v>
+        <v>1456.090092797624</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8332043400546508</v>
+        <v>0.9456906743481727</v>
       </c>
       <c r="T94">
-        <v>18.18485773798271</v>
+        <v>20.78269455769453</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.1318625247296311</v>
+        <v>0.1304446481196351</v>
       </c>
       <c r="W94">
-        <v>0.1029611045670658</v>
+        <v>0.1031292647330113</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9031679776002133</v>
+        <v>0.8934564939701034</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9559,22 +9559,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1621085634060725</v>
+        <v>0.1628365634060725</v>
       </c>
       <c r="C95">
-        <v>-7183.48854435467</v>
+        <v>-7530.038451346987</v>
       </c>
       <c r="D95">
-        <v>13917.54782849619</v>
+        <v>13830.97680723346</v>
       </c>
       <c r="E95">
-        <v>20754.64779989295</v>
+        <v>21014.62668562253</v>
       </c>
       <c r="F95">
-        <v>24178.03637285086</v>
+        <v>24438.01525858044</v>
       </c>
       <c r="G95">
         <v>3077</v>
@@ -9595,37 +9595,37 @@
         <v>2562</v>
       </c>
       <c r="M95">
-        <v>2867.515113820113</v>
+        <v>2898.348609667641</v>
       </c>
       <c r="N95">
-        <v>-305.5151138201127</v>
+        <v>-336.3486096676406</v>
       </c>
       <c r="O95">
-        <v>-44.60520661773645</v>
+        <v>-49.10689701147553</v>
       </c>
       <c r="P95">
-        <v>-260.9099072023762</v>
+        <v>-287.2417126561651</v>
       </c>
       <c r="Q95">
-        <v>1456.090092797624</v>
+        <v>1429.758287343835</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9456906743481727</v>
+        <v>1.095672453406201</v>
       </c>
       <c r="T95">
-        <v>20.78269455769453</v>
+        <v>24.24647698397695</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.1304446481196351</v>
+        <v>0.1290569390970858</v>
       </c>
       <c r="W95">
-        <v>0.1031292647330113</v>
+        <v>0.1032938470230856</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8934564939701034</v>
+        <v>0.8839516376512726</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9641,22 +9641,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1628365634060725</v>
+        <v>0.1635645634060726</v>
       </c>
       <c r="C96">
-        <v>-7530.038451346987</v>
+        <v>-7875.518024417863</v>
       </c>
       <c r="D96">
-        <v>13830.97680723346</v>
+        <v>13745.47611989216</v>
       </c>
       <c r="E96">
-        <v>21014.62668562253</v>
+        <v>21274.60557135211</v>
       </c>
       <c r="F96">
-        <v>24438.01525858044</v>
+        <v>24697.99414431002</v>
       </c>
       <c r="G96">
         <v>3077</v>
@@ -9677,37 +9677,37 @@
         <v>2562</v>
       </c>
       <c r="M96">
-        <v>2898.348609667641</v>
+        <v>2929.182105515169</v>
       </c>
       <c r="N96">
-        <v>-336.3486096676406</v>
+        <v>-367.182105515169</v>
       </c>
       <c r="O96">
-        <v>-49.10689701147553</v>
+        <v>-53.60858740521468</v>
       </c>
       <c r="P96">
-        <v>-287.2417126561651</v>
+        <v>-313.5735181099544</v>
       </c>
       <c r="Q96">
-        <v>1429.758287343835</v>
+        <v>1403.426481890046</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.095672453406201</v>
+        <v>1.305646944087443</v>
       </c>
       <c r="T96">
-        <v>24.24647698397695</v>
+        <v>29.09577238077235</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.1290569390970858</v>
+        <v>0.127698445001327</v>
       </c>
       <c r="W96">
-        <v>0.1032938470230856</v>
+        <v>0.1034549644228426</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8839516376512726</v>
+        <v>0.8746468835707328</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9723,22 +9723,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1635645634060726</v>
+        <v>0.1642925634060725</v>
       </c>
       <c r="C97">
-        <v>-7875.518024417863</v>
+        <v>-8219.946991465942</v>
       </c>
       <c r="D97">
-        <v>13745.47611989216</v>
+        <v>13661.02603857366</v>
       </c>
       <c r="E97">
-        <v>21274.60557135211</v>
+        <v>21534.58445708168</v>
       </c>
       <c r="F97">
-        <v>24697.99414431002</v>
+        <v>24957.9730300396</v>
       </c>
       <c r="G97">
         <v>3077</v>
@@ -9759,37 +9759,37 @@
         <v>2562</v>
       </c>
       <c r="M97">
-        <v>2929.182105515169</v>
+        <v>2960.015601362697</v>
       </c>
       <c r="N97">
-        <v>-367.182105515169</v>
+        <v>-398.015601362697</v>
       </c>
       <c r="O97">
-        <v>-53.60858740521468</v>
+        <v>-58.11027779895376</v>
       </c>
       <c r="P97">
-        <v>-313.5735181099544</v>
+        <v>-339.9053235637433</v>
       </c>
       <c r="Q97">
-        <v>1403.426481890046</v>
+        <v>1377.094676436257</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.305646944087443</v>
+        <v>1.620608680109304</v>
       </c>
       <c r="T97">
-        <v>29.09577238077235</v>
+        <v>36.36971547596546</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.127698445001327</v>
+        <v>0.1263682528658965</v>
       </c>
       <c r="W97">
-        <v>0.1034549644228426</v>
+        <v>0.1036127252101047</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8746468835707328</v>
+        <v>0.8655359785335377</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9805,22 +9805,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1642925634060726</v>
+        <v>0.1650205634060725</v>
       </c>
       <c r="C98">
-        <v>-8219.946991465949</v>
+        <v>-8563.344598529759</v>
       </c>
       <c r="D98">
-        <v>13661.02603857365</v>
+        <v>13577.60731723942</v>
       </c>
       <c r="E98">
-        <v>21534.58445708168</v>
+        <v>21794.56334281126</v>
       </c>
       <c r="F98">
-        <v>24957.9730300396</v>
+        <v>25217.95191576918</v>
       </c>
       <c r="G98">
         <v>3077</v>
@@ -9841,37 +9841,37 @@
         <v>2562</v>
       </c>
       <c r="M98">
-        <v>2960.015601362697</v>
+        <v>2990.849097210225</v>
       </c>
       <c r="N98">
-        <v>-398.0156013626965</v>
+        <v>-428.849097210225</v>
       </c>
       <c r="O98">
-        <v>-58.11027779895369</v>
+        <v>-62.61196819269284</v>
       </c>
       <c r="P98">
-        <v>-339.9053235637429</v>
+        <v>-366.2371290175321</v>
       </c>
       <c r="Q98">
-        <v>1377.094676436257</v>
+        <v>1350.762870982468</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.6206086801093</v>
+        <v>2.1455449068124</v>
       </c>
       <c r="T98">
-        <v>36.36971547596536</v>
+        <v>48.49295396795382</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.1263682528658965</v>
+        <v>0.1250654873724336</v>
       </c>
       <c r="W98">
-        <v>0.1036127252101047</v>
+        <v>0.1037672331976294</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8655359785335378</v>
+        <v>0.8566129272084497</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9887,22 +9887,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1650205634060725</v>
+        <v>0.1657485634060725</v>
       </c>
       <c r="C99">
-        <v>-8563.344598529759</v>
+        <v>-8905.729624410324</v>
       </c>
       <c r="D99">
-        <v>13577.60731723942</v>
+        <v>13495.20117708843</v>
       </c>
       <c r="E99">
-        <v>21794.56334281126</v>
+        <v>22054.54222854084</v>
       </c>
       <c r="F99">
-        <v>25217.95191576918</v>
+        <v>25477.93080149876</v>
       </c>
       <c r="G99">
         <v>3077</v>
@@ -9923,37 +9923,37 @@
         <v>2562</v>
       </c>
       <c r="M99">
-        <v>2990.849097210225</v>
+        <v>3021.682593057753</v>
       </c>
       <c r="N99">
-        <v>-428.849097210225</v>
+        <v>-459.6825930577529</v>
       </c>
       <c r="O99">
-        <v>-62.61196819269284</v>
+        <v>-67.11365858643192</v>
       </c>
       <c r="P99">
-        <v>-366.2371290175321</v>
+        <v>-392.568934471321</v>
       </c>
       <c r="Q99">
-        <v>1350.762870982468</v>
+        <v>1324.431065528679</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.1455449068124</v>
+        <v>3.195417360218598</v>
       </c>
       <c r="T99">
-        <v>48.49295396795382</v>
+        <v>72.73943095193071</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.1250654873724336</v>
+        <v>0.1237893089298578</v>
       </c>
       <c r="W99">
-        <v>0.1037672331976294</v>
+        <v>0.1039185879609189</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8566129272084497</v>
+        <v>0.8478719789716289</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9969,22 +9969,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1657485634060725</v>
+        <v>0.1664765634060725</v>
       </c>
       <c r="C100">
-        <v>-8905.729624410324</v>
+        <v>-9247.120394764603</v>
       </c>
       <c r="D100">
-        <v>13495.20117708843</v>
+        <v>13413.78929246373</v>
       </c>
       <c r="E100">
-        <v>22054.54222854084</v>
+        <v>22314.52111427042</v>
       </c>
       <c r="F100">
-        <v>25477.93080149876</v>
+        <v>25737.90968722834</v>
       </c>
       <c r="G100">
         <v>3077</v>
@@ -10005,37 +10005,37 @@
         <v>2562</v>
       </c>
       <c r="M100">
-        <v>3021.682593057753</v>
+        <v>3052.516088905281</v>
       </c>
       <c r="N100">
-        <v>-459.6825930577529</v>
+        <v>-490.5160889052809</v>
       </c>
       <c r="O100">
-        <v>-67.11365858643192</v>
+        <v>-71.61534898017101</v>
       </c>
       <c r="P100">
-        <v>-392.568934471321</v>
+        <v>-418.9007399251099</v>
       </c>
       <c r="Q100">
-        <v>1324.431065528679</v>
+        <v>1298.09926007489</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.195417360218598</v>
+        <v>6.345034720437199</v>
       </c>
       <c r="T100">
-        <v>72.73943095193071</v>
+        <v>145.4788619038615</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.1237893089298578</v>
+        <v>0.1225389118699603</v>
       </c>
       <c r="W100">
-        <v>0.1039185879609189</v>
+        <v>0.1040668850522227</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10043,91 +10043,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8478719789716289</v>
+        <v>0.8393076155476731</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1664765634060725</v>
-      </c>
-      <c r="C101">
-        <v>-9247.120394764603</v>
-      </c>
-      <c r="D101">
-        <v>13413.78929246373</v>
-      </c>
-      <c r="E101">
-        <v>22314.52111427042</v>
-      </c>
-      <c r="F101">
-        <v>25737.90968722834</v>
-      </c>
-      <c r="G101">
-        <v>3077</v>
-      </c>
-      <c r="H101">
-        <v>22574.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4279</v>
-      </c>
-      <c r="K101">
-        <v>1717</v>
-      </c>
-      <c r="L101">
-        <v>2562</v>
-      </c>
-      <c r="M101">
-        <v>3052.516088905281</v>
-      </c>
-      <c r="N101">
-        <v>-490.5160889052809</v>
-      </c>
-      <c r="O101">
-        <v>-71.61534898017101</v>
-      </c>
-      <c r="P101">
-        <v>-418.9007399251099</v>
-      </c>
-      <c r="Q101">
-        <v>1298.09926007489</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.345034720437199</v>
-      </c>
-      <c r="T101">
-        <v>145.4788619038615</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.1225389118699603</v>
-      </c>
-      <c r="W101">
-        <v>0.1040668850522227</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8393076155476731</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
